--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="458">
   <si>
     <t>id</t>
   </si>
@@ -956,7 +956,7 @@
     <t>ボスシールド</t>
   </si>
   <si>
-    <t>司令官行動</t>
+    <t>行動</t>
   </si>
   <si>
     <t>2/2×4</t>
@@ -965,27 +965,39 @@
     <t>3/3</t>
   </si>
   <si>
+    <t>ヘイト</t>
+  </si>
+  <si>
+    <t>シールド</t>
+  </si>
+  <si>
+    <t>召喚</t>
+  </si>
+  <si>
+    <t>鼓舞</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>3/2×5</t>
+  </si>
+  <si>
+    <t>強化/召喚/鼓舞/シールドからランダム</t>
+  </si>
+  <si>
+    <t>ボス戦</t>
+  </si>
+  <si>
+    <t>8/6×4</t>
+  </si>
+  <si>
+    <t>6/6</t>
+  </si>
+  <si>
     <t>なし（スキップ）</t>
   </si>
   <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>3/2×5</t>
-  </si>
-  <si>
-    <t>強化/召喚/鼓舞/シールドからランダム</t>
-  </si>
-  <si>
-    <t>ボス戦</t>
-  </si>
-  <si>
-    <t>8/6×4</t>
-  </si>
-  <si>
-    <t>6/6</t>
-  </si>
-  <si>
     <t>9/6×4</t>
   </si>
   <si>
@@ -1347,9 +1359,6 @@
   </si>
   <si>
     <t>行動回数+n</t>
-  </si>
-  <si>
-    <t>行動</t>
   </si>
   <si>
     <t>ライフ</t>
@@ -1449,7 +1458,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1461,6 +1470,9 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -7507,7 +7519,7 @@
       <c r="H1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="4" t="s">
         <v>311</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -7535,7 +7547,7 @@
         <v>313</v>
       </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
+      <c r="I2" s="5" t="s">
         <v>314</v>
       </c>
       <c r="J2" s="2"/>
@@ -7561,8 +7573,8 @@
         <v>313</v>
       </c>
       <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>314</v>
+      <c r="I3" s="6" t="s">
+        <v>315</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -7587,8 +7599,8 @@
         <v>313</v>
       </c>
       <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
-        <v>314</v>
+      <c r="I4" s="5" t="s">
+        <v>316</v>
       </c>
       <c r="J4" s="2"/>
     </row>
@@ -7613,8 +7625,8 @@
         <v>313</v>
       </c>
       <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
-        <v>314</v>
+      <c r="I5" s="6" t="s">
+        <v>317</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -7629,25 +7641,25 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E6" s="2">
         <v>1.0</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="5">
         <v>1.0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="7">
@@ -7665,14 +7677,14 @@
         <v>2.0</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H7" s="3"/>
       <c r="I7" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -7691,14 +7703,14 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J8" s="2"/>
     </row>
@@ -7717,14 +7729,14 @@
         <v>2.0</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="H9" s="3"/>
       <c r="I9" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -7743,14 +7755,14 @@
         <v>2.0</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J10" s="2"/>
     </row>
@@ -7765,25 +7777,25 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E11" s="3">
         <v>2.0</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="G11" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="H11" s="5">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>317</v>
-      </c>
       <c r="J11" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="12">
@@ -7801,14 +7813,14 @@
         <v>5.0</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>191</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2"/>
     </row>
@@ -7827,14 +7839,14 @@
         <v>5.0</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G13" s="3" t="s">
         <v>191</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J13" s="3"/>
     </row>
@@ -7853,14 +7865,14 @@
         <v>5.0</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>191</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J14" s="2"/>
     </row>
@@ -7879,14 +7891,14 @@
         <v>5.0</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>191</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J15" s="3"/>
     </row>
@@ -7901,25 +7913,25 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E16" s="2">
         <v>5.0</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="5">
         <v>3.0</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="17">
@@ -7937,14 +7949,14 @@
         <v>15.0</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J17" s="3"/>
     </row>
@@ -7963,14 +7975,14 @@
         <v>15.0</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J18" s="2"/>
     </row>
@@ -7989,14 +8001,14 @@
         <v>15.0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J19" s="3"/>
     </row>
@@ -8015,14 +8027,14 @@
         <v>15.0</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="J20" s="2"/>
     </row>
@@ -8037,25 +8049,25 @@
         <v>4.0</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="E21" s="3">
         <v>15.0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="H21" s="3">
         <v>8.0</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -9063,22 +9075,22 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>237</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2">
@@ -9086,16 +9098,16 @@
         <v>136</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>134</v>
@@ -9106,16 +9118,16 @@
         <v>144</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="F3" s="3" t="s">
         <v>143</v>
@@ -9126,14 +9138,14 @@
         <v>150</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D4" s="2"/>
       <c r="E4" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>149</v>
@@ -9144,14 +9156,14 @@
         <v>155</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>154</v>
@@ -9162,16 +9174,16 @@
         <v>160</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>159</v>
@@ -9182,16 +9194,16 @@
         <v>165</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>164</v>
@@ -9202,16 +9214,16 @@
         <v>173</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>172</v>
@@ -9222,16 +9234,16 @@
         <v>181</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>180</v>
@@ -9242,16 +9254,16 @@
         <v>189</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>188</v>
@@ -9262,16 +9274,16 @@
         <v>197</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>196</v>
@@ -9282,16 +9294,16 @@
         <v>205</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>204</v>
@@ -9302,14 +9314,14 @@
         <v>214</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="F13" s="3" t="s">
         <v>212</v>
@@ -9320,16 +9332,16 @@
         <v>219</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>218</v>
@@ -9340,16 +9352,16 @@
         <v>224</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>223</v>
@@ -9360,16 +9372,16 @@
         <v>229</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>228</v>
@@ -9380,13 +9392,13 @@
         <v>234</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="E17" s="3" t="s">
         <v>235</v>
@@ -9403,14 +9415,14 @@
         <v>3</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
     </row>
     <row r="19">
@@ -9421,14 +9433,14 @@
         <v>3</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="D19" s="3"/>
       <c r="E19" s="3" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
     </row>
     <row r="20">
@@ -9439,11 +9451,11 @@
         <v>3</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>32</v>
@@ -9457,11 +9469,11 @@
         <v>3</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="D21" s="3"/>
       <c r="E21" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>38</v>
@@ -9475,13 +9487,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>45</v>
@@ -9495,16 +9507,16 @@
         <v>3</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -9515,11 +9527,11 @@
         <v>3</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="D24" s="2"/>
       <c r="E24" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
@@ -9533,11 +9545,11 @@
         <v>3</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>63</v>
@@ -9551,13 +9563,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
@@ -9571,13 +9583,13 @@
         <v>10</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>38</v>
@@ -9585,40 +9597,40 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>10</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -9629,13 +9641,13 @@
         <v>9</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>19</v>
@@ -9649,14 +9661,14 @@
         <v>9</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -9667,11 +9679,11 @@
         <v>9</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D32" s="2"/>
       <c r="E32" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>69</v>
@@ -9685,21 +9697,21 @@
         <v>9</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>409</v>
-      </c>
       <c r="E33" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="2" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>9</v>
@@ -9709,10 +9721,10 @@
       </c>
       <c r="D34" s="2"/>
       <c r="E34" s="2" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -9723,36 +9735,36 @@
         <v>9</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>9</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -9763,16 +9775,16 @@
         <v>9</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -9783,16 +9795,16 @@
         <v>9</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -9803,16 +9815,16 @@
         <v>9</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -9823,16 +9835,16 @@
         <v>9</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>442</v>
+        <v>311</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -9843,16 +9855,16 @@
         <v>9</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -9863,16 +9875,16 @@
         <v>9</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -9883,16 +9895,16 @@
         <v>9</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -9903,16 +9915,16 @@
         <v>9</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -6,15 +6,16 @@
     <sheet state="visible" name="指輪プール" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="魔法プール" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="エンチャント" sheetId="3" r:id="rId6"/>
-    <sheet state="visible" name="敵キーワード" sheetId="4" r:id="rId7"/>
-    <sheet state="visible" name="階層データ" sheetId="5" r:id="rId8"/>
+    <sheet state="visible" name="階層データ" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="敵キーワード" sheetId="5" r:id="rId8"/>
     <sheet state="visible" name="effect_id一覧" sheetId="6" r:id="rId9"/>
+    <sheet state="visible" name="詳細" sheetId="7" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId10" roundtripDataChecksum="vj01MYAh/gTIpRWU7kSSAMG3VCGKwqPnKnnjREiJ7Q0="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="oR6WWnaRS4TZNHfWdYaYsGHcZ+Zj8bf0mwnYIXJ7q9c="/>
     </ext>
   </extLst>
 </workbook>
@@ -842,6 +843,105 @@
     <t>召喚時から戦闘終了までヘイト状態</t>
   </si>
   <si>
+    <t>階層</t>
+  </si>
+  <si>
+    <t>power</t>
+  </si>
+  <si>
+    <t>grade</t>
+  </si>
+  <si>
+    <t>ボス</t>
+  </si>
+  <si>
+    <t>Grade係数</t>
+  </si>
+  <si>
+    <t>敵想定(4体均等時)</t>
+  </si>
+  <si>
+    <t>狼G相当の仲間(ATK/HP)</t>
+  </si>
+  <si>
+    <t>ボスシールド</t>
+  </si>
+  <si>
+    <t>行動</t>
+  </si>
+  <si>
+    <t>2/2×4</t>
+  </si>
+  <si>
+    <t>3/3</t>
+  </si>
+  <si>
+    <t>ヘイト</t>
+  </si>
+  <si>
+    <t>シールド</t>
+  </si>
+  <si>
+    <t>召喚</t>
+  </si>
+  <si>
+    <t>鼓舞</t>
+  </si>
+  <si>
+    <t>✓</t>
+  </si>
+  <si>
+    <t>3/2×5</t>
+  </si>
+  <si>
+    <t>強化/召喚/鼓舞/シールドからランダム</t>
+  </si>
+  <si>
+    <t>ボス戦</t>
+  </si>
+  <si>
+    <t>8/6×4</t>
+  </si>
+  <si>
+    <t>6/6</t>
+  </si>
+  <si>
+    <t>なし（スキップ）</t>
+  </si>
+  <si>
+    <t>9/6×4</t>
+  </si>
+  <si>
+    <t>10/7×4</t>
+  </si>
+  <si>
+    <t>11/8×4</t>
+  </si>
+  <si>
+    <t>13/9×5</t>
+  </si>
+  <si>
+    <t>12/9×4</t>
+  </si>
+  <si>
+    <t>15/10×4</t>
+  </si>
+  <si>
+    <t>15/10×5</t>
+  </si>
+  <si>
+    <t>37/27×4</t>
+  </si>
+  <si>
+    <t>45/45</t>
+  </si>
+  <si>
+    <t>44/30×4</t>
+  </si>
+  <si>
+    <t>44/31×5</t>
+  </si>
+  <si>
     <t>キーワード</t>
   </si>
   <si>
@@ -930,105 +1030,6 @@
   </si>
   <si>
     <t>1グループに1体のみ。先頭の敵に付与</t>
-  </si>
-  <si>
-    <t>階層</t>
-  </si>
-  <si>
-    <t>power</t>
-  </si>
-  <si>
-    <t>grade</t>
-  </si>
-  <si>
-    <t>ボス</t>
-  </si>
-  <si>
-    <t>Grade係数</t>
-  </si>
-  <si>
-    <t>敵想定(4体均等時)</t>
-  </si>
-  <si>
-    <t>狼G相当の仲間(ATK/HP)</t>
-  </si>
-  <si>
-    <t>ボスシールド</t>
-  </si>
-  <si>
-    <t>行動</t>
-  </si>
-  <si>
-    <t>2/2×4</t>
-  </si>
-  <si>
-    <t>3/3</t>
-  </si>
-  <si>
-    <t>ヘイト</t>
-  </si>
-  <si>
-    <t>シールド</t>
-  </si>
-  <si>
-    <t>召喚</t>
-  </si>
-  <si>
-    <t>鼓舞</t>
-  </si>
-  <si>
-    <t>✓</t>
-  </si>
-  <si>
-    <t>3/2×5</t>
-  </si>
-  <si>
-    <t>強化/召喚/鼓舞/シールドからランダム</t>
-  </si>
-  <si>
-    <t>ボス戦</t>
-  </si>
-  <si>
-    <t>8/6×4</t>
-  </si>
-  <si>
-    <t>6/6</t>
-  </si>
-  <si>
-    <t>なし（スキップ）</t>
-  </si>
-  <si>
-    <t>9/6×4</t>
-  </si>
-  <si>
-    <t>10/7×4</t>
-  </si>
-  <si>
-    <t>11/8×4</t>
-  </si>
-  <si>
-    <t>13/9×5</t>
-  </si>
-  <si>
-    <t>12/9×4</t>
-  </si>
-  <si>
-    <t>15/10×4</t>
-  </si>
-  <si>
-    <t>15/10×5</t>
-  </si>
-  <si>
-    <t>37/27×4</t>
-  </si>
-  <si>
-    <t>45/45</t>
-  </si>
-  <si>
-    <t>44/30×4</t>
-  </si>
-  <si>
-    <t>44/31×5</t>
   </si>
   <si>
     <t>effect_id</t>
@@ -1458,7 +1459,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1470,15 +1471,6 @@
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1509,6 +1501,10 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -6362,11 +6358,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="16.0"/>
-    <col customWidth="1" min="2" max="2" width="12.0"/>
-    <col customWidth="1" min="3" max="3" width="18.0"/>
-    <col customWidth="1" min="4" max="5" width="40.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="8.0"/>
+    <col customWidth="1" min="2" max="2" width="10.0"/>
+    <col customWidth="1" min="3" max="4" width="8.0"/>
+    <col customWidth="1" min="5" max="5" width="10.0"/>
+    <col customWidth="1" min="6" max="7" width="18.0"/>
+    <col customWidth="1" min="8" max="8" width="14.0"/>
+    <col customWidth="1" min="9" max="9" width="36.0"/>
+    <col customWidth="1" min="10" max="10" width="14.0"/>
+    <col customWidth="1" min="11" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
@@ -6385,110 +6385,566 @@
       <c r="E1" s="1" t="s">
         <v>277</v>
       </c>
+      <c r="F1" s="1" t="s">
+        <v>278</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>281</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="A2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="C2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>282</v>
       </c>
+      <c r="G2" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="J2" s="2"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="D3" s="3" t="s">
+      <c r="H3" s="3"/>
+      <c r="I3" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="B4" s="2">
+        <v>18.0</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="B5" s="3">
+        <v>23.0</v>
+      </c>
+      <c r="C5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="H5" s="3"/>
+      <c r="I5" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C4" s="2" t="s">
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="B6" s="2">
+        <v>31.0</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="G6" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1.0</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>290</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
+      <c r="J6" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="7">
+      <c r="A7" s="3">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="3">
+        <v>180.0</v>
+      </c>
+      <c r="C7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="G7" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3" t="s">
         <v>294</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="2">
+        <v>220.0</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="C6" s="2" t="s">
+      <c r="G8" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="3">
+        <v>270.0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G9" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H9" s="3"/>
+      <c r="I9" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J9" s="3"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="2">
+        <v>340.0</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="G10" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J10" s="2"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="3">
+        <v>600.0</v>
+      </c>
+      <c r="C11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>298</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
+      <c r="G11" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="H11" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="2">
+        <v>450.0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="C7" s="3" t="s">
+      <c r="G12" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J12" s="2"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="C13" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="3"/>
+      <c r="E13" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H13" s="3"/>
+      <c r="I13" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J13" s="3"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="2">
+        <v>450.0</v>
+      </c>
+      <c r="C14" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J14" s="2"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="3">
+        <v>585.0</v>
+      </c>
+      <c r="C15" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J15" s="3"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="2">
+        <v>765.0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="E16" s="2">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="E7" s="3" t="s">
+      <c r="G16" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3.0</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="3">
+        <v>4050.0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D17" s="3"/>
+      <c r="E17" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>302</v>
       </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
+      <c r="G17" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J17" s="3"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="2">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4050.0</v>
+      </c>
+      <c r="C18" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J18" s="2"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="3">
+        <v>4050.0</v>
+      </c>
+      <c r="C19" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="3"/>
+      <c r="E19" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J19" s="3"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="2">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="2">
+        <v>5265.0</v>
+      </c>
+      <c r="C20" s="2">
+        <v>4.0</v>
+      </c>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2">
+        <v>15.0</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="J20" s="2"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="3">
+        <v>6885.0</v>
+      </c>
+      <c r="C21" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="E21" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="H21" s="3">
+        <v>8.0</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>291</v>
+      </c>
+    </row>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -7483,593 +7939,133 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="8.0"/>
-    <col customWidth="1" min="2" max="2" width="10.0"/>
-    <col customWidth="1" min="3" max="4" width="8.0"/>
-    <col customWidth="1" min="5" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="7" width="18.0"/>
-    <col customWidth="1" min="8" max="8" width="14.0"/>
-    <col customWidth="1" min="9" max="9" width="36.0"/>
-    <col customWidth="1" min="10" max="10" width="14.0"/>
-    <col customWidth="1" min="11" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="16.0"/>
+    <col customWidth="1" min="2" max="2" width="12.0"/>
+    <col customWidth="1" min="3" max="3" width="18.0"/>
+    <col customWidth="1" min="4" max="5" width="40.0"/>
+    <col customWidth="1" min="6" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>307</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="H1" s="1" t="s">
         <v>310</v>
       </c>
-      <c r="I1" s="4" t="s">
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="B2" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="C2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="B2" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="C2" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="5" t="s">
+      <c r="D2" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="J2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>315</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="B3" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="C3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="A3" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="J3" s="3"/>
+      <c r="C3" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="B4" s="2">
-        <v>18.0</v>
-      </c>
-      <c r="C4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="A4" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="5" t="s">
-        <v>316</v>
-      </c>
-      <c r="J4" s="2"/>
+      <c r="C4" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>323</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="B5" s="3">
-        <v>23.0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="F5" s="3" t="s">
+      <c r="A5" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="J5" s="3"/>
+      <c r="C5" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>327</v>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="B6" s="2">
-        <v>31.0</v>
-      </c>
-      <c r="C6" s="2">
-        <v>1.0</v>
+      <c r="A6" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="H6" s="5">
-        <v>1.0</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>321</v>
+        <v>330</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3">
-        <v>180.0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="2">
-        <v>220.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="B9" s="3">
-        <v>270.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="2">
-        <v>340.0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3">
-        <v>600.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="H11" s="6">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="2">
-        <v>450.0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3">
-        <v>450.0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="2">
-        <v>450.0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3">
-        <v>585.0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="2">
-        <v>765.0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H16" s="5">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3">
-        <v>4050.0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F17" s="3" t="s">
+      <c r="A7" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="B7" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="C7" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3">
-        <v>4050.0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5265.0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="F20" s="2" t="s">
+      <c r="D7" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G20" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3">
-        <v>6885.0</v>
-      </c>
-      <c r="C21" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E21" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F21" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="G21" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="H21" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>321</v>
-      </c>
-    </row>
+    </row>
+    <row r="21" ht="15.75" customHeight="1"/>
     <row r="22" ht="15.75" customHeight="1"/>
     <row r="23" ht="15.75" customHeight="1"/>
     <row r="24" ht="15.75" customHeight="1"/>
@@ -9844,7 +9840,7 @@
         <v>445</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -10889,4 +10885,15 @@
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
+  <sheetData/>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -15,14 +15,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="oR6WWnaRS4TZNHfWdYaYsGHcZ+Zj8bf0mwnYIXJ7q9c="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="sMePMrDKIwiZ0AJ8bznhiMDdjuTpWZGWDhJCC3Kk++8="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="736" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="462">
   <si>
     <t>id</t>
   </si>
@@ -45,6 +45,12 @@
     <t>基本HP</t>
   </si>
   <si>
+    <t>上昇ATK</t>
+  </si>
+  <si>
+    <t>上昇HP</t>
+  </si>
+  <si>
     <t>アイコン</t>
   </si>
   <si>
@@ -93,6 +99,9 @@
     <t>盤面の全仲間ATK+2×Grade。狼が生存中に発動</t>
   </si>
   <si>
+    <t>2/+2×Grade</t>
+  </si>
+  <si>
     <t>r_hyena</t>
   </si>
   <si>
@@ -201,7 +210,7 @@
     <t>🐀</t>
   </si>
   <si>
-    <t>戦闘開始時に5体召喚。シナジー用</t>
+    <t>戦闘開始時に3体召喚。シナジー用</t>
   </si>
   <si>
     <t>r_skel</t>
@@ -303,7 +312,10 @@
     <t>adj_count</t>
   </si>
   <si>
-    <t>隣接する召喚指輪の召喚数+Grade</t>
+    <t>隣接する召喚指輪の召喚数+1</t>
+  </si>
+  <si>
+    <t>ユニーク</t>
   </si>
   <si>
     <t>r_lifereg</t>
@@ -1402,7 +1414,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -1419,6 +1431,12 @@
       <sz val="9.0"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="9.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="5">
@@ -1459,19 +1477,32 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="9">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1714,15 +1745,15 @@
     <col customWidth="1" min="3" max="3" width="18.0"/>
     <col customWidth="1" min="4" max="4" width="22.0"/>
     <col customWidth="1" min="5" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="7" width="8.0"/>
-    <col customWidth="1" min="8" max="8" width="6.0"/>
-    <col customWidth="1" min="9" max="9" width="8.0"/>
-    <col customWidth="1" min="10" max="10" width="18.0"/>
-    <col customWidth="1" min="11" max="11" width="14.0"/>
-    <col customWidth="1" min="12" max="12" width="10.0"/>
-    <col customWidth="1" min="13" max="13" width="12.0"/>
-    <col customWidth="1" min="14" max="15" width="40.0"/>
-    <col customWidth="1" min="16" max="26" width="8.71"/>
+    <col customWidth="1" min="6" max="9" width="8.0"/>
+    <col customWidth="1" min="10" max="10" width="6.0"/>
+    <col customWidth="1" min="11" max="11" width="8.0"/>
+    <col customWidth="1" min="12" max="12" width="18.0"/>
+    <col customWidth="1" min="13" max="13" width="14.0"/>
+    <col customWidth="1" min="14" max="14" width="10.0"/>
+    <col customWidth="1" min="15" max="15" width="12.0"/>
+    <col customWidth="1" min="16" max="17" width="40.0"/>
+    <col customWidth="1" min="18" max="28" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
@@ -1747,10 +1778,10 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
@@ -1771,709 +1802,1203 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="F2" s="2">
+      <c r="D2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="3">
         <v>3.0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>3.0</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="M2" s="3"/>
+      <c r="N2" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O2" s="3"/>
+      <c r="P2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="F3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="G3" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="H3" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="I3" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="Q3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="G4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L4" s="3"/>
+      <c r="M4" s="3"/>
+      <c r="N4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q4" s="8"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="F5" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="G5" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="H5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="I5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="K5" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="Q5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="G6" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="H6" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="I6" s="4">
+        <v>5.0</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="K6" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="L6" s="3"/>
+      <c r="M6" s="3"/>
+      <c r="N6" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O6" s="3">
+        <v>12.0</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="8"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="G7" s="6">
+        <v>0.0</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O7" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="P7" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q7" s="8"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="2">
+      <c r="E8" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="F8" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="G8" s="4">
         <v>1.0</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="b">
+      <c r="H8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="I8" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="K8" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="L8" s="3"/>
+      <c r="M8" s="3"/>
+      <c r="N8" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="3">
+      <c r="O8" s="3"/>
+      <c r="P8" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q8" s="8"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>63</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="F9" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="G9" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="H9" s="7">
         <v>1.0</v>
       </c>
-      <c r="G3" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="I3" s="3">
+      <c r="I9" s="7">
         <v>1.0</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="b">
+      <c r="J9" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="L9" s="6"/>
+      <c r="M9" s="6"/>
+      <c r="N9" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M3" s="3"/>
-      <c r="N3" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="F4" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="G4" s="2">
+      <c r="O9" s="6"/>
+      <c r="P9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="Q9" s="8"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="F10" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="G10" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="3">
         <v>1.0</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="L10" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="M10" s="3"/>
+      <c r="N10" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O10" s="3"/>
+      <c r="P10" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="Q10" s="8"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="G11" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K11" s="6">
         <v>1.0</v>
       </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="b">
+      <c r="L11" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="M11" s="6"/>
+      <c r="N11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="G5" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="3">
+      <c r="O11" s="6"/>
+      <c r="P11" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="Q11" s="8"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>20.0</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="K12" s="3">
         <v>1.0</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="L5" s="3" t="b">
+      <c r="L12" s="3"/>
+      <c r="M12" s="3"/>
+      <c r="N12" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="O12" s="3"/>
+      <c r="P12" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q12" s="8"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>89</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="6"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="M13" s="6"/>
+      <c r="N13" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M5" s="3"/>
-      <c r="N5" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="G6" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="I6" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="b">
+      <c r="O13" s="6"/>
+      <c r="P13" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q13" s="8"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+      <c r="G14" s="3"/>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3"/>
+      <c r="K14" s="3"/>
+      <c r="L14" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="M14" s="3"/>
+      <c r="N14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M6" s="2">
-        <v>12.0</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="G7" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="I7" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3" t="b">
+      <c r="O14" s="3"/>
+      <c r="P14" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q14" s="5" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="6"/>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="M15" s="6"/>
+      <c r="N15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M7" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="N7" s="3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="I8" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2" t="b">
+      <c r="O15" s="6"/>
+      <c r="P15" s="6" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q15" s="8"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
+      <c r="G16" s="3"/>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3"/>
+      <c r="L16" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="3"/>
+      <c r="N16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="I9" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3" t="b">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="Q16" s="8"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="6"/>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="6"/>
+      <c r="N17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M9" s="3"/>
-      <c r="N9" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F10" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="G10" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="I10" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2" t="b">
+      <c r="O17" s="6"/>
+      <c r="P17" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q17" s="8"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3"/>
+      <c r="F18" s="3"/>
+      <c r="G18" s="3"/>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3"/>
+      <c r="J18" s="3"/>
+      <c r="K18" s="3"/>
+      <c r="L18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="3"/>
+      <c r="N18" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F11" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="G11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3" t="b">
+      <c r="O18" s="3"/>
+      <c r="P18" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="Q18" s="8"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
+      <c r="G19" s="6"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="6"/>
+      <c r="N19" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M11" s="3"/>
-      <c r="N11" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F12" s="2">
-        <v>0.0</v>
-      </c>
-      <c r="G12" s="2">
-        <v>20.0</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I12" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2" t="b">
-        <v>1</v>
-      </c>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="G13" s="3"/>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3"/>
-      <c r="J13" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="3" t="b">
+      <c r="O19" s="6"/>
+      <c r="P19" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q19" s="8"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="3"/>
+      <c r="N20" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M13" s="3"/>
-      <c r="N13" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="O20" s="3"/>
+      <c r="P20" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q20" s="8"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2" t="b">
+      <c r="D21" s="6"/>
+      <c r="E21" s="6"/>
+      <c r="F21" s="6"/>
+      <c r="G21" s="6"/>
+      <c r="H21" s="6"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="M21" s="6"/>
+      <c r="N21" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="G15" s="3"/>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-      <c r="J15" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="b">
+      <c r="O21" s="6"/>
+      <c r="P21" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q21" s="8"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6"/>
+      <c r="B22" s="6"/>
+      <c r="C22" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="6"/>
+      <c r="E22" s="6"/>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="6"/>
+      <c r="M22" s="6"/>
+      <c r="N22" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M15" s="3"/>
-      <c r="N15" s="3" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2" t="b">
+      <c r="O22" s="6"/>
+      <c r="P22" s="6"/>
+      <c r="Q22" s="8"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3"/>
+      <c r="B23" s="3"/>
+      <c r="C23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D23" s="3"/>
+      <c r="E23" s="3"/>
+      <c r="F23" s="3"/>
+      <c r="G23" s="3"/>
+      <c r="H23" s="3"/>
+      <c r="I23" s="3"/>
+      <c r="J23" s="3"/>
+      <c r="K23" s="3"/>
+      <c r="L23" s="3"/>
+      <c r="M23" s="3"/>
+      <c r="N23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-      <c r="J17" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="K17" s="3"/>
-      <c r="L17" s="3" t="b">
+      <c r="O23" s="3"/>
+      <c r="P23" s="3"/>
+      <c r="Q23" s="8"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6"/>
+      <c r="B24" s="6"/>
+      <c r="C24" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D24" s="6"/>
+      <c r="E24" s="6"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="6"/>
+      <c r="H24" s="6"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="6"/>
+      <c r="M24" s="6"/>
+      <c r="N24" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M17" s="3"/>
-      <c r="N17" s="3" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2" t="b">
+      <c r="O24" s="6"/>
+      <c r="P24" s="6"/>
+      <c r="Q24" s="8"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3"/>
+      <c r="B25" s="3"/>
+      <c r="C25" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="3"/>
+      <c r="E25" s="3"/>
+      <c r="F25" s="3"/>
+      <c r="G25" s="3"/>
+      <c r="H25" s="3"/>
+      <c r="I25" s="3"/>
+      <c r="J25" s="3"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="3"/>
+      <c r="N25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="K19" s="3"/>
-      <c r="L19" s="3" t="b">
+      <c r="O25" s="3"/>
+      <c r="P25" s="3"/>
+      <c r="Q25" s="8"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6"/>
+      <c r="B26" s="6"/>
+      <c r="C26" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D26" s="6"/>
+      <c r="E26" s="6"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="6"/>
+      <c r="H26" s="6"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="6"/>
+      <c r="M26" s="6"/>
+      <c r="N26" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M19" s="3"/>
-      <c r="N19" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2" t="b">
+      <c r="O26" s="6"/>
+      <c r="P26" s="6"/>
+      <c r="Q26" s="8"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
+      <c r="C27" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3"/>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3"/>
+      <c r="H27" s="3"/>
+      <c r="I27" s="3"/>
+      <c r="J27" s="3"/>
+      <c r="K27" s="3"/>
+      <c r="L27" s="3"/>
+      <c r="M27" s="3"/>
+      <c r="N27" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="G21" s="3"/>
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-      <c r="J21" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K21" s="3"/>
-      <c r="L21" s="3" t="b">
+      <c r="O27" s="3"/>
+      <c r="P27" s="3"/>
+      <c r="Q27" s="8"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D28" s="6"/>
+      <c r="E28" s="6"/>
+      <c r="F28" s="6"/>
+      <c r="G28" s="6"/>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="6"/>
+      <c r="M28" s="6"/>
+      <c r="N28" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="M21" s="3"/>
-      <c r="N21" s="3" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
+      <c r="O28" s="6"/>
+      <c r="P28" s="6"/>
+      <c r="Q28" s="8"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="3"/>
+      <c r="B29" s="3"/>
+      <c r="C29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D29" s="3"/>
+      <c r="E29" s="3"/>
+      <c r="F29" s="3"/>
+      <c r="G29" s="3"/>
+      <c r="H29" s="3"/>
+      <c r="I29" s="3"/>
+      <c r="J29" s="3"/>
+      <c r="K29" s="3"/>
+      <c r="L29" s="3"/>
+      <c r="M29" s="3"/>
+      <c r="N29" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3"/>
+      <c r="P29" s="3"/>
+      <c r="Q29" s="8"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D30" s="6"/>
+      <c r="E30" s="6"/>
+      <c r="F30" s="6"/>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="6"/>
+      <c r="M30" s="6"/>
+      <c r="N30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O30" s="6"/>
+      <c r="P30" s="6"/>
+      <c r="Q30" s="8"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="6"/>
+      <c r="M31" s="6"/>
+      <c r="N31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O31" s="6"/>
+      <c r="P31" s="6"/>
+      <c r="Q31" s="8"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3"/>
+      <c r="F32" s="3"/>
+      <c r="G32" s="3"/>
+      <c r="H32" s="3"/>
+      <c r="I32" s="3"/>
+      <c r="J32" s="3"/>
+      <c r="K32" s="3"/>
+      <c r="L32" s="3"/>
+      <c r="M32" s="3"/>
+      <c r="N32" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3"/>
+      <c r="P32" s="3"/>
+      <c r="Q32" s="8"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D33" s="6"/>
+      <c r="E33" s="6"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="6"/>
+      <c r="M33" s="6"/>
+      <c r="N33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O33" s="6"/>
+      <c r="P33" s="6"/>
+      <c r="Q33" s="8"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="3"/>
+      <c r="B34" s="3"/>
+      <c r="C34" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3"/>
+      <c r="F34" s="3"/>
+      <c r="G34" s="3"/>
+      <c r="H34" s="3"/>
+      <c r="I34" s="3"/>
+      <c r="J34" s="3"/>
+      <c r="K34" s="3"/>
+      <c r="L34" s="3"/>
+      <c r="M34" s="3"/>
+      <c r="N34" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O34" s="3"/>
+      <c r="P34" s="3"/>
+      <c r="Q34" s="8"/>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="6"/>
+      <c r="B35" s="6"/>
+      <c r="C35" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D35" s="6"/>
+      <c r="E35" s="6"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6"/>
+      <c r="H35" s="6"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="6"/>
+      <c r="M35" s="6"/>
+      <c r="N35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O35" s="6"/>
+      <c r="P35" s="6"/>
+      <c r="Q35" s="8"/>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3"/>
+      <c r="B36" s="3"/>
+      <c r="C36" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D36" s="3"/>
+      <c r="E36" s="3"/>
+      <c r="F36" s="3"/>
+      <c r="G36" s="3"/>
+      <c r="H36" s="3"/>
+      <c r="I36" s="3"/>
+      <c r="J36" s="3"/>
+      <c r="K36" s="3"/>
+      <c r="L36" s="3"/>
+      <c r="M36" s="3"/>
+      <c r="N36" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O36" s="3"/>
+      <c r="P36" s="3"/>
+      <c r="Q36" s="8"/>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="6"/>
+      <c r="B37" s="6"/>
+      <c r="C37" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D37" s="6"/>
+      <c r="E37" s="6"/>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6"/>
+      <c r="H37" s="6"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="6"/>
+      <c r="M37" s="6"/>
+      <c r="N37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O37" s="6"/>
+      <c r="P37" s="6"/>
+      <c r="Q37" s="8"/>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="3"/>
+      <c r="B38" s="3"/>
+      <c r="C38" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D38" s="3"/>
+      <c r="E38" s="3"/>
+      <c r="F38" s="3"/>
+      <c r="G38" s="3"/>
+      <c r="H38" s="3"/>
+      <c r="I38" s="3"/>
+      <c r="J38" s="3"/>
+      <c r="K38" s="3"/>
+      <c r="L38" s="3"/>
+      <c r="M38" s="3"/>
+      <c r="N38" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O38" s="3"/>
+      <c r="P38" s="3"/>
+      <c r="Q38" s="8"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="6"/>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+      <c r="H39" s="6"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="6"/>
+      <c r="M39" s="6"/>
+      <c r="N39" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="O39" s="6"/>
+      <c r="P39" s="6"/>
+      <c r="Q39" s="8"/>
+    </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
@@ -3468,693 +3993,693 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E2" s="2" t="b">
+      <c r="A2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="2" t="b">
+      <c r="F2" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>5.0</v>
       </c>
-      <c r="H2" s="2" t="b">
+      <c r="H2" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="K2" s="2" t="s">
+      <c r="I2" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="E3" s="3" t="b">
+      <c r="D3" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E3" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="3" t="b">
+      <c r="F3" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H3" s="3" t="b">
+      <c r="G3" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H3" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>147</v>
+      <c r="I3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="A4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="E4" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E4" s="2" t="b">
+      <c r="H4" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="2" t="b">
+      <c r="I4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="E6" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H4" s="2" t="b">
+      <c r="F6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="E5" s="3" t="b">
+      <c r="G6" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="3" t="b">
+      <c r="I6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="E7" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H5" s="3" t="b">
+      <c r="F7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H7" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E6" s="2" t="b">
+      <c r="I7" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H8" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="2" t="b">
+      <c r="G9" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H9" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H6" s="2" t="b">
+      <c r="I9" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="E7" s="3" t="b">
+      <c r="F10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H7" s="3" t="b">
+      <c r="G10" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H10" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="E8" s="2" t="b">
+      <c r="I10" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>139</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="2" t="b">
+      <c r="F11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H8" s="2" t="b">
+      <c r="G11" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="H11" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="E9" s="3" t="b">
+      <c r="I11" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H9" s="3" t="b">
+      <c r="F12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10" s="2" t="b">
+      <c r="G12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="H12" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="2" t="b">
+      <c r="I12" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="E13" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H10" s="2" t="b">
+      <c r="F13" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="K10" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="L10" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="M10" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E11" s="3" t="b">
+      <c r="G13" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H13" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="3" t="b">
+      <c r="I13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="E14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="H11" s="3" t="b">
+      <c r="F14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E12" s="2" t="b">
+      <c r="G14" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="2" t="b">
+      <c r="I14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="E15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H12" s="2" t="b">
+      <c r="F15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="K12" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="L12" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="M12" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="E13" s="3" t="b">
+      <c r="G15" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="H15" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="3" t="b">
+      <c r="I15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="E16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="G13" s="3">
+      <c r="F16" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G16" s="3">
         <v>1.0</v>
       </c>
-      <c r="H13" s="3" t="b">
+      <c r="H16" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
+      <c r="I16" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C17" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E14" s="2" t="b">
+      <c r="D17" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="E17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="2" t="b">
+      <c r="F17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="G14" s="2">
+      <c r="G17" s="6">
         <v>1.0</v>
       </c>
-      <c r="H14" s="2" t="b">
+      <c r="H17" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G15" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="H15" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="2">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="K16" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="L16" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>236</v>
+      <c r="I17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="K17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="L17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="M17" s="6" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5168,199 +5693,199 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="B2" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="D2" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="E2" s="3" t="s">
         <v>251</v>
       </c>
+      <c r="F2" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="E3" s="3" t="s">
+      <c r="A3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="H3" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>257</v>
+      <c r="I3" s="6" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="A4" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I4" s="2" t="s">
+      <c r="B4" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D4" s="3" t="s">
         <v>263</v>
       </c>
+      <c r="E4" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>267</v>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>267</v>
+      <c r="A5" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="A6" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>249</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="H7" s="6" t="s">
         <v>270</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>272</v>
+      <c r="I7" s="6" t="s">
+        <v>276</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6371,578 +6896,578 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1.0</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="3">
         <v>18.0</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="3">
         <v>1.0</v>
       </c>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2">
+      <c r="D2" s="3"/>
+      <c r="E2" s="3">
         <v>1.0</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="J2" s="2"/>
+      <c r="F2" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H2" s="3"/>
+      <c r="I2" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="J2" s="3"/>
     </row>
     <row r="3">
-      <c r="A3" s="3">
+      <c r="A3" s="6">
         <v>2.0</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B3" s="6">
         <v>18.0</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C3" s="6">
         <v>1.0</v>
       </c>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3">
+      <c r="D3" s="6"/>
+      <c r="E3" s="6">
         <v>1.0</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="J3" s="3"/>
+      <c r="F3" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>287</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6" t="s">
+        <v>289</v>
+      </c>
+      <c r="J3" s="6"/>
     </row>
     <row r="4">
-      <c r="A4" s="2">
+      <c r="A4" s="3">
         <v>3.0</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4" s="3">
         <v>18.0</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="3">
         <v>1.0</v>
       </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2">
+      <c r="D4" s="3"/>
+      <c r="E4" s="3">
         <v>1.0</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2" t="s">
+      <c r="F4" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="G4" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" s="3"/>
+      <c r="I4" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J4" s="3"/>
     </row>
     <row r="5">
-      <c r="A5" s="3">
+      <c r="A5" s="6">
         <v>4.0</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5" s="6">
         <v>23.0</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="6">
         <v>1.0</v>
       </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3">
+      <c r="D5" s="6"/>
+      <c r="E5" s="6">
         <v>1.0</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="H5" s="3"/>
-      <c r="I5" s="3" t="s">
+      <c r="F5" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="G5" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="J5" s="3"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6" t="s">
+        <v>291</v>
+      </c>
+      <c r="J5" s="6"/>
     </row>
     <row r="6">
-      <c r="A6" s="2">
+      <c r="A6" s="3">
         <v>5.0</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6" s="3">
         <v>31.0</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="3">
         <v>1.0</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E6" s="2">
+      <c r="D6" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="3">
         <v>1.0</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="H6" s="2">
+      <c r="F6" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="H6" s="3">
         <v>1.0</v>
       </c>
-      <c r="I6" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>291</v>
+      <c r="I6" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3">
+      <c r="A7" s="6">
         <v>6.0</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7" s="6">
         <v>180.0</v>
       </c>
-      <c r="C7" s="3">
+      <c r="C7" s="6">
         <v>2.0</v>
       </c>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3">
+      <c r="D7" s="6"/>
+      <c r="E7" s="6">
         <v>2.0</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="F7" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J7" s="6"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="3">
+        <v>220.0</v>
+      </c>
+      <c r="C8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H8" s="3"/>
+      <c r="I8" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J8" s="3"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="6">
+        <v>270.0</v>
+      </c>
+      <c r="C9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="D9" s="6"/>
+      <c r="E9" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J9" s="6"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="3">
+        <v>340.0</v>
+      </c>
+      <c r="C10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="3"/>
+      <c r="E10" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="H10" s="3"/>
+      <c r="I10" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J10" s="3"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="6">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="6">
+        <v>600.0</v>
+      </c>
+      <c r="C11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H7" s="3"/>
-      <c r="I7" s="3" t="s">
+      <c r="E11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>297</v>
+      </c>
+      <c r="H11" s="6">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="2">
-        <v>220.0</v>
-      </c>
-      <c r="C8" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F8" s="2" t="s">
+      <c r="J11" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="3">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="C12" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D12" s="3"/>
+      <c r="E12" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H12" s="3"/>
+      <c r="I12" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J12" s="3"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="6">
+        <v>450.0</v>
+      </c>
+      <c r="C13" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J13" s="6"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="3">
+        <v>450.0</v>
+      </c>
+      <c r="C14" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H14" s="3"/>
+      <c r="I14" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J14" s="3"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="6">
+        <v>585.0</v>
+      </c>
+      <c r="C15" s="6">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="6"/>
+      <c r="E15" s="6">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J15" s="6"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="3">
+        <v>765.0</v>
+      </c>
+      <c r="C16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="E16" s="3">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="H16" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="J8" s="2"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3">
+      <c r="J16" s="3" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="6">
+        <v>4050.0</v>
+      </c>
+      <c r="C17" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G17" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H17" s="6"/>
+      <c r="I17" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J17" s="6"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="3">
+        <v>4050.0</v>
+      </c>
+      <c r="C18" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H18" s="3"/>
+      <c r="I18" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J18" s="3"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="6">
+        <v>4050.0</v>
+      </c>
+      <c r="C19" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="J19" s="6"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="3">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="3">
+        <v>5265.0</v>
+      </c>
+      <c r="C20" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3">
+        <v>15.0</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="J20" s="3"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="6">
+        <v>6885.0</v>
+      </c>
+      <c r="C21" s="6">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>292</v>
+      </c>
+      <c r="E21" s="6">
+        <v>15.0</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="H21" s="6">
         <v>8.0</v>
       </c>
-      <c r="B9" s="3">
-        <v>270.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H9" s="3"/>
-      <c r="I9" s="3" t="s">
+      <c r="I21" s="6" t="s">
         <v>294</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="2">
-        <v>340.0</v>
-      </c>
-      <c r="C10" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J10" s="2"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3">
-        <v>600.0</v>
-      </c>
-      <c r="C11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="H11" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="2">
-        <v>450.0</v>
-      </c>
-      <c r="C12" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J12" s="2"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3">
-        <v>450.0</v>
-      </c>
-      <c r="C13" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H13" s="3"/>
-      <c r="I13" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J13" s="3"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="2">
-        <v>450.0</v>
-      </c>
-      <c r="C14" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J14" s="2"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3">
-        <v>585.0</v>
-      </c>
-      <c r="C15" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J15" s="3"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="2">
-        <v>765.0</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E16" s="2">
-        <v>5.0</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="H16" s="2">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3">
-        <v>4050.0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="H17" s="3"/>
-      <c r="I17" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J17" s="3"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="2">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="2">
-        <v>4050.0</v>
-      </c>
-      <c r="C18" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J18" s="2"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3">
-        <v>4050.0</v>
-      </c>
-      <c r="C19" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="J19" s="3"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="2">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="2">
-        <v>5265.0</v>
-      </c>
-      <c r="C20" s="2">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2">
-        <v>15.0</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="J20" s="2"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3">
-        <v>6885.0</v>
-      </c>
-      <c r="C21" s="3">
-        <v>4.0</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E21" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="H21" s="3">
-        <v>8.0</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>291</v>
+      <c r="J21" s="6" t="s">
+        <v>295</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -7948,121 +8473,121 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>315</v>
       </c>
+      <c r="B2" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>319</v>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="6" t="s">
+        <v>320</v>
+      </c>
+      <c r="B3" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>319</v>
+      <c r="C3" s="6" t="s">
+        <v>321</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>323</v>
+      <c r="A4" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>327</v>
+      <c r="A5" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>331</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>331</v>
+      <c r="A6" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>335</v>
+      <c r="A7" s="6" t="s">
+        <v>336</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>337</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -9071,856 +9596,856 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>342</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>343</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>350</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>351</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D5" s="6"/>
+      <c r="E5" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>357</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>358</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>349</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="D13" s="6"/>
+      <c r="E13" s="6" t="s">
+        <v>374</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>378</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>372</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>366</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>383</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>338</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C10" s="2" t="s">
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="D18" s="3"/>
+      <c r="E18" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>387</v>
+      </c>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="D21" s="6"/>
+      <c r="E21" s="6" t="s">
+        <v>393</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>397</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>398</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>399</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="D24" s="3"/>
+      <c r="E24" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="D27" s="6" t="s">
+        <v>408</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>409</v>
+      </c>
+      <c r="F27" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="6" t="s">
+        <v>415</v>
+      </c>
+      <c r="B29" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E11" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2" t="s">
-        <v>381</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>391</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3" t="s">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6" t="s">
+        <v>416</v>
+      </c>
+      <c r="F29" s="6" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B31" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="6" t="s">
+        <v>363</v>
+      </c>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6" t="s">
+        <v>419</v>
+      </c>
+      <c r="F31" s="6" t="s">
         <v>400</v>
       </c>
-      <c r="F25" s="3" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>403</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C29" s="3" t="s">
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="D32" s="3"/>
+      <c r="E32" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>421</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>417</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>422</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D34" s="3"/>
+      <c r="E34" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>428</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>429</v>
+      </c>
+      <c r="F35" s="6" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>435</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>436</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>437</v>
+      </c>
+      <c r="F37" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>443</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>445</v>
+      </c>
+      <c r="F39" s="6" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="6" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>450</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>451</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>452</v>
+      </c>
+      <c r="F41" s="6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="D31" s="3"/>
-      <c r="E31" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="F34" s="2" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="2" t="s">
+      <c r="D42" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>456</v>
+      </c>
+      <c r="D43" s="6" t="s">
+        <v>457</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>458</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E38" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="F38" s="2" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>443</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="F42" s="2" t="s">
+      <c r="D44" s="3" t="s">
         <v>451</v>
       </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>457</v>
+      <c r="E44" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>461</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -15,14 +15,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="sMePMrDKIwiZ0AJ8bznhiMDdjuTpWZGWDhJCC3Kk++8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="PwGAx27xyYJwXwOWAsKRA8sJa/6C9ASi3yl2gAIyaOs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="760" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="462">
   <si>
     <t>id</t>
   </si>
@@ -66,6 +66,9 @@
     <t>guardian</t>
   </si>
   <si>
+    <t>legend</t>
+  </si>
+  <si>
     <t>triggerCount</t>
   </si>
   <si>
@@ -888,6 +891,9 @@
     <t>3/3</t>
   </si>
   <si>
+    <t>なし（スキップ）</t>
+  </si>
+  <si>
     <t>ヘイト</t>
   </si>
   <si>
@@ -897,9 +903,6 @@
     <t>召喚</t>
   </si>
   <si>
-    <t>鼓舞</t>
-  </si>
-  <si>
     <t>✓</t>
   </si>
   <si>
@@ -916,9 +919,6 @@
   </si>
   <si>
     <t>6/6</t>
-  </si>
-  <si>
-    <t>なし（スキップ）</t>
   </si>
   <si>
     <t>9/6×4</t>
@@ -1750,10 +1750,10 @@
     <col customWidth="1" min="11" max="11" width="8.0"/>
     <col customWidth="1" min="12" max="12" width="18.0"/>
     <col customWidth="1" min="13" max="13" width="14.0"/>
-    <col customWidth="1" min="14" max="14" width="10.0"/>
-    <col customWidth="1" min="15" max="15" width="12.0"/>
-    <col customWidth="1" min="16" max="17" width="40.0"/>
-    <col customWidth="1" min="18" max="28" width="8.71"/>
+    <col customWidth="1" min="14" max="15" width="10.0"/>
+    <col customWidth="1" min="16" max="16" width="12.0"/>
+    <col customWidth="1" min="17" max="18" width="40.0"/>
+    <col customWidth="1" min="19" max="29" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
@@ -1799,7 +1799,7 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="2" t="s">
         <v>14</v>
       </c>
       <c r="P1" s="1" t="s">
@@ -1808,22 +1808,25 @@
       <c r="Q1" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F2" s="3">
         <v>3.0</v>
@@ -1838,56 +1841,57 @@
         <v>2.0</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="K2" s="3">
         <v>1.0</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M2" s="3"/>
       <c r="N2" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O2" s="3"/>
-      <c r="P2" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="Q2" s="5" t="s">
+      <c r="P2" s="3"/>
+      <c r="Q2" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="R2" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="6">
         <v>1.0</v>
       </c>
-      <c r="G3" s="6">
-        <v>2.0</v>
+      <c r="G3" s="7">
+        <v>3.0</v>
       </c>
       <c r="H3" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="I3" s="7">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="6">
         <v>1.0</v>
@@ -1898,28 +1902,29 @@
         <v>0</v>
       </c>
       <c r="O3" s="6"/>
-      <c r="P3" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="Q3" s="5" t="s">
-        <v>25</v>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="R3" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="3">
         <v>4.0</v>
@@ -1930,7 +1935,7 @@
       <c r="H4" s="3"/>
       <c r="I4" s="3"/>
       <c r="J4" s="3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K4" s="3">
         <v>1.0</v>
@@ -1941,75 +1946,77 @@
         <v>0</v>
       </c>
       <c r="O4" s="3"/>
-      <c r="P4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q4" s="8"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="R4" s="8"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="F5" s="6">
-        <v>4.0</v>
-      </c>
-      <c r="G5" s="6">
-        <v>5.0</v>
+        <v>42</v>
+      </c>
+      <c r="F5" s="7">
+        <v>2.0</v>
+      </c>
+      <c r="G5" s="7">
+        <v>6.0</v>
       </c>
       <c r="H5" s="7">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="I5" s="7">
         <v>2.0</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K5" s="6">
         <v>1.0</v>
       </c>
       <c r="L5" s="6"/>
       <c r="M5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O5" s="6"/>
-      <c r="P5" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>25</v>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="R5" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F6" s="3">
         <v>15.0</v>
@@ -2024,7 +2031,7 @@
         <v>5.0</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="K6" s="3">
         <v>1.0</v>
@@ -2034,29 +2041,30 @@
       <c r="N6" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O6" s="3">
+      <c r="O6" s="3"/>
+      <c r="P6" s="3">
         <v>12.0</v>
       </c>
-      <c r="P6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="8"/>
+      <c r="Q6" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="R6" s="8"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F7" s="6">
         <v>0.0</v>
@@ -2067,41 +2075,42 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K7" s="6">
         <v>1.0</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M7" s="6"/>
       <c r="N7" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="6"/>
+      <c r="P7" s="6">
         <v>10.0</v>
       </c>
-      <c r="P7" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q7" s="8"/>
+      <c r="Q7" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="R7" s="8"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F8" s="4">
         <v>2.0</v>
@@ -2116,7 +2125,7 @@
         <v>1.0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="K8" s="4">
         <v>3.0</v>
@@ -2127,26 +2136,27 @@
         <v>0</v>
       </c>
       <c r="O8" s="3"/>
-      <c r="P8" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q8" s="8"/>
+      <c r="P8" s="3"/>
+      <c r="Q8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R8" s="8"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F9" s="7">
         <v>2.0</v>
@@ -2161,7 +2171,7 @@
         <v>1.0</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="K9" s="6">
         <v>1.0</v>
@@ -2172,26 +2182,27 @@
         <v>0</v>
       </c>
       <c r="O9" s="6"/>
-      <c r="P9" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q9" s="8"/>
+      <c r="P9" s="6"/>
+      <c r="Q9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="R9" s="8"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F10" s="3">
         <v>15.0</v>
@@ -2199,42 +2210,47 @@
       <c r="G10" s="3">
         <v>15.0</v>
       </c>
-      <c r="H10" s="3"/>
-      <c r="I10" s="3"/>
+      <c r="H10" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="I10" s="4">
+        <v>7.0</v>
+      </c>
       <c r="J10" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K10" s="3">
         <v>1.0</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O10" s="3"/>
-      <c r="P10" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="Q10" s="8"/>
+      <c r="P10" s="3"/>
+      <c r="Q10" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="R10" s="8"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F11" s="6">
         <v>8.0</v>
@@ -2245,39 +2261,40 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
       <c r="J11" s="6" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K11" s="6">
         <v>1.0</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M11" s="6"/>
       <c r="N11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O11" s="6"/>
-      <c r="P11" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="Q11" s="8"/>
+      <c r="P11" s="6"/>
+      <c r="Q11" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="R11" s="8"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F12" s="3">
         <v>0.0</v>
@@ -2288,7 +2305,7 @@
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
       <c r="J12" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K12" s="3">
         <v>1.0</v>
@@ -2299,20 +2316,21 @@
         <v>1</v>
       </c>
       <c r="O12" s="3"/>
-      <c r="P12" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="Q12" s="8"/>
+      <c r="P12" s="3"/>
+      <c r="Q12" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="R12" s="8"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6"/>
@@ -2323,27 +2341,28 @@
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="M13" s="6"/>
       <c r="N13" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O13" s="6"/>
-      <c r="P13" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q13" s="8"/>
+      <c r="P13" s="6"/>
+      <c r="Q13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="R13" s="8"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
@@ -2354,29 +2373,32 @@
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O14" s="3"/>
-      <c r="P14" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q14" s="5" t="s">
+      <c r="O14" s="3" t="b">
+        <v>1</v>
+      </c>
+      <c r="P14" s="3"/>
+      <c r="Q14" s="4" t="s">
         <v>97</v>
+      </c>
+      <c r="R14" s="5" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D15" s="6"/>
       <c r="E15" s="6"/>
@@ -2387,27 +2409,28 @@
       <c r="J15" s="6"/>
       <c r="K15" s="6"/>
       <c r="L15" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6"/>
       <c r="N15" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O15" s="6"/>
-      <c r="P15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="Q15" s="8"/>
+      <c r="P15" s="6"/>
+      <c r="Q15" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="R15" s="8"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
@@ -2418,27 +2441,28 @@
       <c r="J16" s="3"/>
       <c r="K16" s="3"/>
       <c r="L16" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O16" s="3"/>
-      <c r="P16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="8"/>
+      <c r="P16" s="3"/>
+      <c r="Q16" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="R16" s="8"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
@@ -2449,27 +2473,28 @@
       <c r="J17" s="6"/>
       <c r="K17" s="6"/>
       <c r="L17" s="6" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M17" s="6"/>
       <c r="N17" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O17" s="6"/>
-      <c r="P17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="Q17" s="8"/>
+      <c r="P17" s="6"/>
+      <c r="Q17" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="R17" s="8"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
@@ -2480,27 +2505,28 @@
       <c r="J18" s="3"/>
       <c r="K18" s="3"/>
       <c r="L18" s="3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O18" s="3"/>
-      <c r="P18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q18" s="8"/>
+      <c r="P18" s="3"/>
+      <c r="Q18" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="R18" s="8"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
@@ -2511,27 +2537,28 @@
       <c r="J19" s="6"/>
       <c r="K19" s="6"/>
       <c r="L19" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="M19" s="6"/>
       <c r="N19" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O19" s="6"/>
-      <c r="P19" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q19" s="8"/>
+      <c r="P19" s="6"/>
+      <c r="Q19" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="R19" s="8"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2542,27 +2569,28 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O20" s="3"/>
-      <c r="P20" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q20" s="8"/>
+      <c r="P20" s="3"/>
+      <c r="Q20" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="R20" s="8"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
@@ -2573,23 +2601,24 @@
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
       <c r="L21" s="6" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6" t="b">
         <v>0</v>
       </c>
       <c r="O21" s="6"/>
-      <c r="P21" s="6" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q21" s="8"/>
+      <c r="P21" s="6"/>
+      <c r="Q21" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="R21" s="8"/>
     </row>
     <row r="22">
       <c r="A22" s="6"/>
       <c r="B22" s="6"/>
       <c r="C22" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
@@ -2606,13 +2635,14 @@
       </c>
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
-      <c r="Q22" s="8"/>
+      <c r="Q22" s="6"/>
+      <c r="R22" s="8"/>
     </row>
     <row r="23">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -2629,13 +2659,14 @@
       </c>
       <c r="O23" s="3"/>
       <c r="P23" s="3"/>
-      <c r="Q23" s="8"/>
+      <c r="Q23" s="3"/>
+      <c r="R23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="6"/>
       <c r="B24" s="6"/>
       <c r="C24" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
@@ -2652,13 +2683,14 @@
       </c>
       <c r="O24" s="6"/>
       <c r="P24" s="6"/>
-      <c r="Q24" s="8"/>
+      <c r="Q24" s="6"/>
+      <c r="R24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
@@ -2675,13 +2707,14 @@
       </c>
       <c r="O25" s="3"/>
       <c r="P25" s="3"/>
-      <c r="Q25" s="8"/>
+      <c r="Q25" s="3"/>
+      <c r="R25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="6"/>
       <c r="B26" s="6"/>
       <c r="C26" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
@@ -2698,13 +2731,14 @@
       </c>
       <c r="O26" s="6"/>
       <c r="P26" s="6"/>
-      <c r="Q26" s="8"/>
+      <c r="Q26" s="6"/>
+      <c r="R26" s="8"/>
     </row>
     <row r="27">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
@@ -2721,13 +2755,14 @@
       </c>
       <c r="O27" s="3"/>
       <c r="P27" s="3"/>
-      <c r="Q27" s="8"/>
+      <c r="Q27" s="3"/>
+      <c r="R27" s="8"/>
     </row>
     <row r="28">
       <c r="A28" s="6"/>
       <c r="B28" s="6"/>
       <c r="C28" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
@@ -2744,13 +2779,14 @@
       </c>
       <c r="O28" s="6"/>
       <c r="P28" s="6"/>
-      <c r="Q28" s="8"/>
+      <c r="Q28" s="6"/>
+      <c r="R28" s="8"/>
     </row>
     <row r="29">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
@@ -2767,13 +2803,14 @@
       </c>
       <c r="O29" s="3"/>
       <c r="P29" s="3"/>
-      <c r="Q29" s="8"/>
+      <c r="Q29" s="3"/>
+      <c r="R29" s="8"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
       <c r="B30" s="6"/>
       <c r="C30" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D30" s="6"/>
       <c r="E30" s="6"/>
@@ -2790,13 +2827,14 @@
       </c>
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
-      <c r="Q30" s="8"/>
+      <c r="Q30" s="6"/>
+      <c r="R30" s="8"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6"/>
       <c r="B31" s="6"/>
       <c r="C31" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6"/>
@@ -2813,13 +2851,14 @@
       </c>
       <c r="O31" s="6"/>
       <c r="P31" s="6"/>
-      <c r="Q31" s="8"/>
+      <c r="Q31" s="6"/>
+      <c r="R31" s="8"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2836,13 +2875,14 @@
       </c>
       <c r="O32" s="3"/>
       <c r="P32" s="3"/>
-      <c r="Q32" s="8"/>
+      <c r="Q32" s="3"/>
+      <c r="R32" s="8"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6"/>
       <c r="B33" s="6"/>
       <c r="C33" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D33" s="6"/>
       <c r="E33" s="6"/>
@@ -2859,13 +2899,14 @@
       </c>
       <c r="O33" s="6"/>
       <c r="P33" s="6"/>
-      <c r="Q33" s="8"/>
+      <c r="Q33" s="6"/>
+      <c r="R33" s="8"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -2882,13 +2923,14 @@
       </c>
       <c r="O34" s="3"/>
       <c r="P34" s="3"/>
-      <c r="Q34" s="8"/>
+      <c r="Q34" s="3"/>
+      <c r="R34" s="8"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6"/>
       <c r="B35" s="6"/>
       <c r="C35" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D35" s="6"/>
       <c r="E35" s="6"/>
@@ -2905,13 +2947,14 @@
       </c>
       <c r="O35" s="6"/>
       <c r="P35" s="6"/>
-      <c r="Q35" s="8"/>
+      <c r="Q35" s="6"/>
+      <c r="R35" s="8"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2928,13 +2971,14 @@
       </c>
       <c r="O36" s="3"/>
       <c r="P36" s="3"/>
-      <c r="Q36" s="8"/>
+      <c r="Q36" s="3"/>
+      <c r="R36" s="8"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6"/>
       <c r="B37" s="6"/>
       <c r="C37" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
@@ -2951,13 +2995,14 @@
       </c>
       <c r="O37" s="6"/>
       <c r="P37" s="6"/>
-      <c r="Q37" s="8"/>
+      <c r="Q37" s="6"/>
+      <c r="R37" s="8"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
@@ -2974,13 +3019,14 @@
       </c>
       <c r="O38" s="3"/>
       <c r="P38" s="3"/>
-      <c r="Q38" s="8"/>
+      <c r="Q38" s="3"/>
+      <c r="R38" s="8"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6"/>
       <c r="B39" s="6"/>
       <c r="C39" s="6" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
@@ -2997,7 +3043,8 @@
       </c>
       <c r="O39" s="6"/>
       <c r="P39" s="6"/>
-      <c r="Q39" s="8"/>
+      <c r="Q39" s="6"/>
+      <c r="R39" s="8"/>
     </row>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
@@ -3993,51 +4040,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>1</v>
@@ -4052,33 +4099,33 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E3" s="6" t="b">
         <v>0</v>
@@ -4087,39 +4134,39 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H3" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -4128,39 +4175,39 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E5" s="6" t="b">
         <v>0</v>
@@ -4169,39 +4216,39 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>1</v>
@@ -4210,39 +4257,39 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>0</v>
@@ -4251,39 +4298,39 @@
         <v>1</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -4292,39 +4339,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="E9" s="6" t="b">
         <v>0</v>
@@ -4333,39 +4380,39 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -4374,39 +4421,39 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E11" s="6" t="b">
         <v>0</v>
@@ -4415,39 +4462,39 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -4456,39 +4503,39 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="E13" s="6" t="b">
         <v>0</v>
@@ -4503,33 +4550,33 @@
         <v>0</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E14" s="3" t="b">
         <v>0</v>
@@ -4544,33 +4591,33 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="E15" s="6" t="b">
         <v>0</v>
@@ -4585,33 +4632,33 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="E16" s="3" t="b">
         <v>0</v>
@@ -4626,33 +4673,33 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>0</v>
@@ -4667,19 +4714,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5693,199 +5740,199 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H3" s="6" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6896,34 +6943,34 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
     </row>
     <row r="2">
@@ -6941,14 +6988,14 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H2" s="3"/>
-      <c r="I2" s="3" t="s">
-        <v>288</v>
+      <c r="I2" s="6" t="s">
+        <v>289</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -6967,14 +7014,14 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J3" s="6"/>
     </row>
@@ -6993,14 +7040,14 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -7019,14 +7066,14 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -7041,25 +7088,25 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E6" s="3">
         <v>1.0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H6" s="3">
         <v>1.0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="7">
@@ -7077,14 +7124,14 @@
         <v>2.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -7106,11 +7153,11 @@
         <v>299</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -7132,11 +7179,11 @@
         <v>300</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -7158,11 +7205,11 @@
         <v>301</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -7177,7 +7224,7 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E11" s="6">
         <v>2.0</v>
@@ -7186,16 +7233,16 @@
         <v>302</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H11" s="6">
         <v>2.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="12">
@@ -7216,11 +7263,11 @@
         <v>303</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J12" s="3"/>
     </row>
@@ -7242,11 +7289,11 @@
         <v>303</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -7268,11 +7315,11 @@
         <v>303</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -7294,11 +7341,11 @@
         <v>304</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -7313,7 +7360,7 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E16" s="3">
         <v>5.0</v>
@@ -7322,16 +7369,16 @@
         <v>305</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H16" s="3">
         <v>3.0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="17">
@@ -7356,7 +7403,7 @@
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -7382,7 +7429,7 @@
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -7408,7 +7455,7 @@
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -7434,7 +7481,7 @@
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -7449,7 +7496,7 @@
         <v>4.0</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E21" s="6">
         <v>15.0</v>
@@ -7464,10 +7511,10 @@
         <v>8.0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -9602,7 +9649,7 @@
         <v>341</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>342</v>
@@ -9616,7 +9663,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>345</v>
@@ -9631,12 +9678,12 @@
         <v>348</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>345</v>
@@ -9651,12 +9698,12 @@
         <v>351</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>345</v>
@@ -9669,12 +9716,12 @@
         <v>352</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>345</v>
@@ -9687,12 +9734,12 @@
         <v>354</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>345</v>
@@ -9707,12 +9754,12 @@
         <v>356</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>345</v>
@@ -9727,12 +9774,12 @@
         <v>358</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>345</v>
@@ -9747,12 +9794,12 @@
         <v>361</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>345</v>
@@ -9767,12 +9814,12 @@
         <v>362</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>345</v>
@@ -9787,12 +9834,12 @@
         <v>365</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>345</v>
@@ -9807,12 +9854,12 @@
         <v>368</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>345</v>
@@ -9827,12 +9874,12 @@
         <v>371</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>372</v>
@@ -9845,12 +9892,12 @@
         <v>374</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>372</v>
@@ -9865,12 +9912,12 @@
         <v>377</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>372</v>
@@ -9885,12 +9932,12 @@
         <v>380</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>372</v>
@@ -9905,12 +9952,12 @@
         <v>382</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>372</v>
@@ -9922,15 +9969,15 @@
         <v>383</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>3</v>
@@ -9948,7 +9995,7 @@
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>3</v>
@@ -9966,7 +10013,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>3</v>
@@ -9979,12 +10026,12 @@
         <v>391</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>3</v>
@@ -9997,12 +10044,12 @@
         <v>393</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>3</v>
@@ -10017,12 +10064,12 @@
         <v>396</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="6" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>3</v>
@@ -10042,7 +10089,7 @@
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>3</v>
@@ -10055,12 +10102,12 @@
         <v>402</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="6" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>3</v>
@@ -10073,12 +10120,12 @@
         <v>404</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>3</v>
@@ -10093,12 +10140,12 @@
         <v>407</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>12</v>
@@ -10113,7 +10160,7 @@
         <v>409</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="28" ht="15.75" customHeight="1">
@@ -10156,7 +10203,7 @@
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>11</v>
@@ -10171,12 +10218,12 @@
         <v>418</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>11</v>
@@ -10194,7 +10241,7 @@
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>11</v>
@@ -10207,12 +10254,12 @@
         <v>420</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="6" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>11</v>
@@ -10238,7 +10285,7 @@
         <v>11</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
@@ -10250,7 +10297,7 @@
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>11</v>
@@ -10290,7 +10337,7 @@
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>11</v>
@@ -10310,7 +10357,7 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>11</v>
@@ -10330,7 +10377,7 @@
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="6" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>11</v>
@@ -10350,7 +10397,7 @@
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>11</v>
@@ -10365,12 +10412,12 @@
         <v>449</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>11</v>
@@ -10390,7 +10437,7 @@
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>11</v>
@@ -10410,7 +10457,7 @@
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
@@ -10430,7 +10477,7 @@
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>11</v>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -81,7 +81,7 @@
     <t>r_wolf</t>
   </si>
   <si>
-    <t>狼の指輪</t>
+    <t>狼の契約</t>
   </si>
   <si>
     <t>summon</t>
@@ -1816,7 +1816,7 @@
       <c r="A2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>19</v>
       </c>
       <c r="C2" s="3" t="s">

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="指輪プール" sheetId="1" r:id="rId4"/>
+    <sheet state="visible" name="契約プール" sheetId="1" r:id="rId4"/>
     <sheet state="visible" name="魔法プール" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="エンチャント" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="階層データ" sheetId="4" r:id="rId7"/>
@@ -15,14 +15,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="PwGAx27xyYJwXwOWAsKRA8sJa/6C9ASi3yl2gAIyaOs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="GA6kw8FcyWfUYXNJI/UT4sDKTrUMm98wimCNSfnvoqs="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="761" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="464">
   <si>
     <t>id</t>
   </si>
@@ -108,7 +108,7 @@
     <t>r_hyena</t>
   </si>
   <si>
-    <t>腐臭の指輪</t>
+    <t>腐臭の契約</t>
   </si>
   <si>
     <t>turn_start</t>
@@ -126,7 +126,7 @@
     <t>r_flame</t>
   </si>
   <si>
-    <t>鬼火の指輪</t>
+    <t>鬼火の契約</t>
   </si>
   <si>
     <t>on_summon</t>
@@ -144,7 +144,7 @@
     <t>r_stone</t>
   </si>
   <si>
-    <t>石像の指輪</t>
+    <t>石像の契約</t>
   </si>
   <si>
     <t>on_spell</t>
@@ -165,7 +165,7 @@
     <t>r_dragon</t>
   </si>
   <si>
-    <t>竜の指輪</t>
+    <t>竜の契約</t>
   </si>
   <si>
     <t>on_damage_count</t>
@@ -183,7 +183,7 @@
     <t>r_shadow</t>
   </si>
   <si>
-    <t>影の指輪</t>
+    <t>影の契約</t>
   </si>
   <si>
     <t>on_death_count</t>
@@ -204,7 +204,7 @@
     <t>r_rat</t>
   </si>
   <si>
-    <t>鼠の指輪</t>
+    <t>鼠の契約</t>
   </si>
   <si>
     <t>鼠</t>
@@ -219,7 +219,7 @@
     <t>r_skel</t>
   </si>
   <si>
-    <t>骸骨の指輪</t>
+    <t>骸骨の契約</t>
   </si>
   <si>
     <t>on_ally_death_notskel</t>
@@ -237,7 +237,7 @@
     <t>r_djinn</t>
   </si>
   <si>
-    <t>魔神の指輪</t>
+    <t>魔神の契約</t>
   </si>
   <si>
     <t>on_full_board</t>
@@ -258,7 +258,7 @@
     <t>r_bear</t>
   </si>
   <si>
-    <t>熊の指輪</t>
+    <t>熊の契約</t>
   </si>
   <si>
     <t>on_outnumbered</t>
@@ -279,7 +279,7 @@
     <t>r_wall</t>
   </si>
   <si>
-    <t>城壁の指輪</t>
+    <t>城壁の契約</t>
   </si>
   <si>
     <t>城壁</t>
@@ -294,7 +294,7 @@
     <t>r_needle</t>
   </si>
   <si>
-    <t>針の指輪</t>
+    <t>針の契約</t>
   </si>
   <si>
     <t>passive</t>
@@ -309,13 +309,13 @@
     <t>r_adj_cnt</t>
   </si>
   <si>
-    <t>隣接の指輪</t>
+    <t>隣接の契約</t>
   </si>
   <si>
     <t>adj_count</t>
   </si>
   <si>
-    <t>隣接する召喚指輪の召喚数+1</t>
+    <t>隣接する召喚契約の召喚数+1</t>
   </si>
   <si>
     <t>ユニーク</t>
@@ -324,7 +324,7 @@
     <t>r_lifereg</t>
   </si>
   <si>
-    <t>生命の指輪</t>
+    <t>生命の契約</t>
   </si>
   <si>
     <t>life_reg</t>
@@ -336,7 +336,7 @@
     <t>r_fury</t>
   </si>
   <si>
-    <t>憤激の指輪</t>
+    <t>憤激の契約</t>
   </si>
   <si>
     <t>fury_passive</t>
@@ -348,7 +348,7 @@
     <t>r_extra</t>
   </si>
   <si>
-    <t>行動の指輪</t>
+    <t>行動の契約</t>
   </si>
   <si>
     <t>extra_action</t>
@@ -360,19 +360,19 @@
     <t>r_buff_adj</t>
   </si>
   <si>
-    <t>増幅の指輪</t>
+    <t>増幅の契約</t>
   </si>
   <si>
     <t>buff_adj</t>
   </si>
   <si>
-    <t>戦闘終了時、隣接する召喚指輪の仲間ATK/HP+1（永続累積）</t>
+    <t>戦闘終了時、隣接する召喚契約の仲間ATK/HP+1（永続累積）</t>
   </si>
   <si>
     <t>r_shared_def</t>
   </si>
   <si>
-    <t>共鳴の指輪</t>
+    <t>共鳴の契約</t>
   </si>
   <si>
     <t>shared_def</t>
@@ -384,7 +384,7 @@
     <t>r_poison</t>
   </si>
   <si>
-    <t>毒沼の指輪</t>
+    <t>毒沼の契約</t>
   </si>
   <si>
     <t>poison_aura</t>
@@ -396,7 +396,7 @@
     <t>r_catalyst</t>
   </si>
   <si>
-    <t>触媒の指輪</t>
+    <t>触媒の契約</t>
   </si>
   <si>
     <t>catalyst</t>
@@ -405,6 +405,51 @@
     <t>毒ダメージ×(Grade+1)倍</t>
   </si>
   <si>
+    <t>farsight</t>
+  </si>
+  <si>
+    <t>遠見の契約</t>
+  </si>
+  <si>
+    <t>鍛冶屋、休息所の出現率が1.5倍になり、すべての選択肢を選べるようになる。</t>
+  </si>
+  <si>
+    <t>魔力循環の契約</t>
+  </si>
+  <si>
+    <t>杖のチャージが減らなくなる。</t>
+  </si>
+  <si>
+    <t>触媒環の契約</t>
+  </si>
+  <si>
+    <t>消耗品の効果が2倍になる。</t>
+  </si>
+  <si>
+    <t>孤高の契約</t>
+  </si>
+  <si>
+    <t>盤面に仲間が1体だけの時、その仲間のATKとHPを2倍にする。</t>
+  </si>
+  <si>
+    <t>試行の契約</t>
+  </si>
+  <si>
+    <t>4回リロールするたびにランダムな指輪が1グレードアップする。</t>
+  </si>
+  <si>
+    <t>鏡の契約</t>
+  </si>
+  <si>
+    <t>戦闘開始時、右の契約のコピーになる。（コピー後に戦闘開始時効果がある場合はこのあとで処理）</t>
+  </si>
+  <si>
+    <t>我慢の契約</t>
+  </si>
+  <si>
+    <t>「戦闘開始時」を「ターン開始時」に変更する。</t>
+  </si>
+  <si>
     <t>種別(wand/consumable)</t>
   </si>
   <si>
@@ -753,16 +798,7 @@
     <t>対象</t>
   </si>
   <si>
-    <t>G1効果</t>
-  </si>
-  <si>
-    <t>G2効果</t>
-  </si>
-  <si>
-    <t>G3効果</t>
-  </si>
-  <si>
-    <t>G4効果</t>
+    <t>効果</t>
   </si>
   <si>
     <t>重複可</t>
@@ -777,16 +813,7 @@
     <t>召喚指輪</t>
   </si>
   <si>
-    <t>HP+5</t>
-  </si>
-  <si>
-    <t>HP+10</t>
-  </si>
-  <si>
-    <t>HP+25</t>
-  </si>
-  <si>
-    <t>HP+75</t>
+    <t>HP+5×Grade</t>
   </si>
   <si>
     <t>○</t>
@@ -798,16 +825,7 @@
     <t>凶暴</t>
   </si>
   <si>
-    <t>ATK+5</t>
-  </si>
-  <si>
-    <t>ATK+10</t>
-  </si>
-  <si>
-    <t>ATK+25</t>
-  </si>
-  <si>
-    <t>ATK+75</t>
+    <t>ATK+5×Grade</t>
   </si>
   <si>
     <t>召喚時のグレードで計算</t>
@@ -819,15 +837,6 @@
     <t>召喚数+1</t>
   </si>
   <si>
-    <t>召喚数+2</t>
-  </si>
-  <si>
-    <t>召喚数+5</t>
-  </si>
-  <si>
-    <t>召喚数+15</t>
-  </si>
-  <si>
     <t>Grade×スタック数が追加召喚数</t>
   </si>
   <si>
@@ -961,9 +970,6 @@
   </si>
   <si>
     <t>出現確率(概算)</t>
-  </si>
-  <si>
-    <t>効果</t>
   </si>
   <si>
     <t>実装上の注意</t>
@@ -1866,7 +1872,7 @@
       <c r="A3" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="7" t="s">
         <v>28</v>
       </c>
       <c r="C3" s="6" t="s">
@@ -1914,7 +1920,7 @@
       <c r="A4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
       <c r="C4" s="3" t="s">
@@ -1956,7 +1962,7 @@
       <c r="A5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="7" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="6" t="s">
@@ -2006,7 +2012,7 @@
       <c r="A6" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C6" s="3" t="s">
@@ -2054,7 +2060,7 @@
       <c r="A7" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="7" t="s">
         <v>53</v>
       </c>
       <c r="C7" s="6" t="s">
@@ -2100,7 +2106,7 @@
       <c r="A8" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="4" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="3" t="s">
@@ -2146,7 +2152,7 @@
       <c r="A9" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="7" t="s">
         <v>65</v>
       </c>
       <c r="C9" s="6" t="s">
@@ -2192,7 +2198,7 @@
       <c r="A10" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="4" t="s">
         <v>71</v>
       </c>
       <c r="C10" s="3" t="s">
@@ -2240,7 +2246,7 @@
       <c r="A11" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="7" t="s">
         <v>78</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -2284,7 +2290,7 @@
       <c r="A12" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="4" t="s">
         <v>85</v>
       </c>
       <c r="C12" s="3" t="s">
@@ -2326,7 +2332,7 @@
       <c r="A13" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>90</v>
       </c>
       <c r="C13" s="6" t="s">
@@ -2358,7 +2364,7 @@
       <c r="A14" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="4" t="s">
         <v>95</v>
       </c>
       <c r="C14" s="3" t="s">
@@ -2394,7 +2400,7 @@
       <c r="A15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="7" t="s">
         <v>100</v>
       </c>
       <c r="C15" s="6" t="s">
@@ -2426,7 +2432,7 @@
       <c r="A16" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="4" t="s">
         <v>104</v>
       </c>
       <c r="C16" s="3" t="s">
@@ -2458,7 +2464,7 @@
       <c r="A17" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="B17" s="6" t="s">
+      <c r="B17" s="7" t="s">
         <v>108</v>
       </c>
       <c r="C17" s="6" t="s">
@@ -2490,7 +2496,7 @@
       <c r="A18" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="4" t="s">
         <v>112</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -2513,7 +2519,7 @@
       </c>
       <c r="O18" s="3"/>
       <c r="P18" s="3"/>
-      <c r="Q18" s="3" t="s">
+      <c r="Q18" s="4" t="s">
         <v>114</v>
       </c>
       <c r="R18" s="8"/>
@@ -2522,7 +2528,7 @@
       <c r="A19" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="B19" s="6" t="s">
+      <c r="B19" s="7" t="s">
         <v>116</v>
       </c>
       <c r="C19" s="6" t="s">
@@ -2554,7 +2560,7 @@
       <c r="A20" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="4" t="s">
         <v>120</v>
       </c>
       <c r="C20" s="3" t="s">
@@ -2586,7 +2592,7 @@
       <c r="A21" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="B21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>124</v>
       </c>
       <c r="C21" s="6" t="s">
@@ -2615,8 +2621,12 @@
       <c r="R21" s="8"/>
     </row>
     <row r="22">
-      <c r="A22" s="6"/>
-      <c r="B22" s="6"/>
+      <c r="A22" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>128</v>
+      </c>
       <c r="C22" s="6" t="s">
         <v>91</v>
       </c>
@@ -2633,14 +2643,20 @@
       <c r="N22" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O22" s="6"/>
+      <c r="O22" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P22" s="6"/>
-      <c r="Q22" s="6"/>
+      <c r="Q22" s="7" t="s">
+        <v>129</v>
+      </c>
       <c r="R22" s="8"/>
     </row>
     <row r="23">
       <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
+      <c r="B23" s="4" t="s">
+        <v>95</v>
+      </c>
       <c r="C23" s="3" t="s">
         <v>91</v>
       </c>
@@ -2657,14 +2673,20 @@
       <c r="N23" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O23" s="3"/>
+      <c r="O23" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P23" s="3"/>
-      <c r="Q23" s="3"/>
+      <c r="Q23" s="4" t="s">
+        <v>97</v>
+      </c>
       <c r="R23" s="8"/>
     </row>
     <row r="24">
       <c r="A24" s="6"/>
-      <c r="B24" s="6"/>
+      <c r="B24" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="C24" s="6" t="s">
         <v>91</v>
       </c>
@@ -2681,14 +2703,20 @@
       <c r="N24" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O24" s="6"/>
+      <c r="O24" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P24" s="6"/>
-      <c r="Q24" s="6"/>
+      <c r="Q24" s="7" t="s">
+        <v>131</v>
+      </c>
       <c r="R24" s="8"/>
     </row>
     <row r="25">
       <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="B25" s="4" t="s">
+        <v>132</v>
+      </c>
       <c r="C25" s="3" t="s">
         <v>91</v>
       </c>
@@ -2705,14 +2733,20 @@
       <c r="N25" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O25" s="3"/>
+      <c r="O25" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P25" s="3"/>
-      <c r="Q25" s="3"/>
+      <c r="Q25" s="4" t="s">
+        <v>133</v>
+      </c>
       <c r="R25" s="8"/>
     </row>
     <row r="26">
       <c r="A26" s="6"/>
-      <c r="B26" s="6"/>
+      <c r="B26" s="7" t="s">
+        <v>134</v>
+      </c>
       <c r="C26" s="6" t="s">
         <v>91</v>
       </c>
@@ -2729,14 +2763,20 @@
       <c r="N26" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O26" s="6"/>
+      <c r="O26" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P26" s="6"/>
-      <c r="Q26" s="6"/>
+      <c r="Q26" s="7" t="s">
+        <v>135</v>
+      </c>
       <c r="R26" s="8"/>
     </row>
     <row r="27">
       <c r="A27" s="3"/>
-      <c r="B27" s="3"/>
+      <c r="B27" s="4" t="s">
+        <v>136</v>
+      </c>
       <c r="C27" s="3" t="s">
         <v>91</v>
       </c>
@@ -2753,14 +2793,20 @@
       <c r="N27" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O27" s="3"/>
+      <c r="O27" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P27" s="3"/>
-      <c r="Q27" s="3"/>
+      <c r="Q27" s="4" t="s">
+        <v>137</v>
+      </c>
       <c r="R27" s="8"/>
     </row>
     <row r="28">
       <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
+      <c r="B28" s="7" t="s">
+        <v>138</v>
+      </c>
       <c r="C28" s="6" t="s">
         <v>91</v>
       </c>
@@ -2777,14 +2823,20 @@
       <c r="N28" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O28" s="6"/>
+      <c r="O28" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P28" s="6"/>
-      <c r="Q28" s="6"/>
+      <c r="Q28" s="7" t="s">
+        <v>139</v>
+      </c>
       <c r="R28" s="8"/>
     </row>
     <row r="29">
       <c r="A29" s="3"/>
-      <c r="B29" s="3"/>
+      <c r="B29" s="4" t="s">
+        <v>140</v>
+      </c>
       <c r="C29" s="3" t="s">
         <v>91</v>
       </c>
@@ -2801,9 +2853,13 @@
       <c r="N29" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O29" s="3"/>
+      <c r="O29" s="3" t="b">
+        <v>1</v>
+      </c>
       <c r="P29" s="3"/>
-      <c r="Q29" s="3"/>
+      <c r="Q29" s="4" t="s">
+        <v>141</v>
+      </c>
       <c r="R29" s="8"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -4040,51 +4096,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>133</v>
+        <v>148</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>134</v>
+        <v>149</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>137</v>
+        <v>152</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>138</v>
+        <v>153</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>1</v>
@@ -4099,33 +4155,33 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>145</v>
+        <v>160</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>146</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>147</v>
+        <v>162</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="E3" s="6" t="b">
         <v>0</v>
@@ -4134,39 +4190,39 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H3" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -4175,39 +4231,39 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="E5" s="6" t="b">
         <v>0</v>
@@ -4216,39 +4272,39 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>1</v>
@@ -4257,39 +4313,39 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>0</v>
@@ -4298,39 +4354,39 @@
         <v>1</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -4339,39 +4395,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>179</v>
+        <v>194</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>182</v>
+        <v>197</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>184</v>
+        <v>199</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="E9" s="6" t="b">
         <v>0</v>
@@ -4380,39 +4436,39 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>188</v>
+        <v>203</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>189</v>
+        <v>204</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>190</v>
+        <v>205</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>191</v>
+        <v>206</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -4421,39 +4477,39 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="E11" s="6" t="b">
         <v>0</v>
@@ -4462,39 +4518,39 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -4503,39 +4559,39 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>150</v>
+        <v>165</v>
       </c>
       <c r="H12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>211</v>
+        <v>226</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>212</v>
+        <v>227</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>214</v>
+        <v>229</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>215</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>216</v>
+        <v>231</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="E13" s="6" t="b">
         <v>0</v>
@@ -4550,33 +4606,33 @@
         <v>0</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>222</v>
+        <v>237</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="E14" s="3" t="b">
         <v>0</v>
@@ -4591,33 +4647,33 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="E15" s="6" t="b">
         <v>0</v>
@@ -4632,33 +4688,33 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>218</v>
-      </c>
       <c r="D16" s="3" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="E16" s="3" t="b">
         <v>0</v>
@@ -4673,33 +4729,33 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>218</v>
+        <v>233</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>0</v>
@@ -4714,19 +4770,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5726,10 +5782,10 @@
   <cols>
     <col customWidth="1" min="1" max="2" width="12.0"/>
     <col customWidth="1" min="3" max="3" width="14.0"/>
-    <col customWidth="1" min="4" max="7" width="20.0"/>
-    <col customWidth="1" min="8" max="8" width="8.0"/>
-    <col customWidth="1" min="9" max="9" width="40.0"/>
-    <col customWidth="1" min="10" max="26" width="8.71"/>
+    <col customWidth="1" min="4" max="4" width="20.0"/>
+    <col customWidth="1" min="5" max="5" width="8.0"/>
+    <col customWidth="1" min="6" max="6" width="40.0"/>
+    <col customWidth="1" min="7" max="23" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
@@ -5740,199 +5796,136 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>243</v>
+        <v>257</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>258</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>245</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>246</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>247</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>249</v>
+        <v>261</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>263</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>252</v>
+        <v>264</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>250</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>258</v>
+        <v>262</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>267</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>255</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D4" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="F4" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="G4" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="H4" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>270</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>250</v>
+        <v>262</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>151</v>
+        <v>274</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>271</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6943,34 +6936,34 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
@@ -6988,14 +6981,14 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -7014,14 +7007,14 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="J3" s="6"/>
     </row>
@@ -7040,14 +7033,14 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -7066,14 +7059,14 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -7088,25 +7081,25 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E6" s="3">
         <v>1.0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H6" s="3">
         <v>1.0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="7">
@@ -7124,14 +7117,14 @@
         <v>2.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -7150,14 +7143,14 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -7176,14 +7169,14 @@
         <v>2.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -7202,14 +7195,14 @@
         <v>2.0</v>
       </c>
       <c r="F10" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="G10" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -7224,25 +7217,25 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E11" s="6">
         <v>2.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="H11" s="6">
         <v>2.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="12">
@@ -7260,14 +7253,14 @@
         <v>5.0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J12" s="3"/>
     </row>
@@ -7286,14 +7279,14 @@
         <v>5.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -7312,14 +7305,14 @@
         <v>5.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -7338,14 +7331,14 @@
         <v>5.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -7360,25 +7353,25 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E16" s="3">
         <v>5.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="H16" s="3">
         <v>3.0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="17">
@@ -7396,14 +7389,14 @@
         <v>15.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -7422,14 +7415,14 @@
         <v>15.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -7448,14 +7441,14 @@
         <v>15.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -7474,14 +7467,14 @@
         <v>15.0</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -7496,25 +7489,25 @@
         <v>4.0</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E21" s="6">
         <v>15.0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="H21" s="6">
         <v>8.0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -8520,121 +8513,121 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>313</v>
+        <v>258</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -9643,336 +9636,336 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>141</v>
+        <v>156</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>139</v>
+        <v>154</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>149</v>
+        <v>164</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>148</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>177</v>
+        <v>192</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>201</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>185</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>194</v>
+        <v>209</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>193</v>
+        <v>208</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>210</v>
+        <v>225</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>219</v>
+        <v>234</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>217</v>
+        <v>232</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
     </row>
     <row r="18">
@@ -9983,14 +9976,14 @@
         <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="19">
@@ -10001,14 +9994,14 @@
         <v>3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="20">
@@ -10019,11 +10012,11 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>36</v>
@@ -10037,11 +10030,11 @@
         <v>3</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>42</v>
@@ -10055,13 +10048,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>49</v>
@@ -10075,16 +10068,16 @@
         <v>3</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -10095,11 +10088,11 @@
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>73</v>
@@ -10113,11 +10106,11 @@
         <v>3</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>67</v>
@@ -10131,13 +10124,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>80</v>
@@ -10151,13 +10144,13 @@
         <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>42</v>
@@ -10165,40 +10158,40 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
+        <v>418</v>
+      </c>
+      <c r="F29" s="6" t="s">
         <v>416</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -10209,13 +10202,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -10229,14 +10222,14 @@
         <v>11</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -10247,11 +10240,11 @@
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>73</v>
@@ -10265,21 +10258,21 @@
         <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -10289,10 +10282,10 @@
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -10303,36 +10296,36 @@
         <v>11</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -10343,16 +10336,16 @@
         <v>11</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -10363,16 +10356,16 @@
         <v>11</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -10383,16 +10376,16 @@
         <v>11</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -10403,16 +10396,16 @@
         <v>11</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -10423,16 +10416,16 @@
         <v>11</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -10443,16 +10436,16 @@
         <v>11</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -10463,16 +10456,16 @@
         <v>11</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -10483,16 +10476,16 @@
         <v>11</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -15,14 +15,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="GA6kw8FcyWfUYXNJI/UT4sDKTrUMm98wimCNSfnvoqs="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="tG32v3HQ64QCNgyY6PxkQuVgpciYZHlhRzlUk1TTFnA="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="757" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="475">
   <si>
     <t>id</t>
   </si>
@@ -252,7 +252,7 @@
     <t>djinn_replace</t>
   </si>
   <si>
-    <t>盤面6体時、魔神以外を全破壊して魔神を召喚</t>
+    <t>盤面に魔神以外で6体いる時、全破壊して魔神を召喚</t>
   </si>
   <si>
     <t>r_bear</t>
@@ -306,6 +306,102 @@
     <t>ターン開始時、ランダムな敵に1ダメ×(Grade×2)回</t>
   </si>
   <si>
+    <t>r_lifereg</t>
+  </si>
+  <si>
+    <t>生命の契約</t>
+  </si>
+  <si>
+    <t>life_reg</t>
+  </si>
+  <si>
+    <t>戦闘終了時ライフ+Grade</t>
+  </si>
+  <si>
+    <t>r_fury</t>
+  </si>
+  <si>
+    <t>憤激の契約</t>
+  </si>
+  <si>
+    <t>fury_passive</t>
+  </si>
+  <si>
+    <t>キャラがダメージを受けるたび全仲間ATK+Grade</t>
+  </si>
+  <si>
+    <t>r_extra</t>
+  </si>
+  <si>
+    <t>行動の契約</t>
+  </si>
+  <si>
+    <t>extra_action</t>
+  </si>
+  <si>
+    <t>プレイヤーの行動回数+Grade</t>
+  </si>
+  <si>
+    <t>r_buff_adj</t>
+  </si>
+  <si>
+    <t>増幅の契約</t>
+  </si>
+  <si>
+    <t>buff_adj</t>
+  </si>
+  <si>
+    <t>戦闘終了時、隣接する召喚契約の仲間ATK/HP+1（永続累積）</t>
+  </si>
+  <si>
+    <t>r_shared_def</t>
+  </si>
+  <si>
+    <t>共鳴の契約</t>
+  </si>
+  <si>
+    <t>shared_def</t>
+  </si>
+  <si>
+    <t>同名仲間が複数いる場合、全員にATK+5/HP+5×Grade</t>
+  </si>
+  <si>
+    <t>r_poison</t>
+  </si>
+  <si>
+    <t>毒沼の契約</t>
+  </si>
+  <si>
+    <t>poison_aura</t>
+  </si>
+  <si>
+    <t>ダメージを受けた敵に毒付与（HP-3×Grade/ターン、重複可）</t>
+  </si>
+  <si>
+    <t>r_catalyst</t>
+  </si>
+  <si>
+    <t>触媒の契約</t>
+  </si>
+  <si>
+    <t>catalyst</t>
+  </si>
+  <si>
+    <t>毒ダメージ×(Grade+1)倍</t>
+  </si>
+  <si>
+    <t>r_farsight</t>
+  </si>
+  <si>
+    <t>遠見の契約</t>
+  </si>
+  <si>
+    <t>farsight</t>
+  </si>
+  <si>
+    <t>鍛冶屋、休息所の出現率が1.5倍になり、すべての選択肢を選べるようになる。</t>
+  </si>
+  <si>
     <t>r_adj_cnt</t>
   </si>
   <si>
@@ -318,133 +414,70 @@
     <t>隣接する召喚契約の召喚数+1</t>
   </si>
   <si>
-    <t>ユニーク</t>
-  </si>
-  <si>
-    <t>r_lifereg</t>
-  </si>
-  <si>
-    <t>生命の契約</t>
-  </si>
-  <si>
-    <t>life_reg</t>
-  </si>
-  <si>
-    <t>戦闘終了時ライフ+Grade</t>
-  </si>
-  <si>
-    <t>r_fury</t>
-  </si>
-  <si>
-    <t>憤激の契約</t>
-  </si>
-  <si>
-    <t>fury_passive</t>
-  </si>
-  <si>
-    <t>キャラがダメージを受けるたび全仲間ATK+Grade</t>
-  </si>
-  <si>
-    <t>r_extra</t>
-  </si>
-  <si>
-    <t>行動の契約</t>
-  </si>
-  <si>
-    <t>extra_action</t>
-  </si>
-  <si>
-    <t>プレイヤーの行動回数+Grade</t>
-  </si>
-  <si>
-    <t>r_buff_adj</t>
-  </si>
-  <si>
-    <t>増幅の契約</t>
-  </si>
-  <si>
-    <t>buff_adj</t>
-  </si>
-  <si>
-    <t>戦闘終了時、隣接する召喚契約の仲間ATK/HP+1（永続累積）</t>
-  </si>
-  <si>
-    <t>r_shared_def</t>
-  </si>
-  <si>
-    <t>共鳴の契約</t>
-  </si>
-  <si>
-    <t>shared_def</t>
-  </si>
-  <si>
-    <t>同名仲間が複数いる場合、全員にATK+5/HP+5×Grade</t>
-  </si>
-  <si>
-    <t>r_poison</t>
-  </si>
-  <si>
-    <t>毒沼の契約</t>
-  </si>
-  <si>
-    <t>poison_aura</t>
-  </si>
-  <si>
-    <t>ダメージを受けた敵に毒付与（HP-3×Grade/ターン、重複可）</t>
-  </si>
-  <si>
-    <t>r_catalyst</t>
-  </si>
-  <si>
-    <t>触媒の契約</t>
-  </si>
-  <si>
-    <t>catalyst</t>
-  </si>
-  <si>
-    <t>毒ダメージ×(Grade+1)倍</t>
-  </si>
-  <si>
-    <t>farsight</t>
-  </si>
-  <si>
-    <t>遠見の契約</t>
-  </si>
-  <si>
-    <t>鍛冶屋、休息所の出現率が1.5倍になり、すべての選択肢を選べるようになる。</t>
+    <t>r_mana_cycle</t>
   </si>
   <si>
     <t>魔力循環の契約</t>
   </si>
   <si>
+    <t>mana_cycle</t>
+  </si>
+  <si>
     <t>杖のチャージが減らなくなる。</t>
   </si>
   <si>
+    <t>r_catalyst_ring</t>
+  </si>
+  <si>
     <t>触媒環の契約</t>
   </si>
   <si>
+    <t>catalyst_ring</t>
+  </si>
+  <si>
     <t>消耗品の効果が2倍になる。</t>
   </si>
   <si>
+    <t>r_solitude</t>
+  </si>
+  <si>
     <t>孤高の契約</t>
   </si>
   <si>
+    <t>solitude</t>
+  </si>
+  <si>
     <t>盤面に仲間が1体だけの時、その仲間のATKとHPを2倍にする。</t>
   </si>
   <si>
+    <t>r_trials</t>
+  </si>
+  <si>
     <t>試行の契約</t>
   </si>
   <si>
+    <t>trials</t>
+  </si>
+  <si>
     <t>4回リロールするたびにランダムな指輪が1グレードアップする。</t>
   </si>
   <si>
+    <t>r_patience</t>
+  </si>
+  <si>
     <t>鏡の契約</t>
   </si>
   <si>
+    <t>mirror</t>
+  </si>
+  <si>
     <t>戦闘開始時、右の契約のコピーになる。（コピー後に戦闘開始時効果がある場合はこのあとで処理）</t>
   </si>
   <si>
     <t>我慢の契約</t>
+  </si>
+  <si>
+    <t>patience</t>
   </si>
   <si>
     <t>「戦闘開始時」を「ターン開始時」に変更する。</t>
@@ -1483,7 +1516,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="15">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1508,7 +1541,25 @@
     <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="4" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="1" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1946,7 +1997,7 @@
       <c r="K4" s="3">
         <v>1.0</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="8"/>
       <c r="M4" s="3"/>
       <c r="N4" s="3" t="b">
         <v>0</v>
@@ -1956,7 +2007,7 @@
       <c r="Q4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="R4" s="8"/>
+      <c r="R4" s="9"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
@@ -1992,7 +2043,7 @@
       <c r="K5" s="6">
         <v>1.0</v>
       </c>
-      <c r="L5" s="6"/>
+      <c r="L5" s="10"/>
       <c r="M5" s="6" t="s">
         <v>44</v>
       </c>
@@ -2042,7 +2093,7 @@
       <c r="K6" s="3">
         <v>1.0</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="8"/>
       <c r="M6" s="3"/>
       <c r="N6" s="3" t="b">
         <v>0</v>
@@ -2054,7 +2105,7 @@
       <c r="Q6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="R6" s="8"/>
+      <c r="R6" s="9"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
@@ -2086,7 +2137,7 @@
       <c r="K7" s="6">
         <v>1.0</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="10" t="s">
         <v>57</v>
       </c>
       <c r="M7" s="6"/>
@@ -2100,7 +2151,7 @@
       <c r="Q7" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="R7" s="8"/>
+      <c r="R7" s="9"/>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
@@ -2136,7 +2187,7 @@
       <c r="K8" s="4">
         <v>3.0</v>
       </c>
-      <c r="L8" s="3"/>
+      <c r="L8" s="8"/>
       <c r="M8" s="3"/>
       <c r="N8" s="3" t="b">
         <v>0</v>
@@ -2146,7 +2197,7 @@
       <c r="Q8" s="4" t="s">
         <v>63</v>
       </c>
-      <c r="R8" s="8"/>
+      <c r="R8" s="9"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
@@ -2182,7 +2233,7 @@
       <c r="K9" s="6">
         <v>1.0</v>
       </c>
-      <c r="L9" s="6"/>
+      <c r="L9" s="10"/>
       <c r="M9" s="6"/>
       <c r="N9" s="6" t="b">
         <v>0</v>
@@ -2192,7 +2243,7 @@
       <c r="Q9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="R9" s="8"/>
+      <c r="R9" s="9"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -2228,7 +2279,7 @@
       <c r="K10" s="3">
         <v>1.0</v>
       </c>
-      <c r="L10" s="3" t="s">
+      <c r="L10" s="8" t="s">
         <v>75</v>
       </c>
       <c r="M10" s="3"/>
@@ -2237,10 +2288,10 @@
       </c>
       <c r="O10" s="3"/>
       <c r="P10" s="3"/>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="R10" s="8"/>
+      <c r="R10" s="9"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
@@ -2272,7 +2323,7 @@
       <c r="K11" s="6">
         <v>1.0</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="10" t="s">
         <v>82</v>
       </c>
       <c r="M11" s="6"/>
@@ -2284,7 +2335,7 @@
       <c r="Q11" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="R11" s="8"/>
+      <c r="R11" s="9"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
@@ -2316,7 +2367,7 @@
       <c r="K12" s="3">
         <v>1.0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="8"/>
       <c r="M12" s="3"/>
       <c r="N12" s="3" t="b">
         <v>1</v>
@@ -2326,7 +2377,7 @@
       <c r="Q12" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="R12" s="8"/>
+      <c r="R12" s="9"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
@@ -2346,7 +2397,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
       <c r="K13" s="6"/>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="10" t="s">
         <v>92</v>
       </c>
       <c r="M13" s="6"/>
@@ -2358,242 +2409,238 @@
       <c r="Q13" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="R13" s="8"/>
+      <c r="R13" s="9"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C14" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3"/>
-      <c r="L14" s="3" t="s">
+      <c r="D14" s="6"/>
+      <c r="E14" s="6"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="M14" s="3"/>
-      <c r="N14" s="3" t="b">
+      <c r="M14" s="6"/>
+      <c r="N14" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O14" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P14" s="3"/>
-      <c r="Q14" s="4" t="s">
+      <c r="O14" s="6"/>
+      <c r="P14" s="6"/>
+      <c r="Q14" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="R14" s="5" t="s">
+      <c r="R14" s="9"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="s">
+      <c r="B15" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C15" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+      <c r="G15" s="3"/>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3"/>
+      <c r="L15" s="8" t="s">
         <v>100</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="M15" s="3"/>
+      <c r="N15" s="3" t="b">
+        <v>0</v>
+      </c>
+      <c r="O15" s="3"/>
+      <c r="P15" s="3"/>
+      <c r="Q15" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="R15" s="9"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C16" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D15" s="6"/>
-      <c r="E15" s="6"/>
-      <c r="F15" s="6"/>
-      <c r="G15" s="6"/>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6"/>
-      <c r="L15" s="6" t="s">
-        <v>101</v>
-      </c>
-      <c r="M15" s="6"/>
-      <c r="N15" s="6" t="b">
+      <c r="D16" s="6"/>
+      <c r="E16" s="6"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="6"/>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="M16" s="6"/>
+      <c r="N16" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O15" s="6"/>
-      <c r="P15" s="6"/>
-      <c r="Q15" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="R15" s="8"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="C16" s="3" t="s">
+      <c r="O16" s="6"/>
+      <c r="P16" s="6"/>
+      <c r="Q16" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="R16" s="9"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="M16" s="3"/>
-      <c r="N16" s="3" t="b">
+      <c r="D17" s="3"/>
+      <c r="E17" s="3"/>
+      <c r="F17" s="3"/>
+      <c r="G17" s="3"/>
+      <c r="H17" s="3"/>
+      <c r="I17" s="3"/>
+      <c r="J17" s="3"/>
+      <c r="K17" s="3"/>
+      <c r="L17" s="8" t="s">
+        <v>108</v>
+      </c>
+      <c r="M17" s="3"/>
+      <c r="N17" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O16" s="3"/>
-      <c r="P16" s="3"/>
-      <c r="Q16" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="R16" s="8"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C17" s="6" t="s">
+      <c r="O17" s="3"/>
+      <c r="P17" s="3"/>
+      <c r="Q17" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="R17" s="9"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
-      <c r="G17" s="6"/>
-      <c r="H17" s="6"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
-      <c r="K17" s="6"/>
-      <c r="L17" s="6" t="s">
-        <v>109</v>
-      </c>
-      <c r="M17" s="6"/>
-      <c r="N17" s="6" t="b">
+      <c r="D18" s="6"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="6"/>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="M18" s="6"/>
+      <c r="N18" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6"/>
-      <c r="Q17" s="6" t="s">
-        <v>110</v>
-      </c>
-      <c r="R17" s="8"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="O18" s="6"/>
+      <c r="P18" s="6"/>
+      <c r="Q18" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="R18" s="9"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-      <c r="J18" s="3"/>
-      <c r="K18" s="3"/>
-      <c r="L18" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="M18" s="3"/>
-      <c r="N18" s="3" t="b">
+      <c r="D19" s="3"/>
+      <c r="E19" s="3"/>
+      <c r="F19" s="3"/>
+      <c r="G19" s="3"/>
+      <c r="H19" s="3"/>
+      <c r="I19" s="3"/>
+      <c r="J19" s="3"/>
+      <c r="K19" s="3"/>
+      <c r="L19" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="M19" s="3"/>
+      <c r="N19" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O18" s="3"/>
-      <c r="P18" s="3"/>
-      <c r="Q18" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="R18" s="8"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>116</v>
-      </c>
-      <c r="C19" s="6" t="s">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+      <c r="Q19" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="R19" s="9"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1">
+      <c r="A20" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C20" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6" t="s">
-        <v>117</v>
-      </c>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6" t="b">
+      <c r="D20" s="6"/>
+      <c r="E20" s="6"/>
+      <c r="F20" s="6"/>
+      <c r="G20" s="6"/>
+      <c r="H20" s="6"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="M20" s="6"/>
+      <c r="N20" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="R19" s="8"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-      <c r="J20" s="3"/>
-      <c r="K20" s="3"/>
-      <c r="L20" s="3" t="s">
+      <c r="O20" s="6"/>
+      <c r="P20" s="6"/>
+      <c r="Q20" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="M20" s="3"/>
-      <c r="N20" s="3" t="b">
-        <v>0</v>
-      </c>
-      <c r="O20" s="3"/>
-      <c r="P20" s="3"/>
-      <c r="Q20" s="3" t="s">
+      <c r="R20" s="9"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="R20" s="8"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="6" t="s">
+      <c r="B21" s="7" t="s">
         <v>123</v>
-      </c>
-      <c r="B21" s="7" t="s">
-        <v>124</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>91</v>
@@ -2606,261 +2653,283 @@
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
       <c r="K21" s="6"/>
-      <c r="L21" s="6" t="s">
-        <v>125</v>
+      <c r="L21" s="11" t="s">
+        <v>124</v>
       </c>
       <c r="M21" s="6"/>
       <c r="N21" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O21" s="6"/>
+      <c r="O21" s="6" t="b">
+        <v>1</v>
+      </c>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6" t="s">
+      <c r="Q21" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="R21" s="9"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="R21" s="8"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="7" t="s">
+      <c r="B22" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C22" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="D22" s="3"/>
+      <c r="E22" s="3"/>
+      <c r="F22" s="3"/>
+      <c r="G22" s="3"/>
+      <c r="H22" s="3"/>
+      <c r="I22" s="3"/>
+      <c r="J22" s="3"/>
+      <c r="K22" s="3"/>
+      <c r="L22" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="C22" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D22" s="6"/>
-      <c r="E22" s="6"/>
-      <c r="F22" s="6"/>
-      <c r="G22" s="6"/>
-      <c r="H22" s="6"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
-      <c r="K22" s="6"/>
-      <c r="L22" s="6"/>
-      <c r="M22" s="6"/>
-      <c r="N22" s="6" t="b">
+      <c r="M22" s="3"/>
+      <c r="N22" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O22" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="P22" s="6"/>
-      <c r="Q22" s="7" t="s">
+      <c r="P22" s="3"/>
+      <c r="Q22" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="R22" s="8"/>
+      <c r="R22" s="9"/>
     </row>
     <row r="23">
-      <c r="A23" s="3"/>
-      <c r="B23" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="3" t="s">
+      <c r="A23" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="G23" s="3"/>
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-      <c r="J23" s="3"/>
-      <c r="K23" s="3"/>
-      <c r="L23" s="3"/>
-      <c r="M23" s="3"/>
-      <c r="N23" s="3" t="b">
+      <c r="D23" s="6"/>
+      <c r="E23" s="6"/>
+      <c r="F23" s="6"/>
+      <c r="G23" s="6"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="M23" s="6"/>
+      <c r="N23" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O23" s="3" t="b">
+      <c r="O23" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="P23" s="3"/>
-      <c r="Q23" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="R23" s="8"/>
+      <c r="P23" s="6"/>
+      <c r="Q23" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="R23" s="9"/>
     </row>
     <row r="24">
-      <c r="A24" s="6"/>
-      <c r="B24" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="C24" s="6" t="s">
+      <c r="A24" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D24" s="6"/>
-      <c r="E24" s="6"/>
-      <c r="F24" s="6"/>
-      <c r="G24" s="6"/>
-      <c r="H24" s="6"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
-      <c r="K24" s="6"/>
-      <c r="L24" s="6"/>
-      <c r="M24" s="6"/>
-      <c r="N24" s="6" t="b">
+      <c r="D24" s="3"/>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
+      <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
+      <c r="L24" s="13" t="s">
+        <v>136</v>
+      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O24" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="P24" s="6"/>
-      <c r="Q24" s="7" t="s">
-        <v>131</v>
-      </c>
-      <c r="R24" s="8"/>
+      <c r="P24" s="3"/>
+      <c r="Q24" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="R24" s="9"/>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="C25" s="3" t="s">
+      <c r="A25" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C25" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="3"/>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="G25" s="3"/>
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-      <c r="J25" s="3"/>
-      <c r="K25" s="3"/>
-      <c r="L25" s="3"/>
-      <c r="M25" s="3"/>
-      <c r="N25" s="3" t="b">
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O25" s="3" t="b">
+      <c r="O25" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="P25" s="3"/>
-      <c r="Q25" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="R25" s="8"/>
+      <c r="P25" s="6"/>
+      <c r="Q25" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="R25" s="9"/>
     </row>
     <row r="26">
-      <c r="A26" s="6"/>
-      <c r="B26" s="7" t="s">
-        <v>134</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="A26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
-      <c r="K26" s="6"/>
-      <c r="L26" s="6"/>
-      <c r="M26" s="6"/>
-      <c r="N26" s="6" t="b">
+      <c r="D26" s="3"/>
+      <c r="E26" s="3"/>
+      <c r="F26" s="3"/>
+      <c r="G26" s="3"/>
+      <c r="H26" s="3"/>
+      <c r="I26" s="3"/>
+      <c r="J26" s="3"/>
+      <c r="K26" s="3"/>
+      <c r="L26" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="M26" s="3"/>
+      <c r="N26" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O26" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="P26" s="6"/>
-      <c r="Q26" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="R26" s="8"/>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="R26" s="9"/>
     </row>
     <row r="27">
-      <c r="A27" s="3"/>
-      <c r="B27" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="C27" s="3" t="s">
+      <c r="A27" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D27" s="3"/>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="G27" s="3"/>
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-      <c r="J27" s="3"/>
-      <c r="K27" s="3"/>
-      <c r="L27" s="3"/>
-      <c r="M27" s="3"/>
-      <c r="N27" s="3" t="b">
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="M27" s="6"/>
+      <c r="N27" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O27" s="3" t="b">
+      <c r="O27" s="6" t="b">
         <v>1</v>
       </c>
-      <c r="P27" s="3"/>
-      <c r="Q27" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="R27" s="8"/>
+      <c r="P27" s="6"/>
+      <c r="Q27" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="R27" s="9"/>
     </row>
     <row r="28">
-      <c r="A28" s="6"/>
-      <c r="B28" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="C28" s="6" t="s">
+      <c r="A28" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C28" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
-      <c r="K28" s="6"/>
-      <c r="L28" s="6"/>
-      <c r="M28" s="6"/>
-      <c r="N28" s="6" t="b">
+      <c r="D28" s="3"/>
+      <c r="E28" s="3"/>
+      <c r="F28" s="3"/>
+      <c r="G28" s="3"/>
+      <c r="H28" s="3"/>
+      <c r="I28" s="3"/>
+      <c r="J28" s="3"/>
+      <c r="K28" s="3"/>
+      <c r="L28" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="M28" s="3"/>
+      <c r="N28" s="3" t="b">
         <v>0</v>
       </c>
       <c r="O28" s="3" t="b">
         <v>1</v>
       </c>
-      <c r="P28" s="6"/>
-      <c r="Q28" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="R28" s="8"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="3"/>
-      <c r="B29" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="C29" s="3" t="s">
+      <c r="P28" s="3"/>
+      <c r="Q28" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="R28" s="9"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D29" s="3"/>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="G29" s="3"/>
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-      <c r="J29" s="3"/>
-      <c r="K29" s="3"/>
-      <c r="L29" s="3"/>
-      <c r="M29" s="3"/>
-      <c r="N29" s="3" t="b">
+      <c r="D29" s="6"/>
+      <c r="E29" s="6"/>
+      <c r="F29" s="6"/>
+      <c r="G29" s="6"/>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="10"/>
+      <c r="M29" s="6"/>
+      <c r="N29" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="b">
-        <v>1</v>
-      </c>
-      <c r="P29" s="3"/>
-      <c r="Q29" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="R29" s="8"/>
+      <c r="O29" s="6"/>
+      <c r="P29" s="6"/>
+      <c r="Q29" s="6"/>
+      <c r="R29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="6"/>
@@ -2876,7 +2945,7 @@
       <c r="I30" s="6"/>
       <c r="J30" s="6"/>
       <c r="K30" s="6"/>
-      <c r="L30" s="6"/>
+      <c r="L30" s="10"/>
       <c r="M30" s="6"/>
       <c r="N30" s="6" t="b">
         <v>0</v>
@@ -2884,224 +2953,201 @@
       <c r="O30" s="6"/>
       <c r="P30" s="6"/>
       <c r="Q30" s="6"/>
-      <c r="R30" s="8"/>
+      <c r="R30" s="9"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6" t="s">
+      <c r="A31" s="3"/>
+      <c r="B31" s="3"/>
+      <c r="C31" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D31" s="6"/>
-      <c r="E31" s="6"/>
-      <c r="F31" s="6"/>
-      <c r="G31" s="6"/>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
-      <c r="K31" s="6"/>
-      <c r="L31" s="6"/>
-      <c r="M31" s="6"/>
-      <c r="N31" s="6" t="b">
+      <c r="D31" s="3"/>
+      <c r="E31" s="3"/>
+      <c r="F31" s="3"/>
+      <c r="G31" s="3"/>
+      <c r="H31" s="3"/>
+      <c r="I31" s="3"/>
+      <c r="J31" s="3"/>
+      <c r="K31" s="3"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="3"/>
+      <c r="N31" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O31" s="6"/>
-      <c r="P31" s="6"/>
-      <c r="Q31" s="6"/>
-      <c r="R31" s="8"/>
+      <c r="O31" s="3"/>
+      <c r="P31" s="3"/>
+      <c r="Q31" s="3"/>
+      <c r="R31" s="9"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3"/>
-      <c r="B32" s="3"/>
-      <c r="C32" s="3" t="s">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D32" s="3"/>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="G32" s="3"/>
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-      <c r="J32" s="3"/>
-      <c r="K32" s="3"/>
-      <c r="L32" s="3"/>
-      <c r="M32" s="3"/>
-      <c r="N32" s="3" t="b">
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="10"/>
+      <c r="M32" s="6"/>
+      <c r="N32" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O32" s="3"/>
-      <c r="P32" s="3"/>
-      <c r="Q32" s="3"/>
-      <c r="R32" s="8"/>
+      <c r="O32" s="6"/>
+      <c r="P32" s="6"/>
+      <c r="Q32" s="6"/>
+      <c r="R32" s="9"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6" t="s">
+      <c r="A33" s="3"/>
+      <c r="B33" s="3"/>
+      <c r="C33" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
-      <c r="K33" s="6"/>
-      <c r="L33" s="6"/>
-      <c r="M33" s="6"/>
-      <c r="N33" s="6" t="b">
+      <c r="D33" s="3"/>
+      <c r="E33" s="3"/>
+      <c r="F33" s="3"/>
+      <c r="G33" s="3"/>
+      <c r="H33" s="3"/>
+      <c r="I33" s="3"/>
+      <c r="J33" s="3"/>
+      <c r="K33" s="3"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="3"/>
+      <c r="N33" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O33" s="6"/>
-      <c r="P33" s="6"/>
-      <c r="Q33" s="6"/>
-      <c r="R33" s="8"/>
+      <c r="O33" s="3"/>
+      <c r="P33" s="3"/>
+      <c r="Q33" s="3"/>
+      <c r="R33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3"/>
-      <c r="B34" s="3"/>
-      <c r="C34" s="3" t="s">
+      <c r="A34" s="6"/>
+      <c r="B34" s="6"/>
+      <c r="C34" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D34" s="3"/>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="G34" s="3"/>
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-      <c r="J34" s="3"/>
-      <c r="K34" s="3"/>
-      <c r="L34" s="3"/>
-      <c r="M34" s="3"/>
-      <c r="N34" s="3" t="b">
+      <c r="D34" s="6"/>
+      <c r="E34" s="6"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="10"/>
+      <c r="M34" s="6"/>
+      <c r="N34" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O34" s="3"/>
-      <c r="P34" s="3"/>
-      <c r="Q34" s="3"/>
-      <c r="R34" s="8"/>
+      <c r="O34" s="6"/>
+      <c r="P34" s="6"/>
+      <c r="Q34" s="6"/>
+      <c r="R34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="6"/>
-      <c r="B35" s="6"/>
-      <c r="C35" s="6" t="s">
+      <c r="A35" s="3"/>
+      <c r="B35" s="3"/>
+      <c r="C35" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="6"/>
-      <c r="G35" s="6"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
-      <c r="K35" s="6"/>
-      <c r="L35" s="6"/>
-      <c r="M35" s="6"/>
-      <c r="N35" s="6" t="b">
+      <c r="D35" s="3"/>
+      <c r="E35" s="3"/>
+      <c r="F35" s="3"/>
+      <c r="G35" s="3"/>
+      <c r="H35" s="3"/>
+      <c r="I35" s="3"/>
+      <c r="J35" s="3"/>
+      <c r="K35" s="3"/>
+      <c r="L35" s="8"/>
+      <c r="M35" s="3"/>
+      <c r="N35" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O35" s="6"/>
-      <c r="P35" s="6"/>
-      <c r="Q35" s="6"/>
-      <c r="R35" s="8"/>
+      <c r="O35" s="3"/>
+      <c r="P35" s="3"/>
+      <c r="Q35" s="3"/>
+      <c r="R35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3" t="s">
+      <c r="A36" s="6"/>
+      <c r="B36" s="6"/>
+      <c r="C36" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="3"/>
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-      <c r="J36" s="3"/>
-      <c r="K36" s="3"/>
-      <c r="L36" s="3"/>
-      <c r="M36" s="3"/>
-      <c r="N36" s="3" t="b">
+      <c r="D36" s="6"/>
+      <c r="E36" s="6"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6"/>
+      <c r="H36" s="6"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="10"/>
+      <c r="M36" s="6"/>
+      <c r="N36" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O36" s="3"/>
-      <c r="P36" s="3"/>
-      <c r="Q36" s="3"/>
-      <c r="R36" s="8"/>
+      <c r="O36" s="6"/>
+      <c r="P36" s="6"/>
+      <c r="Q36" s="6"/>
+      <c r="R36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="6"/>
-      <c r="B37" s="6"/>
-      <c r="C37" s="6" t="s">
+      <c r="A37" s="3"/>
+      <c r="B37" s="3"/>
+      <c r="C37" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D37" s="6"/>
-      <c r="E37" s="6"/>
-      <c r="F37" s="6"/>
-      <c r="G37" s="6"/>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
-      <c r="K37" s="6"/>
-      <c r="L37" s="6"/>
-      <c r="M37" s="6"/>
-      <c r="N37" s="6" t="b">
+      <c r="D37" s="3"/>
+      <c r="E37" s="3"/>
+      <c r="F37" s="3"/>
+      <c r="G37" s="3"/>
+      <c r="H37" s="3"/>
+      <c r="I37" s="3"/>
+      <c r="J37" s="3"/>
+      <c r="K37" s="3"/>
+      <c r="L37" s="8"/>
+      <c r="M37" s="3"/>
+      <c r="N37" s="3" t="b">
         <v>0</v>
       </c>
-      <c r="O37" s="6"/>
-      <c r="P37" s="6"/>
-      <c r="Q37" s="6"/>
-      <c r="R37" s="8"/>
+      <c r="O37" s="3"/>
+      <c r="P37" s="3"/>
+      <c r="Q37" s="3"/>
+      <c r="R37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3" t="s">
+      <c r="A38" s="6"/>
+      <c r="B38" s="6"/>
+      <c r="C38" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="D38" s="3"/>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-      <c r="J38" s="3"/>
-      <c r="K38" s="3"/>
-      <c r="L38" s="3"/>
-      <c r="M38" s="3"/>
-      <c r="N38" s="3" t="b">
+      <c r="D38" s="6"/>
+      <c r="E38" s="6"/>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6"/>
+      <c r="H38" s="6"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="6"/>
+      <c r="N38" s="6" t="b">
         <v>0</v>
       </c>
-      <c r="O38" s="3"/>
-      <c r="P38" s="3"/>
-      <c r="Q38" s="3"/>
-      <c r="R38" s="8"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="6"/>
-      <c r="B39" s="6"/>
-      <c r="C39" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="D39" s="6"/>
-      <c r="E39" s="6"/>
-      <c r="F39" s="6"/>
-      <c r="G39" s="6"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
-      <c r="K39" s="6"/>
-      <c r="L39" s="6"/>
-      <c r="M39" s="6"/>
-      <c r="N39" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="O39" s="6"/>
-      <c r="P39" s="6"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="8"/>
-    </row>
+      <c r="O38" s="6"/>
+      <c r="P38" s="6"/>
+      <c r="Q38" s="6"/>
+      <c r="R38" s="9"/>
+    </row>
+    <row r="39" ht="15.75" customHeight="1"/>
     <row r="40" ht="15.75" customHeight="1"/>
     <row r="41" ht="15.75" customHeight="1"/>
     <row r="42" ht="15.75" customHeight="1"/>
@@ -4062,7 +4108,6 @@
     <row r="997" ht="15.75" customHeight="1"/>
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
-    <row r="1000" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -4096,51 +4141,51 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>146</v>
+        <v>157</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="E2" s="3" t="b">
         <v>1</v>
@@ -4155,33 +4200,33 @@
         <v>1</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>158</v>
+        <v>169</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>160</v>
+        <v>171</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="E3" s="6" t="b">
         <v>0</v>
@@ -4190,39 +4235,39 @@
         <v>1</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H3" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="J3" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="L3" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="E4" s="3" t="b">
         <v>0</v>
@@ -4231,39 +4276,39 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H4" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="E5" s="6" t="b">
         <v>0</v>
@@ -4272,39 +4317,39 @@
         <v>0</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H5" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="J5" s="6" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="L5" s="6" t="s">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>177</v>
+        <v>188</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="E6" s="3" t="b">
         <v>1</v>
@@ -4313,39 +4358,39 @@
         <v>0</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H6" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>181</v>
+        <v>192</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="E7" s="6" t="b">
         <v>0</v>
@@ -4354,39 +4399,39 @@
         <v>1</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H7" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="J7" s="6" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="L7" s="6" t="s">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>190</v>
+        <v>201</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>191</v>
+        <v>202</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="E8" s="3" t="b">
         <v>0</v>
@@ -4395,39 +4440,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H8" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>198</v>
+        <v>209</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>199</v>
+        <v>210</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="E9" s="6" t="b">
         <v>0</v>
@@ -4436,39 +4481,39 @@
         <v>1</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H9" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>203</v>
+        <v>214</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>204</v>
+        <v>215</v>
       </c>
       <c r="L9" s="6" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>206</v>
+        <v>217</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="E10" s="3" t="b">
         <v>0</v>
@@ -4477,39 +4522,39 @@
         <v>0</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H10" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>213</v>
+        <v>224</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>214</v>
+        <v>225</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="E11" s="6" t="b">
         <v>0</v>
@@ -4518,39 +4563,39 @@
         <v>0</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H11" s="6" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>218</v>
+        <v>229</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>219</v>
+        <v>230</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>220</v>
+        <v>231</v>
       </c>
       <c r="L11" s="6" t="s">
-        <v>221</v>
+        <v>232</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>222</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>223</v>
+        <v>234</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="E12" s="3" t="b">
         <v>0</v>
@@ -4559,39 +4604,39 @@
         <v>0</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="H12" s="3" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>229</v>
+        <v>240</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="E13" s="6" t="b">
         <v>0</v>
@@ -4606,33 +4651,33 @@
         <v>0</v>
       </c>
       <c r="I13" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="J13" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="L13" s="6" t="s">
-        <v>235</v>
+        <v>246</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>236</v>
+        <v>247</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="E14" s="3" t="b">
         <v>0</v>
@@ -4647,33 +4692,33 @@
         <v>0</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>240</v>
+        <v>251</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>241</v>
+        <v>252</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>242</v>
+        <v>253</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="E15" s="6" t="b">
         <v>0</v>
@@ -4688,33 +4733,33 @@
         <v>0</v>
       </c>
       <c r="I15" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="J15" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>246</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>247</v>
+        <v>258</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="E16" s="3" t="b">
         <v>0</v>
@@ -4729,33 +4774,33 @@
         <v>0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>250</v>
+        <v>261</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>251</v>
+        <v>262</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>252</v>
+        <v>263</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>233</v>
+        <v>244</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="E17" s="6" t="b">
         <v>0</v>
@@ -4770,19 +4815,19 @@
         <v>0</v>
       </c>
       <c r="I17" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="J17" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="L17" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>256</v>
+        <v>267</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -5796,136 +5841,136 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>259</v>
+        <v>270</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>265</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>266</v>
+        <v>277</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>267</v>
+        <v>278</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>268</v>
+        <v>279</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>269</v>
+        <v>280</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>270</v>
+        <v>281</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>271</v>
+        <v>282</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>272</v>
+        <v>283</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>273</v>
+        <v>284</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>275</v>
+        <v>286</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>277</v>
+        <v>288</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>264</v>
+        <v>275</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>262</v>
+        <v>273</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>274</v>
+        <v>285</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -6936,34 +6981,34 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>282</v>
+        <v>293</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>283</v>
+        <v>294</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>284</v>
+        <v>295</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>260</v>
+        <v>271</v>
       </c>
     </row>
     <row r="2">
@@ -6981,14 +7026,14 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="H2" s="3"/>
       <c r="I2" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -7007,14 +7052,14 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="J3" s="6"/>
     </row>
@@ -7033,14 +7078,14 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -7059,14 +7104,14 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
       <c r="J5" s="6"/>
     </row>
@@ -7081,25 +7126,25 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E6" s="3">
         <v>1.0</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="H6" s="3">
         <v>1.0</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="7">
@@ -7117,14 +7162,14 @@
         <v>2.0</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J7" s="6"/>
     </row>
@@ -7143,14 +7188,14 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H8" s="3"/>
       <c r="I8" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -7169,14 +7214,14 @@
         <v>2.0</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J9" s="6"/>
     </row>
@@ -7195,14 +7240,14 @@
         <v>2.0</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H10" s="3"/>
       <c r="I10" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -7217,25 +7262,25 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E11" s="6">
         <v>2.0</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="H11" s="6">
         <v>2.0</v>
       </c>
       <c r="I11" s="6" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J11" s="6" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="12">
@@ -7253,14 +7298,14 @@
         <v>5.0</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J12" s="3"/>
     </row>
@@ -7279,14 +7324,14 @@
         <v>5.0</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="G13" s="6" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J13" s="6"/>
     </row>
@@ -7305,14 +7350,14 @@
         <v>5.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J14" s="3"/>
     </row>
@@ -7331,14 +7376,14 @@
         <v>5.0</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="G15" s="6" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J15" s="6"/>
     </row>
@@ -7353,25 +7398,25 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E16" s="3">
         <v>5.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>211</v>
+        <v>222</v>
       </c>
       <c r="H16" s="3">
         <v>3.0</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="17">
@@ -7389,14 +7434,14 @@
         <v>15.0</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G17" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J17" s="6"/>
     </row>
@@ -7415,14 +7460,14 @@
         <v>15.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J18" s="3"/>
     </row>
@@ -7441,14 +7486,14 @@
         <v>15.0</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="G19" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J19" s="6"/>
     </row>
@@ -7467,14 +7512,14 @@
         <v>15.0</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="J20" s="3"/>
     </row>
@@ -7489,25 +7534,25 @@
         <v>4.0</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="E21" s="6">
         <v>15.0</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="H21" s="6">
         <v>8.0</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="J21" s="6" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -8513,121 +8558,121 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>258</v>
+        <v>269</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>326</v>
+        <v>337</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>327</v>
+        <v>338</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -9636,336 +9681,336 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>257</v>
+        <v>268</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>174</v>
+        <v>185</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>179</v>
+        <v>190</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>192</v>
+        <v>203</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>200</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>217</v>
+        <v>228</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>216</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>224</v>
+        <v>235</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>234</v>
+        <v>245</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="D13" s="6"/>
       <c r="E13" s="6" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>232</v>
+        <v>243</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>244</v>
+        <v>255</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>243</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>248</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>254</v>
+        <v>265</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>255</v>
+        <v>266</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>253</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18">
@@ -9976,14 +10021,14 @@
         <v>3</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
       <c r="D18" s="3"/>
       <c r="E18" s="3" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="19">
@@ -9994,14 +10039,14 @@
         <v>3</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="20">
@@ -10012,11 +10057,11 @@
         <v>3</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>36</v>
@@ -10030,11 +10075,11 @@
         <v>3</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>42</v>
@@ -10048,13 +10093,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>49</v>
@@ -10068,16 +10113,16 @@
         <v>3</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
@@ -10088,11 +10133,11 @@
         <v>3</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="D24" s="3"/>
       <c r="E24" s="3" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>73</v>
@@ -10106,11 +10151,11 @@
         <v>3</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6" t="s">
-        <v>406</v>
+        <v>417</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>67</v>
@@ -10124,13 +10169,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>80</v>
@@ -10144,13 +10189,13 @@
         <v>12</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="F27" s="6" t="s">
         <v>42</v>
@@ -10158,40 +10203,40 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="6" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D29" s="6"/>
       <c r="E29" s="6" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -10202,13 +10247,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>22</v>
@@ -10222,14 +10267,14 @@
         <v>11</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D31" s="6"/>
       <c r="E31" s="6" t="s">
-        <v>421</v>
+        <v>432</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
     </row>
     <row r="32" ht="15.75" customHeight="1">
@@ -10240,11 +10285,11 @@
         <v>11</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3" t="s">
-        <v>422</v>
+        <v>433</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>73</v>
@@ -10258,21 +10303,21 @@
         <v>11</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>423</v>
+        <v>434</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>424</v>
+        <v>435</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>425</v>
+        <v>436</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>426</v>
+        <v>437</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>11</v>
@@ -10282,90 +10327,90 @@
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>428</v>
+        <v>439</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="3" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>419</v>
+        <v>430</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
       <c r="A37" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -10376,116 +10421,116 @@
         <v>11</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="3" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="6" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
       <c r="A42" s="3" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="3" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -15,14 +15,14 @@
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="CFkTDYxSLniCx4yhpmP8lZ96PK8PuJRR+yltRk38YuI="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId11" roundtripDataChecksum="G+eqJxKYCXQD03/153e/9uxebnz0PSs0Q7TTrcb5cAE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="778" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="489">
   <si>
     <t>id</t>
   </si>
@@ -309,7 +309,7 @@
     <t>耐久</t>
   </si>
   <si>
-    <t>あなたが杖を使用すると、</t>
+    <t>あなたが杖を使用した時、</t>
   </si>
   <si>
     <t>r_needle</t>
@@ -561,7 +561,7 @@
     <t>8ダメ</t>
   </si>
   <si>
-    <t>初期装備専用。対象の敵にダメージ</t>
+    <t>初期装備専用。対象の敵に2ダメージ</t>
   </si>
   <si>
     <t>w_hate</t>
@@ -624,7 +624,7 @@
     <t>ATK0(1T)</t>
   </si>
   <si>
-    <t>対象の敵のATKを0にする（1ターン）</t>
+    <t>対象のATKを0にする（1ターン）</t>
   </si>
   <si>
     <t>w_boost</t>
@@ -648,7 +648,7 @@
     <t>+200%</t>
   </si>
   <si>
-    <t>対象の仲間のATK・HP増加</t>
+    <t>対象のATK・HPを1.5倍にする</t>
   </si>
   <si>
     <t>w_rally</t>
@@ -672,7 +672,7 @@
     <t>ATK+120%</t>
   </si>
   <si>
-    <t>全仲間のATK増加</t>
+    <t>全ての仲間のATKを1.2倍にする。</t>
   </si>
   <si>
     <t>w_heal</t>
@@ -696,7 +696,7 @@
     <t>HP+120%</t>
   </si>
   <si>
-    <t>対象の仲間のHP回復（最大値の%）</t>
+    <t>全ての仲間のHPを全回復</t>
   </si>
   <si>
     <t>w_golem</t>
@@ -720,7 +720,7 @@
     <t>40/40</t>
   </si>
   <si>
-    <t>ヘイト持ちゴーレムを召喚</t>
+    <t>初期装備専用。ヘイト持ちの2/2ゴーレムを召喚</t>
   </si>
   <si>
     <t>w_spread</t>
@@ -744,7 +744,7 @@
     <t>×5回</t>
   </si>
   <si>
-    <t>もう片方の杖がGrade+1回発動するようになる</t>
+    <t>右隣の杖の効果を使用する。</t>
   </si>
   <si>
     <t>w_meteor</t>
@@ -768,7 +768,28 @@
     <t>12×2</t>
   </si>
   <si>
-    <t>ランダムなキャラにダメージ×2回</t>
+    <t>全キャラに1ダメージ</t>
+  </si>
+  <si>
+    <t>対象を破壊する。</t>
+  </si>
+  <si>
+    <t>対象に即死付与。</t>
+  </si>
+  <si>
+    <t>対象に再生付与。</t>
+  </si>
+  <si>
+    <t>対象の仲間と、最もATKの低い敵を入れ替える。</t>
+  </si>
+  <si>
+    <t>対象の仲間を破壊し、全ての敵にATKに等しいダメージ</t>
+  </si>
+  <si>
+    <t>このターンをスキップする。</t>
+  </si>
+  <si>
+    <t>対象に隠密付与。</t>
   </si>
   <si>
     <t>c_kill</t>
@@ -1572,7 +1593,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="20">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1606,20 +1627,29 @@
     <xf borderId="3" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
-    <xf borderId="4" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -2606,7 +2636,9 @@
       <c r="B13" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C13" s="4"/>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
       <c r="F13" s="5">
@@ -2649,7 +2681,9 @@
     <row r="14">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
-      <c r="C14" s="4"/>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D14" s="4"/>
       <c r="E14" s="4"/>
       <c r="F14" s="4"/>
@@ -2680,7 +2714,9 @@
     <row r="15">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="4"/>
+      <c r="C15" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D15" s="4"/>
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
@@ -2713,7 +2749,9 @@
     <row r="16">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
-      <c r="C16" s="4"/>
+      <c r="C16" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D16" s="4"/>
       <c r="E16" s="4"/>
       <c r="F16" s="4"/>
@@ -2744,7 +2782,9 @@
     <row r="17">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
-      <c r="C17" s="4"/>
+      <c r="C17" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
       <c r="F17" s="5">
@@ -2779,7 +2819,9 @@
     <row r="18">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
-      <c r="C18" s="4"/>
+      <c r="C18" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
       <c r="F18" s="5">
@@ -2814,7 +2856,9 @@
     <row r="19">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
-      <c r="C19" s="4"/>
+      <c r="C19" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
       <c r="F19" s="5">
@@ -2849,7 +2893,9 @@
     <row r="20">
       <c r="A20" s="4"/>
       <c r="B20" s="5"/>
-      <c r="C20" s="4"/>
+      <c r="C20" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D20" s="4"/>
       <c r="E20" s="4"/>
       <c r="F20" s="5">
@@ -2884,7 +2930,9 @@
     <row r="21">
       <c r="A21" s="4"/>
       <c r="B21" s="5"/>
-      <c r="C21" s="4"/>
+      <c r="C21" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D21" s="4"/>
       <c r="E21" s="4"/>
       <c r="F21" s="5">
@@ -2919,7 +2967,9 @@
     <row r="22">
       <c r="A22" s="4"/>
       <c r="B22" s="5"/>
-      <c r="C22" s="4"/>
+      <c r="C22" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
       <c r="F22" s="4">
@@ -2954,7 +3004,9 @@
     <row r="23">
       <c r="A23" s="4"/>
       <c r="B23" s="5"/>
-      <c r="C23" s="4"/>
+      <c r="C23" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D23" s="4"/>
       <c r="E23" s="4"/>
       <c r="F23" s="5">
@@ -2989,7 +3041,9 @@
     <row r="24">
       <c r="A24" s="4"/>
       <c r="B24" s="5"/>
-      <c r="C24" s="4"/>
+      <c r="C24" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D24" s="4"/>
       <c r="E24" s="4"/>
       <c r="F24" s="5">
@@ -3024,7 +3078,9 @@
     <row r="25">
       <c r="A25" s="4"/>
       <c r="B25" s="5"/>
-      <c r="C25" s="4"/>
+      <c r="C25" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D25" s="4"/>
       <c r="E25" s="4"/>
       <c r="F25" s="4">
@@ -3059,7 +3115,9 @@
     <row r="26">
       <c r="A26" s="4"/>
       <c r="B26" s="5"/>
-      <c r="C26" s="4"/>
+      <c r="C26" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D26" s="4"/>
       <c r="E26" s="4"/>
       <c r="F26" s="5">
@@ -3094,7 +3152,9 @@
     <row r="27">
       <c r="A27" s="4"/>
       <c r="B27" s="5"/>
-      <c r="C27" s="4"/>
+      <c r="C27" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D27" s="4"/>
       <c r="E27" s="4"/>
       <c r="F27" s="4">
@@ -3129,7 +3189,9 @@
     <row r="28">
       <c r="A28" s="4"/>
       <c r="B28" s="5"/>
-      <c r="C28" s="4"/>
+      <c r="C28" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
       <c r="F28" s="5">
@@ -3164,7 +3226,9 @@
     <row r="29">
       <c r="A29" s="4"/>
       <c r="B29" s="5"/>
-      <c r="C29" s="4"/>
+      <c r="C29" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
@@ -3195,7 +3259,9 @@
     <row r="30">
       <c r="A30" s="4"/>
       <c r="B30" s="5"/>
-      <c r="C30" s="4"/>
+      <c r="C30" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
@@ -3226,7 +3292,9 @@
     <row r="31">
       <c r="A31" s="4"/>
       <c r="B31" s="5"/>
-      <c r="C31" s="4"/>
+      <c r="C31" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
       <c r="F31" s="4"/>
@@ -3257,7 +3325,9 @@
     <row r="32">
       <c r="A32" s="4"/>
       <c r="B32" s="5"/>
-      <c r="C32" s="4"/>
+      <c r="C32" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D32" s="4"/>
       <c r="E32" s="4"/>
       <c r="F32" s="4"/>
@@ -3288,7 +3358,9 @@
     <row r="33">
       <c r="A33" s="4"/>
       <c r="B33" s="5"/>
-      <c r="C33" s="4"/>
+      <c r="C33" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D33" s="4"/>
       <c r="E33" s="4"/>
       <c r="F33" s="4"/>
@@ -3319,7 +3391,9 @@
     <row r="34">
       <c r="A34" s="4"/>
       <c r="B34" s="5"/>
-      <c r="C34" s="4"/>
+      <c r="C34" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D34" s="4"/>
       <c r="E34" s="4"/>
       <c r="F34" s="4"/>
@@ -3350,7 +3424,9 @@
     <row r="35">
       <c r="A35" s="4"/>
       <c r="B35" s="5"/>
-      <c r="C35" s="4"/>
+      <c r="C35" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D35" s="4"/>
       <c r="E35" s="4"/>
       <c r="F35" s="4"/>
@@ -3381,7 +3457,9 @@
     <row r="36">
       <c r="A36" s="4"/>
       <c r="B36" s="5"/>
-      <c r="C36" s="4"/>
+      <c r="C36" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
       <c r="F36" s="4"/>
@@ -3412,7 +3490,9 @@
     <row r="37">
       <c r="A37" s="4"/>
       <c r="B37" s="5"/>
-      <c r="C37" s="4"/>
+      <c r="C37" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
       <c r="F37" s="4"/>
@@ -3443,7 +3523,9 @@
     <row r="38">
       <c r="A38" s="4"/>
       <c r="B38" s="5"/>
-      <c r="C38" s="4"/>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
       <c r="F38" s="4"/>
@@ -3474,7 +3556,9 @@
     <row r="39">
       <c r="A39" s="4"/>
       <c r="B39" s="5"/>
-      <c r="C39" s="4"/>
+      <c r="C39" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D39" s="4"/>
       <c r="E39" s="4"/>
       <c r="F39" s="4"/>
@@ -3505,7 +3589,9 @@
     <row r="40">
       <c r="A40" s="4"/>
       <c r="B40" s="5"/>
-      <c r="C40" s="4"/>
+      <c r="C40" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D40" s="4"/>
       <c r="E40" s="4"/>
       <c r="F40" s="4"/>
@@ -3536,7 +3622,9 @@
     <row r="41">
       <c r="A41" s="4"/>
       <c r="B41" s="5"/>
-      <c r="C41" s="4"/>
+      <c r="C41" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D41" s="4"/>
       <c r="E41" s="4"/>
       <c r="F41" s="4"/>
@@ -3567,7 +3655,9 @@
     <row r="42">
       <c r="A42" s="4"/>
       <c r="B42" s="5"/>
-      <c r="C42" s="4"/>
+      <c r="C42" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D42" s="4"/>
       <c r="E42" s="4"/>
       <c r="F42" s="4"/>
@@ -3598,7 +3688,9 @@
     <row r="43">
       <c r="A43" s="4"/>
       <c r="B43" s="5"/>
-      <c r="C43" s="4"/>
+      <c r="C43" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D43" s="4"/>
       <c r="E43" s="4"/>
       <c r="F43" s="4"/>
@@ -3629,7 +3721,9 @@
     <row r="44">
       <c r="A44" s="4"/>
       <c r="B44" s="5"/>
-      <c r="C44" s="4"/>
+      <c r="C44" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D44" s="4"/>
       <c r="E44" s="4"/>
       <c r="F44" s="4"/>
@@ -3660,7 +3754,9 @@
     <row r="45">
       <c r="A45" s="4"/>
       <c r="B45" s="5"/>
-      <c r="C45" s="4"/>
+      <c r="C45" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D45" s="4"/>
       <c r="E45" s="4"/>
       <c r="F45" s="4"/>
@@ -3691,7 +3787,9 @@
     <row r="46">
       <c r="A46" s="4"/>
       <c r="B46" s="5"/>
-      <c r="C46" s="4"/>
+      <c r="C46" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D46" s="4"/>
       <c r="E46" s="4"/>
       <c r="F46" s="4"/>
@@ -3722,7 +3820,9 @@
     <row r="47">
       <c r="A47" s="4"/>
       <c r="B47" s="5"/>
-      <c r="C47" s="4"/>
+      <c r="C47" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D47" s="4"/>
       <c r="E47" s="4"/>
       <c r="F47" s="4"/>
@@ -3753,7 +3853,9 @@
     <row r="48">
       <c r="A48" s="4"/>
       <c r="B48" s="5"/>
-      <c r="C48" s="4"/>
+      <c r="C48" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D48" s="4"/>
       <c r="E48" s="4"/>
       <c r="F48" s="4"/>
@@ -3784,7 +3886,9 @@
     <row r="49">
       <c r="A49" s="4"/>
       <c r="B49" s="5"/>
-      <c r="C49" s="4"/>
+      <c r="C49" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D49" s="4"/>
       <c r="E49" s="4"/>
       <c r="F49" s="4"/>
@@ -3815,7 +3919,9 @@
     <row r="50">
       <c r="A50" s="4"/>
       <c r="B50" s="5"/>
-      <c r="C50" s="4"/>
+      <c r="C50" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4"/>
       <c r="F50" s="4"/>
@@ -3846,7 +3952,9 @@
     <row r="51">
       <c r="A51" s="4"/>
       <c r="B51" s="5"/>
-      <c r="C51" s="4"/>
+      <c r="C51" s="4" t="s">
+        <v>20</v>
+      </c>
       <c r="D51" s="4"/>
       <c r="E51" s="4"/>
       <c r="F51" s="4"/>
@@ -35721,48 +35829,48 @@
       <c r="L2" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="M2" s="12" t="s">
+      <c r="M2" s="13" t="s">
         <v>179</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="E3" s="13" t="b">
+      <c r="E3" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="13" t="b">
+      <c r="F3" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H3" s="13" t="b">
+      <c r="H3" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>184</v>
       </c>
-      <c r="M3" s="13" t="s">
+      <c r="M3" s="12" t="s">
         <v>185</v>
       </c>
     </row>
@@ -35808,43 +35916,43 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>191</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="C5" s="13" t="s">
+      <c r="C5" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="D5" s="12" t="s">
         <v>193</v>
       </c>
-      <c r="E5" s="13" t="b">
+      <c r="E5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="13" t="b">
+      <c r="F5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H5" s="13" t="b">
+      <c r="H5" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="13" t="s">
+      <c r="I5" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="K5" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="L5" s="12" t="s">
         <v>194</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="M5" s="12" t="s">
         <v>195</v>
       </c>
     </row>
@@ -35885,45 +35993,45 @@
       <c r="L6" s="12" t="s">
         <v>199</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="13" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>201</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="12" t="s">
         <v>202</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D7" s="13" t="s">
+      <c r="D7" s="12" t="s">
         <v>203</v>
       </c>
-      <c r="E7" s="13" t="b">
+      <c r="E7" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="13" t="b">
+      <c r="F7" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H7" s="13" t="b">
+      <c r="H7" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="12" t="s">
         <v>204</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="J7" s="12" t="s">
         <v>205</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="K7" s="12" t="s">
         <v>206</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="L7" s="12" t="s">
         <v>207</v>
       </c>
       <c r="M7" s="13" t="s">
@@ -35967,45 +36075,45 @@
       <c r="L8" s="12" t="s">
         <v>215</v>
       </c>
-      <c r="M8" s="12" t="s">
+      <c r="M8" s="13" t="s">
         <v>216</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="C9" s="13" t="s">
+      <c r="C9" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="E9" s="13" t="b">
+      <c r="E9" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="13" t="b">
+      <c r="F9" s="12" t="b">
         <v>1</v>
       </c>
-      <c r="G9" s="13" t="s">
+      <c r="G9" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H9" s="13" t="b">
+      <c r="H9" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="13" t="s">
+      <c r="I9" s="12" t="s">
         <v>220</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="J9" s="12" t="s">
         <v>221</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="K9" s="12" t="s">
         <v>222</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="L9" s="12" t="s">
         <v>223</v>
       </c>
       <c r="M9" s="13" t="s">
@@ -36035,7 +36143,7 @@
         <v>183</v>
       </c>
       <c r="H10" s="12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" s="12" t="s">
         <v>228</v>
@@ -36049,45 +36157,45 @@
       <c r="L10" s="12" t="s">
         <v>231</v>
       </c>
-      <c r="M10" s="12" t="s">
+      <c r="M10" s="13" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>233</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="12" t="s">
         <v>234</v>
       </c>
-      <c r="C11" s="13" t="s">
+      <c r="C11" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="D11" s="13" t="s">
+      <c r="D11" s="12" t="s">
         <v>235</v>
       </c>
-      <c r="E11" s="13" t="b">
+      <c r="E11" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="b">
+      <c r="F11" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="13" t="s">
+      <c r="G11" s="12" t="s">
         <v>183</v>
       </c>
-      <c r="H11" s="13" t="b">
+      <c r="H11" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="13" t="s">
+      <c r="I11" s="12" t="s">
         <v>236</v>
       </c>
-      <c r="J11" s="13" t="s">
+      <c r="J11" s="12" t="s">
         <v>237</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="K11" s="12" t="s">
         <v>238</v>
       </c>
-      <c r="L11" s="13" t="s">
+      <c r="L11" s="12" t="s">
         <v>239</v>
       </c>
       <c r="M11" s="13" t="s">
@@ -36131,239 +36239,589 @@
       <c r="L12" s="12" t="s">
         <v>247</v>
       </c>
-      <c r="M12" s="12" t="s">
+      <c r="M12" s="13" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
+      <c r="I13" s="12"/>
+      <c r="J13" s="12"/>
+      <c r="K13" s="12"/>
+      <c r="L13" s="12"/>
+      <c r="M13" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="B13" s="13" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" s="12"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12"/>
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12"/>
+      <c r="J14" s="12"/>
+      <c r="K14" s="12"/>
+      <c r="L14" s="12"/>
+      <c r="M14" s="13" t="s">
         <v>250</v>
       </c>
-      <c r="C13" s="13" t="s">
+    </row>
+    <row r="15">
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="I15" s="12"/>
+      <c r="J15" s="12"/>
+      <c r="K15" s="12"/>
+      <c r="L15" s="12"/>
+      <c r="M15" s="13" t="s">
         <v>251</v>
       </c>
-      <c r="D13" s="13" t="s">
+    </row>
+    <row r="16">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="I16" s="12"/>
+      <c r="J16" s="12"/>
+      <c r="K16" s="12"/>
+      <c r="L16" s="12"/>
+      <c r="M16" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="E13" s="13" t="b">
+    </row>
+    <row r="17">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="I17" s="12"/>
+      <c r="J17" s="12"/>
+      <c r="K17" s="12"/>
+      <c r="L17" s="12"/>
+      <c r="M17" s="13" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="13" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="13" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="12"/>
+      <c r="B32" s="12"/>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="12"/>
+      <c r="B33" s="12"/>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="12"/>
+      <c r="B34" s="12"/>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="12"/>
+      <c r="B35" s="12"/>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="12"/>
+      <c r="B36" s="12"/>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D37" s="12" t="s">
+        <v>259</v>
+      </c>
+      <c r="E37" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F13" s="13" t="b">
+      <c r="F37" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G13" s="13">
+      <c r="G37" s="12">
         <v>1.0</v>
       </c>
-      <c r="H13" s="13" t="b">
+      <c r="H37" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="J13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="K13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>253</v>
-      </c>
-      <c r="M13" s="13" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="E14" s="12" t="b">
+      <c r="I37" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="L37" s="12" t="s">
+        <v>260</v>
+      </c>
+      <c r="M37" s="12" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="12" t="s">
+        <v>262</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>263</v>
+      </c>
+      <c r="C38" s="12" t="s">
+        <v>258</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>264</v>
+      </c>
+      <c r="E38" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F14" s="12" t="b">
+      <c r="F38" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G14" s="12">
+      <c r="G38" s="12">
         <v>1.0</v>
       </c>
-      <c r="H14" s="12" t="b">
+      <c r="H38" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I14" s="12" t="s">
+      <c r="I38" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="J38" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="K38" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="L38" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="M38" s="12" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="12" t="s">
+        <v>267</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>268</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="J14" s="12" t="s">
+      <c r="D39" s="12" t="s">
+        <v>269</v>
+      </c>
+      <c r="E39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H39" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="L39" s="12" t="s">
+        <v>270</v>
+      </c>
+      <c r="M39" s="12" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="C40" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="K14" s="12" t="s">
+      <c r="D40" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="E40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="F40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="G40" s="12">
+        <v>1.0</v>
+      </c>
+      <c r="H40" s="12" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="J40" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="K40" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="L40" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="M40" s="12" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="12" t="s">
+        <v>277</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>278</v>
+      </c>
+      <c r="C41" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="L14" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="M14" s="12" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>260</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>261</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="E15" s="13" t="b">
+      <c r="D41" s="12" t="s">
+        <v>279</v>
+      </c>
+      <c r="E41" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="F15" s="13" t="b">
+      <c r="F41" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="G15" s="13">
+      <c r="G41" s="12">
         <v>1.0</v>
       </c>
-      <c r="H15" s="13" t="b">
+      <c r="H41" s="12" t="b">
         <v>0</v>
       </c>
-      <c r="I15" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="J15" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>263</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="E16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="F16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="G16" s="12">
-        <v>1.0</v>
-      </c>
-      <c r="H16" s="12" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="K16" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="L16" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="M16" s="12" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>270</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>271</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>251</v>
-      </c>
-      <c r="D17" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="E17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" s="13">
-        <v>1.0</v>
-      </c>
-      <c r="H17" s="13" t="b">
-        <v>0</v>
-      </c>
-      <c r="I17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="L17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="M17" s="13" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
-    <row r="33" ht="15.75" customHeight="1"/>
-    <row r="34" ht="15.75" customHeight="1"/>
-    <row r="35" ht="15.75" customHeight="1"/>
-    <row r="36" ht="15.75" customHeight="1"/>
-    <row r="37" ht="15.75" customHeight="1"/>
-    <row r="38" ht="15.75" customHeight="1"/>
-    <row r="39" ht="15.75" customHeight="1"/>
-    <row r="40" ht="15.75" customHeight="1"/>
-    <row r="41" ht="15.75" customHeight="1"/>
-    <row r="42" ht="15.75" customHeight="1"/>
-    <row r="43" ht="15.75" customHeight="1"/>
-    <row r="44" ht="15.75" customHeight="1"/>
+      <c r="I41" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="J41" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="L41" s="12" t="s">
+        <v>280</v>
+      </c>
+      <c r="M41" s="12" t="s">
+        <v>281</v>
+      </c>
+    </row>
     <row r="45" ht="15.75" customHeight="1"/>
     <row r="46" ht="15.75" customHeight="1"/>
     <row r="47" ht="15.75" customHeight="1"/>
@@ -37320,6 +37778,30 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
+    <row r="1001" ht="15.75" customHeight="1"/>
+    <row r="1002" ht="15.75" customHeight="1"/>
+    <row r="1003" ht="15.75" customHeight="1"/>
+    <row r="1004" ht="15.75" customHeight="1"/>
+    <row r="1005" ht="15.75" customHeight="1"/>
+    <row r="1006" ht="15.75" customHeight="1"/>
+    <row r="1007" ht="15.75" customHeight="1"/>
+    <row r="1008" ht="15.75" customHeight="1"/>
+    <row r="1009" ht="15.75" customHeight="1"/>
+    <row r="1010" ht="15.75" customHeight="1"/>
+    <row r="1011" ht="15.75" customHeight="1"/>
+    <row r="1012" ht="15.75" customHeight="1"/>
+    <row r="1013" ht="15.75" customHeight="1"/>
+    <row r="1014" ht="15.75" customHeight="1"/>
+    <row r="1015" ht="15.75" customHeight="1"/>
+    <row r="1016" ht="15.75" customHeight="1"/>
+    <row r="1017" ht="15.75" customHeight="1"/>
+    <row r="1018" ht="15.75" customHeight="1"/>
+    <row r="1019" ht="15.75" customHeight="1"/>
+    <row r="1020" ht="15.75" customHeight="1"/>
+    <row r="1021" ht="15.75" customHeight="1"/>
+    <row r="1022" ht="15.75" customHeight="1"/>
+    <row r="1023" ht="15.75" customHeight="1"/>
+    <row r="1024" ht="15.75" customHeight="1"/>
   </sheetData>
   <printOptions/>
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
@@ -37344,143 +37826,143 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D1" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>277</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>278</v>
+      <c r="C1" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>284</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>279</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>281</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="F2" s="12" t="s">
-        <v>283</v>
+      <c r="A2" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>286</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D2" s="17" t="s">
+        <v>288</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="F2" s="16" t="s">
+        <v>290</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>284</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>282</v>
-      </c>
-      <c r="F3" s="13" t="s">
-        <v>286</v>
+      <c r="A3" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="B3" s="18" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>292</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>289</v>
+      </c>
+      <c r="F3" s="18" t="s">
+        <v>293</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>294</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>287</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="D4" s="16" t="s">
+        <v>295</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="C5" s="18" t="s">
         <v>287</v>
       </c>
-      <c r="C4" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>288</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="F4" s="12" t="s">
+      <c r="D5" s="18" t="s">
+        <v>298</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="E6" s="16" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>290</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>291</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>294</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>280</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>295</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>282</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>296</v>
+      <c r="F6" s="16" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>280</v>
-      </c>
-      <c r="D7" s="13" t="s">
+      <c r="A7" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>304</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="E7" s="13" t="s">
-        <v>292</v>
-      </c>
-      <c r="F7" s="13" t="s">
-        <v>298</v>
+      <c r="E7" s="18" t="s">
+        <v>299</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -38490,579 +38972,579 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>299</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>301</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>302</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>303</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>304</v>
-      </c>
-      <c r="G1" s="11" t="s">
-        <v>305</v>
-      </c>
-      <c r="H1" s="11" t="s">
+      <c r="A1" s="14" t="s">
         <v>306</v>
       </c>
-      <c r="I1" s="11" t="s">
+      <c r="B1" s="14" t="s">
         <v>307</v>
       </c>
-      <c r="J1" s="11" t="s">
-        <v>278</v>
+      <c r="C1" s="14" t="s">
+        <v>308</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>309</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>310</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>311</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>312</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>313</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>314</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>285</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12">
+      <c r="A2" s="16">
         <v>1.0</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="16">
         <v>18.0</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="16">
         <v>1.0</v>
       </c>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12">
+      <c r="D2" s="16"/>
+      <c r="E2" s="16">
         <v>1.0</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J2" s="12"/>
+      <c r="F2" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="H2" s="16"/>
+      <c r="I2" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J2" s="16"/>
     </row>
     <row r="3">
-      <c r="A3" s="13">
+      <c r="A3" s="18">
         <v>2.0</v>
       </c>
-      <c r="B3" s="13">
+      <c r="B3" s="18">
         <v>18.0</v>
       </c>
-      <c r="C3" s="13">
+      <c r="C3" s="18">
         <v>1.0</v>
       </c>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13">
+      <c r="D3" s="18"/>
+      <c r="E3" s="18">
         <v>1.0</v>
       </c>
-      <c r="F3" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="G3" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13" t="s">
-        <v>311</v>
-      </c>
-      <c r="J3" s="13"/>
+      <c r="F3" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18" t="s">
+        <v>318</v>
+      </c>
+      <c r="J3" s="18"/>
     </row>
     <row r="4">
-      <c r="A4" s="12">
+      <c r="A4" s="16">
         <v>3.0</v>
       </c>
-      <c r="B4" s="12">
+      <c r="B4" s="16">
         <v>18.0</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="16">
         <v>1.0</v>
       </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16">
         <v>1.0</v>
       </c>
-      <c r="F4" s="12" t="s">
-        <v>308</v>
-      </c>
-      <c r="G4" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="12" t="s">
-        <v>312</v>
-      </c>
-      <c r="J4" s="12"/>
+      <c r="F4" s="16" t="s">
+        <v>315</v>
+      </c>
+      <c r="G4" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16" t="s">
+        <v>319</v>
+      </c>
+      <c r="J4" s="16"/>
     </row>
     <row r="5">
-      <c r="A5" s="13">
+      <c r="A5" s="18">
         <v>4.0</v>
       </c>
-      <c r="B5" s="13">
+      <c r="B5" s="18">
         <v>23.0</v>
       </c>
-      <c r="C5" s="13">
+      <c r="C5" s="18">
         <v>1.0</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13">
+      <c r="D5" s="18"/>
+      <c r="E5" s="18">
         <v>1.0</v>
       </c>
-      <c r="F5" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="G5" s="13" t="s">
-        <v>309</v>
-      </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13" t="s">
-        <v>313</v>
-      </c>
-      <c r="J5" s="13"/>
+      <c r="F5" s="18" t="s">
+        <v>315</v>
+      </c>
+      <c r="G5" s="18" t="s">
+        <v>316</v>
+      </c>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="J5" s="18"/>
     </row>
     <row r="6">
-      <c r="A6" s="12">
+      <c r="A6" s="16">
         <v>5.0</v>
       </c>
-      <c r="B6" s="12">
+      <c r="B6" s="16">
         <v>31.0</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="16">
         <v>1.0</v>
       </c>
-      <c r="D6" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="D6" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E6" s="16">
         <v>1.0</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>315</v>
-      </c>
-      <c r="G6" s="12" t="s">
-        <v>309</v>
-      </c>
-      <c r="H6" s="12">
+      <c r="F6" s="16" t="s">
+        <v>322</v>
+      </c>
+      <c r="G6" s="16" t="s">
+        <v>316</v>
+      </c>
+      <c r="H6" s="16">
         <v>1.0</v>
       </c>
-      <c r="I6" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="18">
+        <v>180.0</v>
+      </c>
+      <c r="C7" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="18" t="s">
+        <v>325</v>
+      </c>
+      <c r="G7" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18" t="s">
         <v>317</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="13">
-        <v>180.0</v>
-      </c>
-      <c r="C7" s="13">
+      <c r="J7" s="18"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="16">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="16">
+        <v>220.0</v>
+      </c>
+      <c r="C8" s="16">
         <v>2.0</v>
       </c>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16">
         <v>2.0</v>
       </c>
-      <c r="F7" s="13" t="s">
-        <v>318</v>
-      </c>
-      <c r="G7" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J7" s="13"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="12">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="12">
-        <v>220.0</v>
-      </c>
-      <c r="C8" s="12">
+      <c r="F8" s="16" t="s">
+        <v>327</v>
+      </c>
+      <c r="G8" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="18">
+        <v>270.0</v>
+      </c>
+      <c r="C9" s="18">
         <v>2.0</v>
       </c>
-      <c r="D8" s="12"/>
-      <c r="E8" s="12">
+      <c r="D9" s="18"/>
+      <c r="E9" s="18">
         <v>2.0</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>320</v>
-      </c>
-      <c r="G8" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="H8" s="12"/>
-      <c r="I8" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J8" s="12"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="13">
+      <c r="F9" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="G9" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J9" s="18"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="16">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="16">
+        <v>340.0</v>
+      </c>
+      <c r="C10" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>329</v>
+      </c>
+      <c r="G10" s="16" t="s">
+        <v>326</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="18">
+        <v>600.0</v>
+      </c>
+      <c r="C11" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="E11" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="G11" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="H11" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="J11" s="18" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="16">
+        <v>450.0</v>
+      </c>
+      <c r="C12" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="G12" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="18">
+        <v>450.0</v>
+      </c>
+      <c r="C13" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="G13" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J13" s="18"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="16">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="16">
+        <v>450.0</v>
+      </c>
+      <c r="C14" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="G14" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="18">
+        <v>585.0</v>
+      </c>
+      <c r="C15" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="G15" s="18" t="s">
+        <v>229</v>
+      </c>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J15" s="18"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="16">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="16">
+        <v>765.0</v>
+      </c>
+      <c r="C16" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>321</v>
+      </c>
+      <c r="E16" s="16">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>333</v>
+      </c>
+      <c r="G16" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="H16" s="16">
+        <v>3.0</v>
+      </c>
+      <c r="I16" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="J16" s="16" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="18">
+        <v>4050.0</v>
+      </c>
+      <c r="C17" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="G17" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J17" s="18"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="16">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="16">
+        <v>4050.0</v>
+      </c>
+      <c r="C18" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16">
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>334</v>
+      </c>
+      <c r="G18" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="H18" s="16"/>
+      <c r="I18" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J18" s="16"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="18">
+        <v>4050.0</v>
+      </c>
+      <c r="C19" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>334</v>
+      </c>
+      <c r="G19" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18" t="s">
+        <v>317</v>
+      </c>
+      <c r="J19" s="18"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="16">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="16">
+        <v>5265.0</v>
+      </c>
+      <c r="C20" s="16">
+        <v>4.0</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16">
+        <v>15.0</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>336</v>
+      </c>
+      <c r="G20" s="16" t="s">
+        <v>335</v>
+      </c>
+      <c r="H20" s="16"/>
+      <c r="I20" s="16" t="s">
+        <v>317</v>
+      </c>
+      <c r="J20" s="16"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="18">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="18">
+        <v>6885.0</v>
+      </c>
+      <c r="C21" s="18">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="E21" s="18">
+        <v>15.0</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>337</v>
+      </c>
+      <c r="G21" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="H21" s="18">
         <v>8.0</v>
       </c>
-      <c r="B9" s="13">
-        <v>270.0</v>
-      </c>
-      <c r="C9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>321</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J9" s="13"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="12">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="12">
-        <v>340.0</v>
-      </c>
-      <c r="C10" s="12">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="12"/>
-      <c r="E10" s="12">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>322</v>
-      </c>
-      <c r="G10" s="12" t="s">
-        <v>319</v>
-      </c>
-      <c r="H10" s="12"/>
-      <c r="I10" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J10" s="12"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="13">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="13">
-        <v>600.0</v>
-      </c>
-      <c r="C11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="13" t="s">
+      <c r="I21" s="18" t="s">
         <v>323</v>
       </c>
-      <c r="G11" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="H11" s="13">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="J11" s="13" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="12">
-        <v>450.0</v>
-      </c>
-      <c r="C12" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="D12" s="12"/>
-      <c r="E12" s="12">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="12" t="s">
+      <c r="J21" s="18" t="s">
         <v>324</v>
-      </c>
-      <c r="G12" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H12" s="12"/>
-      <c r="I12" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J12" s="12"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="13">
-        <v>450.0</v>
-      </c>
-      <c r="C13" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>324</v>
-      </c>
-      <c r="G13" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J13" s="13"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="12">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="12">
-        <v>450.0</v>
-      </c>
-      <c r="C14" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12">
-        <v>5.0</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>324</v>
-      </c>
-      <c r="G14" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J14" s="12"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="13">
-        <v>585.0</v>
-      </c>
-      <c r="C15" s="13">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="G15" s="13" t="s">
-        <v>229</v>
-      </c>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J15" s="13"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="12">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="12">
-        <v>765.0</v>
-      </c>
-      <c r="C16" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>314</v>
-      </c>
-      <c r="E16" s="12">
-        <v>5.0</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="H16" s="12">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="12" t="s">
-        <v>316</v>
-      </c>
-      <c r="J16" s="12" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="13">
-        <v>4050.0</v>
-      </c>
-      <c r="C17" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13">
-        <v>15.0</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J17" s="13"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="12">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="12">
-        <v>4050.0</v>
-      </c>
-      <c r="C18" s="12">
-        <v>4.0</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12">
-        <v>15.0</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>327</v>
-      </c>
-      <c r="G18" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J18" s="12"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="13">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="13">
-        <v>4050.0</v>
-      </c>
-      <c r="C19" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="G19" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="J19" s="13"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="12">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="12">
-        <v>5265.0</v>
-      </c>
-      <c r="C20" s="12">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12">
-        <v>15.0</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>329</v>
-      </c>
-      <c r="G20" s="12" t="s">
-        <v>328</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="12" t="s">
-        <v>310</v>
-      </c>
-      <c r="J20" s="12"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="13">
-        <v>6885.0</v>
-      </c>
-      <c r="C21" s="13">
-        <v>4.0</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>314</v>
-      </c>
-      <c r="E21" s="13">
-        <v>15.0</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="G21" s="13" t="s">
-        <v>328</v>
-      </c>
-      <c r="H21" s="13">
-        <v>8.0</v>
-      </c>
-      <c r="I21" s="13" t="s">
-        <v>316</v>
-      </c>
-      <c r="J21" s="13" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -40067,122 +40549,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>332</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>333</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>334</v>
+      <c r="A1" s="14" t="s">
+        <v>338</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>339</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>340</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
-        <v>335</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>337</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>338</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>339</v>
+      <c r="A2" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="B2" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>344</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>345</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
-        <v>340</v>
-      </c>
-      <c r="B3" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="E3" s="13" t="s">
+      <c r="A3" s="18" t="s">
+        <v>347</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>343</v>
       </c>
+      <c r="C3" s="18" t="s">
+        <v>348</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>349</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>350</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
-        <v>344</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>345</v>
-      </c>
-      <c r="D4" s="12" t="s">
-        <v>346</v>
-      </c>
-      <c r="E4" s="12" t="s">
-        <v>347</v>
+      <c r="A4" s="16" t="s">
+        <v>351</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>352</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>353</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
-        <v>348</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" s="13" t="s">
-        <v>349</v>
-      </c>
-      <c r="D5" s="13" t="s">
-        <v>350</v>
-      </c>
-      <c r="E5" s="13" t="s">
-        <v>351</v>
+      <c r="A5" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B5" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="E5" s="18" t="s">
+        <v>358</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="s">
-        <v>352</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>336</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>353</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>354</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>355</v>
+      <c r="A6" s="16" t="s">
+        <v>359</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>343</v>
+      </c>
+      <c r="C6" s="16" t="s">
+        <v>360</v>
+      </c>
+      <c r="D6" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>362</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>356</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>359</v>
+      <c r="A7" s="18" t="s">
+        <v>363</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>343</v>
+      </c>
+      <c r="C7" s="18" t="s">
+        <v>364</v>
+      </c>
+      <c r="D7" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>366</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -41190,857 +41672,857 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="B1" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>362</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>364</v>
+      <c r="A1" s="14" t="s">
+        <v>367</v>
+      </c>
+      <c r="B1" s="14" t="s">
+        <v>368</v>
+      </c>
+      <c r="C1" s="14" t="s">
+        <v>282</v>
+      </c>
+      <c r="D1" s="14" t="s">
+        <v>369</v>
+      </c>
+      <c r="E1" s="14" t="s">
+        <v>370</v>
+      </c>
+      <c r="F1" s="14" t="s">
+        <v>371</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="E2" s="12" t="s">
-        <v>368</v>
-      </c>
-      <c r="F2" s="12" t="s">
+      <c r="B2" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>373</v>
+      </c>
+      <c r="D2" s="16" t="s">
+        <v>374</v>
+      </c>
+      <c r="E2" s="16" t="s">
+        <v>375</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C3" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="D3" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="E3" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="F3" s="13" t="s">
+      <c r="B3" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C3" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D3" s="18" t="s">
+        <v>377</v>
+      </c>
+      <c r="E3" s="18" t="s">
+        <v>378</v>
+      </c>
+      <c r="F3" s="18" t="s">
         <v>181</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="B4" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>369</v>
-      </c>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12" t="s">
+      <c r="B4" s="16" t="s">
         <v>372</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="C4" s="16" t="s">
+        <v>376</v>
+      </c>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="16" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="B5" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C5" s="13" t="s">
+      <c r="B5" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C5" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="F5" s="18" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="s">
+        <v>198</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C6" s="16" t="s">
         <v>373</v>
       </c>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="F5" s="13" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="12" t="s">
-        <v>198</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>375</v>
-      </c>
-      <c r="E6" s="12" t="s">
+      <c r="D6" s="16" t="s">
+        <v>382</v>
+      </c>
+      <c r="E6" s="16" t="s">
+        <v>383</v>
+      </c>
+      <c r="F6" s="16" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="s">
+        <v>203</v>
+      </c>
+      <c r="B7" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C7" s="18" t="s">
         <v>376</v>
       </c>
-      <c r="F6" s="12" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C7" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="D7" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="E7" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="D7" s="18" t="s">
+        <v>384</v>
+      </c>
+      <c r="E7" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="F7" s="18" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="16" t="s">
         <v>211</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>380</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>381</v>
-      </c>
-      <c r="F8" s="12" t="s">
+      <c r="B8" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>387</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>388</v>
+      </c>
+      <c r="F8" s="16" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="B9" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C9" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="D9" s="13" t="s">
-        <v>380</v>
-      </c>
-      <c r="E9" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="F9" s="13" t="s">
+      <c r="B9" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="D9" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="E9" s="18" t="s">
+        <v>389</v>
+      </c>
+      <c r="F9" s="18" t="s">
         <v>218</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="16" t="s">
         <v>227</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>384</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="F10" s="12" t="s">
+      <c r="B10" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>391</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>392</v>
+      </c>
+      <c r="F10" s="16" t="s">
         <v>226</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="18" t="s">
         <v>235</v>
       </c>
-      <c r="B11" s="13" t="s">
-        <v>365</v>
-      </c>
-      <c r="C11" s="13" t="s">
+      <c r="B11" s="18" t="s">
+        <v>372</v>
+      </c>
+      <c r="C11" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="D11" s="18" t="s">
+        <v>394</v>
+      </c>
+      <c r="E11" s="18" t="s">
+        <v>395</v>
+      </c>
+      <c r="F11" s="18" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" s="16" t="s">
+        <v>372</v>
+      </c>
+      <c r="C12" s="16" t="s">
+        <v>396</v>
+      </c>
+      <c r="D12" s="16" t="s">
+        <v>397</v>
+      </c>
+      <c r="E12" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="F12" s="16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="s">
+        <v>259</v>
+      </c>
+      <c r="B13" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="C13" s="18" t="s">
+        <v>400</v>
+      </c>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18" t="s">
+        <v>401</v>
+      </c>
+      <c r="F13" s="18" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="B14" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>402</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>403</v>
+      </c>
+      <c r="E14" s="16" t="s">
+        <v>404</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="C15" s="18" t="s">
+        <v>405</v>
+      </c>
+      <c r="D15" s="18" t="s">
+        <v>406</v>
+      </c>
+      <c r="E15" s="18" t="s">
+        <v>407</v>
+      </c>
+      <c r="F15" s="18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="s">
+        <v>274</v>
+      </c>
+      <c r="B16" s="16" t="s">
+        <v>399</v>
+      </c>
+      <c r="C16" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="D11" s="13" t="s">
-        <v>387</v>
-      </c>
-      <c r="E11" s="13" t="s">
-        <v>388</v>
-      </c>
-      <c r="F11" s="13" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>365</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="D12" s="12" t="s">
+      <c r="D16" s="16" t="s">
+        <v>408</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>409</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="s">
+        <v>279</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>399</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>393</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>410</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>280</v>
+      </c>
+      <c r="F17" s="18" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>411</v>
+      </c>
+      <c r="D18" s="16"/>
+      <c r="E18" s="16" t="s">
+        <v>412</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>414</v>
+      </c>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18" t="s">
+        <v>415</v>
+      </c>
+      <c r="F19" s="18" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="B20" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>417</v>
+      </c>
+      <c r="D20" s="16"/>
+      <c r="E20" s="16" t="s">
+        <v>418</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="D21" s="18"/>
+      <c r="E21" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="F21" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="B22" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="16" t="s">
+        <v>421</v>
+      </c>
+      <c r="D22" s="16" t="s">
+        <v>422</v>
+      </c>
+      <c r="E22" s="16" t="s">
+        <v>423</v>
+      </c>
+      <c r="F22" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="18" t="s">
+        <v>57</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="18" t="s">
+        <v>424</v>
+      </c>
+      <c r="D23" s="18" t="s">
+        <v>425</v>
+      </c>
+      <c r="E23" s="18" t="s">
+        <v>426</v>
+      </c>
+      <c r="F23" s="18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>428</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16" t="s">
+        <v>429</v>
+      </c>
+      <c r="F24" s="16" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="18" t="s">
+        <v>430</v>
+      </c>
+      <c r="D25" s="18"/>
+      <c r="E25" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="F25" s="18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>432</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>434</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="18" t="s">
+        <v>45</v>
+      </c>
+      <c r="B27" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="D27" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="E27" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="F27" s="18" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="16" t="s">
+        <v>437</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="16" t="s">
+        <v>438</v>
+      </c>
+      <c r="D28" s="16" t="s">
+        <v>439</v>
+      </c>
+      <c r="E28" s="16" t="s">
+        <v>440</v>
+      </c>
+      <c r="F28" s="16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="18" t="s">
+        <v>442</v>
+      </c>
+      <c r="B29" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="18" t="s">
         <v>390</v>
       </c>
-      <c r="E12" s="12" t="s">
-        <v>391</v>
-      </c>
-      <c r="F12" s="12" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="s">
-        <v>252</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>393</v>
-      </c>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13" t="s">
-        <v>394</v>
-      </c>
-      <c r="F13" s="13" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>395</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>396</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>397</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="s">
-        <v>262</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>398</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>399</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>400</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>392</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>401</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>402</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="s">
-        <v>272</v>
-      </c>
-      <c r="B17" s="13" t="s">
-        <v>392</v>
-      </c>
-      <c r="C17" s="13" t="s">
+      <c r="D29" s="18"/>
+      <c r="E29" s="18" t="s">
+        <v>443</v>
+      </c>
+      <c r="F29" s="18" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="16" t="s">
         <v>386</v>
       </c>
-      <c r="D17" s="13" t="s">
-        <v>403</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>273</v>
-      </c>
-      <c r="F17" s="13" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>404</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="F18" s="12" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>407</v>
-      </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13" t="s">
-        <v>408</v>
-      </c>
-      <c r="F19" s="13" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>410</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12" t="s">
-        <v>411</v>
-      </c>
-      <c r="F20" s="12" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>412</v>
-      </c>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13" t="s">
-        <v>413</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>414</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>415</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>416</v>
-      </c>
-      <c r="F22" s="12" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B23" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>417</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>418</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>419</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12" t="s">
-        <v>422</v>
-      </c>
-      <c r="F24" s="12" t="s">
+      <c r="D30" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>445</v>
+      </c>
+      <c r="F30" s="16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="B31" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18" t="s">
+        <v>446</v>
+      </c>
+      <c r="F31" s="18" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="16" t="s">
+        <v>78</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>390</v>
+      </c>
+      <c r="D32" s="16"/>
+      <c r="E32" s="16" t="s">
+        <v>447</v>
+      </c>
+      <c r="F32" s="16" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>423</v>
-      </c>
-      <c r="D25" s="13"/>
-      <c r="E25" s="13" t="s">
-        <v>424</v>
-      </c>
-      <c r="F25" s="13" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>448</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>444</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="F33" s="18" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="16" t="s">
+        <v>451</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="16" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>425</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>426</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>427</v>
-      </c>
-      <c r="F26" s="12" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>428</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>429</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="12" t="s">
-        <v>430</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>431</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>432</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>433</v>
-      </c>
-      <c r="F28" s="12" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="13" t="s">
-        <v>435</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13" t="s">
-        <v>436</v>
-      </c>
-      <c r="F29" s="13" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B30" s="12" t="s">
+      <c r="D34" s="16"/>
+      <c r="E34" s="16" t="s">
+        <v>452</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="18" t="s">
+        <v>115</v>
+      </c>
+      <c r="B35" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D30" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="E30" s="12" t="s">
-        <v>438</v>
-      </c>
-      <c r="F30" s="12" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="B31" s="13" t="s">
+      <c r="C35" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="D35" s="18" t="s">
+        <v>455</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>456</v>
+      </c>
+      <c r="F35" s="18" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="16" t="s">
+        <v>458</v>
+      </c>
+      <c r="B36" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="13" t="s">
-        <v>383</v>
-      </c>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13" t="s">
-        <v>439</v>
-      </c>
-      <c r="F31" s="13" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="12" t="s">
+      <c r="C36" s="16" t="s">
+        <v>459</v>
+      </c>
+      <c r="D36" s="16" t="s">
+        <v>444</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>460</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="B37" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="12" t="s">
-        <v>383</v>
-      </c>
-      <c r="D32" s="12"/>
-      <c r="E32" s="12" t="s">
-        <v>440</v>
-      </c>
-      <c r="F32" s="12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="B33" s="13" t="s">
+      <c r="C37" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="D37" s="18" t="s">
+        <v>463</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>464</v>
+      </c>
+      <c r="F37" s="18" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="16" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="13" t="s">
-        <v>441</v>
-      </c>
-      <c r="D33" s="13" t="s">
-        <v>437</v>
-      </c>
-      <c r="E33" s="13" t="s">
-        <v>442</v>
-      </c>
-      <c r="F33" s="13" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="12" t="s">
-        <v>444</v>
-      </c>
-      <c r="B34" s="12" t="s">
+      <c r="C38" s="16" t="s">
+        <v>466</v>
+      </c>
+      <c r="D38" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="E38" s="16" t="s">
+        <v>468</v>
+      </c>
+      <c r="F38" s="16" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="18" t="s">
+        <v>99</v>
+      </c>
+      <c r="B39" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D34" s="12"/>
-      <c r="E34" s="12" t="s">
-        <v>445</v>
-      </c>
-      <c r="F34" s="12" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B35" s="13" t="s">
+      <c r="C39" s="18" t="s">
+        <v>470</v>
+      </c>
+      <c r="D39" s="18" t="s">
+        <v>471</v>
+      </c>
+      <c r="E39" s="18" t="s">
+        <v>472</v>
+      </c>
+      <c r="F39" s="18" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="B40" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="13" t="s">
-        <v>447</v>
-      </c>
-      <c r="D35" s="13" t="s">
-        <v>448</v>
-      </c>
-      <c r="E35" s="13" t="s">
-        <v>449</v>
-      </c>
-      <c r="F35" s="13" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="12" t="s">
-        <v>451</v>
-      </c>
-      <c r="B36" s="12" t="s">
+      <c r="C40" s="16" t="s">
+        <v>474</v>
+      </c>
+      <c r="D40" s="16" t="s">
+        <v>475</v>
+      </c>
+      <c r="E40" s="16" t="s">
+        <v>476</v>
+      </c>
+      <c r="F40" s="16" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B41" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="12" t="s">
-        <v>452</v>
-      </c>
-      <c r="D36" s="12" t="s">
-        <v>437</v>
-      </c>
-      <c r="E36" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="F36" s="12" t="s">
+      <c r="C41" s="18" t="s">
+        <v>477</v>
+      </c>
+      <c r="D41" s="18" t="s">
+        <v>478</v>
+      </c>
+      <c r="E41" s="18" t="s">
+        <v>479</v>
+      </c>
+      <c r="F41" s="18" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B42" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="16" t="s">
+        <v>386</v>
+      </c>
+      <c r="D42" s="16" t="s">
+        <v>478</v>
+      </c>
+      <c r="E42" s="16" t="s">
+        <v>481</v>
+      </c>
+      <c r="F42" s="16" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B43" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="18" t="s">
+        <v>483</v>
+      </c>
+      <c r="D43" s="18" t="s">
+        <v>484</v>
+      </c>
+      <c r="E43" s="18" t="s">
+        <v>485</v>
+      </c>
+      <c r="F43" s="18" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="16" t="s">
+        <v>135</v>
+      </c>
+      <c r="B44" s="16" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="16" t="s">
         <v>454</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="13" t="s">
-        <v>123</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="13" t="s">
-        <v>455</v>
-      </c>
-      <c r="D37" s="13" t="s">
-        <v>456</v>
-      </c>
-      <c r="E37" s="13" t="s">
-        <v>457</v>
-      </c>
-      <c r="F37" s="13" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="12" t="s">
-        <v>127</v>
-      </c>
-      <c r="B38" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="D38" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="E38" s="12" t="s">
-        <v>461</v>
-      </c>
-      <c r="F38" s="12" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="13" t="s">
-        <v>463</v>
-      </c>
-      <c r="D39" s="13" t="s">
-        <v>464</v>
-      </c>
-      <c r="E39" s="13" t="s">
-        <v>465</v>
-      </c>
-      <c r="F39" s="13" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="12" t="s">
-        <v>111</v>
-      </c>
-      <c r="B40" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="D40" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="E40" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="F40" s="12" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="13" t="s">
-        <v>470</v>
-      </c>
-      <c r="D41" s="13" t="s">
-        <v>471</v>
-      </c>
-      <c r="E41" s="13" t="s">
-        <v>472</v>
-      </c>
-      <c r="F41" s="13" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="B42" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D42" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>474</v>
-      </c>
-      <c r="F42" s="12" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="13" t="s">
-        <v>476</v>
-      </c>
-      <c r="D43" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="E43" s="13" t="s">
+      <c r="D44" s="16" t="s">
         <v>478</v>
       </c>
-      <c r="F43" s="13" t="s">
-        <v>479</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>447</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>471</v>
-      </c>
-      <c r="E44" s="12" t="s">
-        <v>480</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>481</v>
+      <c r="E44" s="16" t="s">
+        <v>487</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>488</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="501">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="500">
   <si>
     <t>id</t>
   </si>
@@ -574,9 +574,6 @@
   </si>
   <si>
     <t>G4効果値</t>
-  </si>
-  <si>
-    <t>説明・備考</t>
   </si>
   <si>
     <t>w_fire</t>
@@ -35017,21 +35014,21 @@
         <v>181</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>182</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="14" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="14" t="s">
+      <c r="C2" s="14" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="D2" s="14" t="s">
         <v>185</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>186</v>
       </c>
       <c r="E2" s="14" t="b">
         <v>1</v>
@@ -35046,19 +35043,19 @@
         <v>1</v>
       </c>
       <c r="I2" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="J2" s="14" t="s">
         <v>187</v>
       </c>
-      <c r="J2" s="14" t="s">
+      <c r="K2" s="14" t="s">
         <v>188</v>
       </c>
-      <c r="K2" s="14" t="s">
+      <c r="L2" s="14" t="s">
         <v>189</v>
       </c>
-      <c r="L2" s="14" t="s">
+      <c r="M2" s="15" t="s">
         <v>190</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>191</v>
       </c>
       <c r="N2" s="16">
         <v>50.0</v>
@@ -35066,16 +35063,16 @@
     </row>
     <row r="3">
       <c r="A3" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B3" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="C3" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D3" s="14" t="s">
         <v>193</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>194</v>
       </c>
       <c r="E3" s="14" t="b">
         <v>0</v>
@@ -35084,39 +35081,39 @@
         <v>1</v>
       </c>
       <c r="G3" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H3" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I3" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="K3" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="L3" s="14" t="s">
+        <v>195</v>
+      </c>
+      <c r="M3" s="14" t="s">
         <v>196</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="B4" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C4" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" s="14" t="s">
         <v>199</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>200</v>
       </c>
       <c r="E4" s="14" t="b">
         <v>0</v>
@@ -35125,39 +35122,39 @@
         <v>1</v>
       </c>
       <c r="G4" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H4" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I4" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="J4" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="K4" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="L4" s="14" t="s">
+        <v>200</v>
+      </c>
+      <c r="M4" s="14" t="s">
         <v>201</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>201</v>
-      </c>
-      <c r="M4" s="14" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="14" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>203</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="C5" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D5" s="14" t="s">
         <v>204</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>205</v>
       </c>
       <c r="E5" s="14" t="b">
         <v>0</v>
@@ -35166,39 +35163,39 @@
         <v>0</v>
       </c>
       <c r="G5" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H5" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I5" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="J5" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="K5" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="L5" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="M5" s="14" t="s">
         <v>206</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="14" t="s">
+        <v>207</v>
+      </c>
+      <c r="B6" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="C6" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D6" s="14" t="s">
         <v>209</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>210</v>
       </c>
       <c r="E6" s="14" t="b">
         <v>1</v>
@@ -35207,39 +35204,39 @@
         <v>0</v>
       </c>
       <c r="G6" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H6" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I6" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="J6" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="K6" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="L6" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="M6" s="15" t="s">
         <v>211</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="C7" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D7" s="14" t="s">
         <v>214</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>215</v>
       </c>
       <c r="E7" s="14" t="b">
         <v>0</v>
@@ -35248,39 +35245,39 @@
         <v>1</v>
       </c>
       <c r="G7" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H7" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I7" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" s="14" t="s">
         <v>216</v>
       </c>
-      <c r="J7" s="14" t="s">
+      <c r="K7" s="14" t="s">
         <v>217</v>
       </c>
-      <c r="K7" s="14" t="s">
+      <c r="L7" s="14" t="s">
         <v>218</v>
       </c>
-      <c r="L7" s="14" t="s">
+      <c r="M7" s="15" t="s">
         <v>219</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="14" t="s">
+        <v>220</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>221</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="C8" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D8" s="14" t="s">
         <v>222</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>223</v>
       </c>
       <c r="E8" s="14" t="b">
         <v>0</v>
@@ -35289,39 +35286,39 @@
         <v>0</v>
       </c>
       <c r="G8" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H8" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I8" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="J8" s="14" t="s">
         <v>224</v>
       </c>
-      <c r="J8" s="14" t="s">
+      <c r="K8" s="14" t="s">
         <v>225</v>
       </c>
-      <c r="K8" s="14" t="s">
+      <c r="L8" s="14" t="s">
         <v>226</v>
       </c>
-      <c r="L8" s="14" t="s">
+      <c r="M8" s="15" t="s">
         <v>227</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B9" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="C9" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D9" s="14" t="s">
         <v>230</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>231</v>
       </c>
       <c r="E9" s="14" t="b">
         <v>0</v>
@@ -35330,39 +35327,39 @@
         <v>1</v>
       </c>
       <c r="G9" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H9" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I9" s="14" t="s">
+        <v>231</v>
+      </c>
+      <c r="J9" s="14" t="s">
         <v>232</v>
       </c>
-      <c r="J9" s="14" t="s">
+      <c r="K9" s="14" t="s">
         <v>233</v>
       </c>
-      <c r="K9" s="14" t="s">
+      <c r="L9" s="14" t="s">
         <v>234</v>
       </c>
-      <c r="L9" s="14" t="s">
+      <c r="M9" s="15" t="s">
         <v>235</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="s">
+        <v>236</v>
+      </c>
+      <c r="B10" s="14" t="s">
         <v>237</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="C10" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D10" s="14" t="s">
         <v>238</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>239</v>
       </c>
       <c r="E10" s="14" t="b">
         <v>0</v>
@@ -35371,39 +35368,39 @@
         <v>0</v>
       </c>
       <c r="G10" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H10" s="14" t="b">
         <v>1</v>
       </c>
       <c r="I10" s="14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="J10" s="14" t="s">
+      <c r="K10" s="14" t="s">
         <v>241</v>
       </c>
-      <c r="K10" s="14" t="s">
+      <c r="L10" s="14" t="s">
         <v>242</v>
       </c>
-      <c r="L10" s="14" t="s">
+      <c r="M10" s="15" t="s">
         <v>243</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="s">
+        <v>244</v>
+      </c>
+      <c r="B11" s="14" t="s">
         <v>245</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="C11" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D11" s="14" t="s">
         <v>246</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>247</v>
       </c>
       <c r="E11" s="14" t="b">
         <v>0</v>
@@ -35412,39 +35409,39 @@
         <v>0</v>
       </c>
       <c r="G11" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H11" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I11" s="14" t="s">
+        <v>247</v>
+      </c>
+      <c r="J11" s="14" t="s">
         <v>248</v>
       </c>
-      <c r="J11" s="14" t="s">
+      <c r="K11" s="14" t="s">
         <v>249</v>
       </c>
-      <c r="K11" s="14" t="s">
+      <c r="L11" s="14" t="s">
         <v>250</v>
       </c>
-      <c r="L11" s="14" t="s">
+      <c r="M11" s="15" t="s">
         <v>251</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="s">
+        <v>252</v>
+      </c>
+      <c r="B12" s="14" t="s">
         <v>253</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="C12" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="D12" s="14" t="s">
         <v>254</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>255</v>
       </c>
       <c r="E12" s="14" t="b">
         <v>0</v>
@@ -35453,25 +35450,25 @@
         <v>0</v>
       </c>
       <c r="G12" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H12" s="14" t="b">
         <v>0</v>
       </c>
       <c r="I12" s="14" t="s">
+        <v>255</v>
+      </c>
+      <c r="J12" s="14" t="s">
         <v>256</v>
       </c>
-      <c r="J12" s="14" t="s">
+      <c r="K12" s="14" t="s">
         <v>257</v>
       </c>
-      <c r="K12" s="14" t="s">
+      <c r="L12" s="14" t="s">
         <v>258</v>
       </c>
-      <c r="L12" s="14" t="s">
+      <c r="M12" s="15" t="s">
         <v>259</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="13">
@@ -35488,7 +35485,7 @@
       <c r="K13" s="14"/>
       <c r="L13" s="14"/>
       <c r="M13" s="15" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14">
@@ -35505,7 +35502,7 @@
       <c r="K14" s="14"/>
       <c r="L14" s="14"/>
       <c r="M14" s="15" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="15">
@@ -35522,7 +35519,7 @@
       <c r="K15" s="14"/>
       <c r="L15" s="14"/>
       <c r="M15" s="15" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="16">
@@ -35539,7 +35536,7 @@
       <c r="K16" s="14"/>
       <c r="L16" s="14"/>
       <c r="M16" s="15" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="17">
@@ -35556,7 +35553,7 @@
       <c r="K17" s="14"/>
       <c r="L17" s="14"/>
       <c r="M17" s="15" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="18">
@@ -35573,7 +35570,7 @@
       <c r="K18" s="14"/>
       <c r="L18" s="14"/>
       <c r="M18" s="15" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="19">
@@ -35590,7 +35587,7 @@
       <c r="K19" s="14"/>
       <c r="L19" s="14"/>
       <c r="M19" s="15" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20">
@@ -35850,16 +35847,16 @@
     </row>
     <row r="37">
       <c r="A37" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B37" s="14" t="s">
         <v>268</v>
       </c>
-      <c r="B37" s="14" t="s">
+      <c r="C37" s="14" t="s">
         <v>269</v>
       </c>
-      <c r="C37" s="14" t="s">
+      <c r="D37" s="14" t="s">
         <v>270</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>271</v>
       </c>
       <c r="E37" s="14" t="b">
         <v>0</v>
@@ -35874,33 +35871,33 @@
         <v>0</v>
       </c>
       <c r="I37" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="J37" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="K37" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="L37" s="14" t="s">
+        <v>271</v>
+      </c>
+      <c r="M37" s="14" t="s">
         <v>272</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>272</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="14" t="s">
+        <v>273</v>
+      </c>
+      <c r="B38" s="14" t="s">
         <v>274</v>
       </c>
-      <c r="B38" s="14" t="s">
+      <c r="C38" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D38" s="14" t="s">
         <v>275</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>276</v>
       </c>
       <c r="E38" s="14" t="b">
         <v>0</v>
@@ -35915,33 +35912,33 @@
         <v>0</v>
       </c>
       <c r="I38" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="J38" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="K38" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="L38" s="14" t="s">
+        <v>276</v>
+      </c>
+      <c r="M38" s="14" t="s">
         <v>277</v>
-      </c>
-      <c r="J38" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>277</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="14" t="s">
+        <v>278</v>
+      </c>
+      <c r="B39" s="14" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="14" t="s">
+      <c r="C39" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D39" s="14" t="s">
         <v>280</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>281</v>
       </c>
       <c r="E39" s="14" t="b">
         <v>0</v>
@@ -35956,33 +35953,33 @@
         <v>0</v>
       </c>
       <c r="I39" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="J39" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="K39" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="L39" s="14" t="s">
+        <v>281</v>
+      </c>
+      <c r="M39" s="14" t="s">
         <v>282</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>282</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="14" t="s">
+        <v>283</v>
+      </c>
+      <c r="B40" s="14" t="s">
         <v>284</v>
       </c>
-      <c r="B40" s="14" t="s">
+      <c r="C40" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D40" s="14" t="s">
         <v>285</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>286</v>
       </c>
       <c r="E40" s="14" t="b">
         <v>0</v>
@@ -35997,33 +35994,33 @@
         <v>0</v>
       </c>
       <c r="I40" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="J40" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="K40" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="L40" s="14" t="s">
+        <v>286</v>
+      </c>
+      <c r="M40" s="14" t="s">
         <v>287</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>287</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="14" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" s="14" t="s">
         <v>289</v>
       </c>
-      <c r="B41" s="14" t="s">
+      <c r="C41" s="14" t="s">
+        <v>269</v>
+      </c>
+      <c r="D41" s="14" t="s">
         <v>290</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>291</v>
       </c>
       <c r="E41" s="14" t="b">
         <v>0</v>
@@ -36038,19 +36035,19 @@
         <v>0</v>
       </c>
       <c r="I41" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="J41" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="K41" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="L41" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="M41" s="14" t="s">
         <v>292</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>292</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>293</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -37064,136 +37061,136 @@
         <v>1</v>
       </c>
       <c r="C1" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="D1" s="18" t="s">
+      <c r="E1" s="17" t="s">
         <v>295</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>296</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>297</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>298</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="20" t="s">
         <v>299</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="E2" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>301</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>302</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="22" t="s">
         <v>303</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>303</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D3" s="22" t="s">
+      <c r="E3" s="21" t="s">
+        <v>300</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>304</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>301</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="D4" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F4" s="19" t="s">
         <v>307</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D5" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="F5" s="21" t="s">
         <v>311</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>312</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>298</v>
+      </c>
+      <c r="D6" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="F6" s="19" t="s">
         <v>314</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>301</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>310</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>316</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>196</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>311</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -38204,34 +38201,34 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>317</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>318</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>322</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="G1" s="17" t="s">
         <v>323</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="H1" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="I1" s="17" t="s">
         <v>325</v>
       </c>
-      <c r="I1" s="17" t="s">
-        <v>326</v>
-      </c>
       <c r="J1" s="17" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="2">
@@ -38249,14 +38246,14 @@
         <v>1.0</v>
       </c>
       <c r="F2" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G2" s="19" t="s">
         <v>327</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>328</v>
       </c>
       <c r="H2" s="19"/>
       <c r="I2" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J2" s="19"/>
     </row>
@@ -38275,14 +38272,14 @@
         <v>1.0</v>
       </c>
       <c r="F3" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="G3" s="21" t="s">
         <v>327</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>328</v>
       </c>
       <c r="H3" s="21"/>
       <c r="I3" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J3" s="21"/>
     </row>
@@ -38301,14 +38298,14 @@
         <v>1.0</v>
       </c>
       <c r="F4" s="19" t="s">
+        <v>326</v>
+      </c>
+      <c r="G4" s="19" t="s">
         <v>327</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>328</v>
       </c>
       <c r="H4" s="19"/>
       <c r="I4" s="19" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J4" s="19"/>
     </row>
@@ -38327,14 +38324,14 @@
         <v>1.0</v>
       </c>
       <c r="F5" s="21" t="s">
+        <v>326</v>
+      </c>
+      <c r="G5" s="21" t="s">
         <v>327</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>328</v>
       </c>
       <c r="H5" s="21"/>
       <c r="I5" s="21" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="J5" s="21"/>
     </row>
@@ -38349,25 +38346,25 @@
         <v>1.0</v>
       </c>
       <c r="D6" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E6" s="19">
         <v>1.0</v>
       </c>
       <c r="F6" s="19" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G6" s="19" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H6" s="19">
         <v>1.0</v>
       </c>
       <c r="I6" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J6" s="19" t="s">
         <v>335</v>
-      </c>
-      <c r="J6" s="19" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="7">
@@ -38385,14 +38382,14 @@
         <v>2.0</v>
       </c>
       <c r="F7" s="21" t="s">
+        <v>336</v>
+      </c>
+      <c r="G7" s="21" t="s">
         <v>337</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>338</v>
       </c>
       <c r="H7" s="21"/>
       <c r="I7" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J7" s="21"/>
     </row>
@@ -38411,14 +38408,14 @@
         <v>2.0</v>
       </c>
       <c r="F8" s="19" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H8" s="19"/>
       <c r="I8" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J8" s="19"/>
     </row>
@@ -38437,14 +38434,14 @@
         <v>2.0</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G9" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H9" s="21"/>
       <c r="I9" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J9" s="21"/>
     </row>
@@ -38463,14 +38460,14 @@
         <v>2.0</v>
       </c>
       <c r="F10" s="19" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H10" s="19"/>
       <c r="I10" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J10" s="19"/>
     </row>
@@ -38485,25 +38482,25 @@
         <v>2.0</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E11" s="21">
         <v>2.0</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="G11" s="21" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H11" s="21">
         <v>2.0</v>
       </c>
       <c r="I11" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="J11" s="21" t="s">
         <v>335</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="12">
@@ -38521,14 +38518,14 @@
         <v>5.0</v>
       </c>
       <c r="F12" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G12" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H12" s="19"/>
       <c r="I12" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J12" s="19"/>
     </row>
@@ -38547,14 +38544,14 @@
         <v>5.0</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G13" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H13" s="21"/>
       <c r="I13" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J13" s="21"/>
     </row>
@@ -38573,14 +38570,14 @@
         <v>5.0</v>
       </c>
       <c r="F14" s="19" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="G14" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H14" s="19"/>
       <c r="I14" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J14" s="19"/>
     </row>
@@ -38599,14 +38596,14 @@
         <v>5.0</v>
       </c>
       <c r="F15" s="21" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G15" s="21" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H15" s="21"/>
       <c r="I15" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J15" s="21"/>
     </row>
@@ -38621,25 +38618,25 @@
         <v>3.0</v>
       </c>
       <c r="D16" s="19" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E16" s="19">
         <v>5.0</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H16" s="19">
         <v>3.0</v>
       </c>
       <c r="I16" s="19" t="s">
+        <v>334</v>
+      </c>
+      <c r="J16" s="19" t="s">
         <v>335</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="17">
@@ -38657,14 +38654,14 @@
         <v>15.0</v>
       </c>
       <c r="F17" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="G17" s="21" t="s">
         <v>346</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>347</v>
       </c>
       <c r="H17" s="21"/>
       <c r="I17" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J17" s="21"/>
     </row>
@@ -38683,14 +38680,14 @@
         <v>15.0</v>
       </c>
       <c r="F18" s="19" t="s">
+        <v>345</v>
+      </c>
+      <c r="G18" s="19" t="s">
         <v>346</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>347</v>
       </c>
       <c r="H18" s="19"/>
       <c r="I18" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J18" s="19"/>
     </row>
@@ -38709,14 +38706,14 @@
         <v>15.0</v>
       </c>
       <c r="F19" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="G19" s="21" t="s">
         <v>346</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>347</v>
       </c>
       <c r="H19" s="21"/>
       <c r="I19" s="21" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J19" s="21"/>
     </row>
@@ -38735,14 +38732,14 @@
         <v>15.0</v>
       </c>
       <c r="F20" s="19" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G20" s="19" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H20" s="19"/>
       <c r="I20" s="19" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="J20" s="19"/>
     </row>
@@ -38757,25 +38754,25 @@
         <v>4.0</v>
       </c>
       <c r="D21" s="21" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="E21" s="21">
         <v>15.0</v>
       </c>
       <c r="F21" s="21" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G21" s="21" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H21" s="21">
         <v>8.0</v>
       </c>
       <c r="I21" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="J21" s="21" t="s">
         <v>335</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>336</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -39781,121 +39778,121 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>349</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>350</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
+        <v>294</v>
+      </c>
+      <c r="E1" s="17" t="s">
         <v>352</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>353</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="s">
+        <v>353</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>354</v>
       </c>
-      <c r="B2" s="19" t="s">
+      <c r="C2" s="19" t="s">
         <v>355</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>356</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>357</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>359</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="D3" s="21" t="s">
         <v>360</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="21" t="s">
         <v>361</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="s">
+        <v>362</v>
+      </c>
+      <c r="B4" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C4" s="19" t="s">
         <v>363</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="C4" s="19" t="s">
+      <c r="D4" s="19" t="s">
         <v>364</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="E4" s="19" t="s">
         <v>365</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="s">
+        <v>366</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>367</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="D5" s="21" t="s">
         <v>368</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="E5" s="21" t="s">
         <v>369</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>370</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
+        <v>370</v>
+      </c>
+      <c r="B6" s="19" t="s">
+        <v>354</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>371</v>
       </c>
-      <c r="B6" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="C6" s="19" t="s">
+      <c r="D6" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="E6" s="19" t="s">
         <v>373</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="s">
+        <v>374</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>354</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>375</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>355</v>
-      </c>
-      <c r="C7" s="21" t="s">
+      <c r="D7" s="21" t="s">
         <v>376</v>
       </c>
-      <c r="D7" s="21" t="s">
+      <c r="E7" s="21" t="s">
         <v>377</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>378</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -40904,336 +40901,336 @@
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
       <c r="A1" s="17" t="s">
+        <v>378</v>
+      </c>
+      <c r="B1" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="C1" s="17" t="s">
+        <v>293</v>
+      </c>
+      <c r="D1" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="E1" s="17" t="s">
+      <c r="F1" s="17" t="s">
         <v>382</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>383</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="19" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>386</v>
       </c>
-      <c r="E2" s="19" t="s">
-        <v>387</v>
-      </c>
       <c r="F2" s="19" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="21" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C3" s="21" t="s">
+        <v>387</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>388</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="E3" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>390</v>
-      </c>
       <c r="F3" s="21" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C4" s="19" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="19" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="21" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="D5" s="21"/>
       <c r="E5" s="21" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="B6" s="19" t="s">
+        <v>383</v>
+      </c>
+      <c r="C6" s="19" t="s">
         <v>384</v>
       </c>
-      <c r="C6" s="19" t="s">
-        <v>385</v>
-      </c>
       <c r="D6" s="19" t="s">
+        <v>393</v>
+      </c>
+      <c r="E6" s="19" t="s">
         <v>394</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>395</v>
-      </c>
       <c r="F6" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="21" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D7" s="21" t="s">
+        <v>395</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>396</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>397</v>
-      </c>
       <c r="F7" s="21" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="B8" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C8" s="19" t="s">
+        <v>397</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="D8" s="19" t="s">
+      <c r="E8" s="19" t="s">
         <v>399</v>
       </c>
-      <c r="E8" s="19" t="s">
-        <v>400</v>
-      </c>
       <c r="F8" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="21" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E9" s="21" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="F9" s="21" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="B10" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C10" s="19" t="s">
+        <v>401</v>
+      </c>
+      <c r="D10" s="19" t="s">
         <v>402</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="E10" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="E10" s="19" t="s">
-        <v>404</v>
-      </c>
       <c r="F10" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="21" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B11" s="21" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C11" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D11" s="21" t="s">
         <v>405</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="E11" s="21" t="s">
         <v>406</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>407</v>
-      </c>
       <c r="F11" s="21" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="C12" s="19" t="s">
+        <v>407</v>
+      </c>
+      <c r="D12" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="D12" s="19" t="s">
+      <c r="E12" s="19" t="s">
         <v>409</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>410</v>
-      </c>
       <c r="F12" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="21" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="B13" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="C13" s="21" t="s">
         <v>411</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>412</v>
       </c>
       <c r="D13" s="21"/>
       <c r="E13" s="21" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F13" s="21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B14" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C14" s="19" t="s">
+        <v>413</v>
+      </c>
+      <c r="D14" s="19" t="s">
         <v>414</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="E14" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="E14" s="19" t="s">
-        <v>416</v>
-      </c>
       <c r="F14" s="19" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="21" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C15" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="D15" s="21" t="s">
         <v>417</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>418</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>419</v>
-      </c>
       <c r="F15" s="21" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B16" s="19" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D16" s="19" t="s">
+        <v>419</v>
+      </c>
+      <c r="E16" s="19" t="s">
         <v>420</v>
       </c>
-      <c r="E16" s="19" t="s">
-        <v>421</v>
-      </c>
       <c r="F16" s="19" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="21" t="s">
+        <v>290</v>
+      </c>
+      <c r="B17" s="21" t="s">
+        <v>410</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>404</v>
+      </c>
+      <c r="D17" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="E17" s="21" t="s">
         <v>291</v>
       </c>
-      <c r="B17" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="C17" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="D17" s="21" t="s">
-        <v>422</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>292</v>
-      </c>
       <c r="F17" s="21" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
     </row>
     <row r="18">
@@ -41244,14 +41241,14 @@
         <v>3</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="19" t="s">
+        <v>423</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>424</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="19">
@@ -41262,14 +41259,14 @@
         <v>3</v>
       </c>
       <c r="C19" s="21" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D19" s="21"/>
       <c r="E19" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="F19" s="21" t="s">
         <v>427</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="20">
@@ -41280,11 +41277,11 @@
         <v>3</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="19" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="F20" s="19" t="s">
         <v>42</v>
@@ -41298,11 +41295,11 @@
         <v>3</v>
       </c>
       <c r="C21" s="21" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="D21" s="21"/>
       <c r="E21" s="21" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="F21" s="21" t="s">
         <v>48</v>
@@ -41316,13 +41313,13 @@
         <v>3</v>
       </c>
       <c r="C22" s="19" t="s">
+        <v>432</v>
+      </c>
+      <c r="D22" s="19" t="s">
         <v>433</v>
       </c>
-      <c r="D22" s="19" t="s">
+      <c r="E22" s="19" t="s">
         <v>434</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>435</v>
       </c>
       <c r="F22" s="19" t="s">
         <v>56</v>
@@ -41336,13 +41333,13 @@
         <v>3</v>
       </c>
       <c r="C23" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>436</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="E23" s="21" t="s">
         <v>437</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>438</v>
       </c>
       <c r="F23" s="21" t="s">
         <v>63</v>
@@ -41356,11 +41353,11 @@
         <v>3</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F24" s="19" t="s">
         <v>81</v>
@@ -41374,14 +41371,14 @@
         <v>3</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="D25" s="21"/>
       <c r="E25" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="F25" s="21" t="s">
         <v>442</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>443</v>
       </c>
     </row>
     <row r="26" ht="15.75" customHeight="1">
@@ -41392,13 +41389,13 @@
         <v>3</v>
       </c>
       <c r="C26" s="19" t="s">
+        <v>443</v>
+      </c>
+      <c r="D26" s="19" t="s">
         <v>444</v>
       </c>
-      <c r="D26" s="19" t="s">
+      <c r="E26" s="19" t="s">
         <v>445</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>446</v>
       </c>
       <c r="F26" s="19" t="s">
         <v>88</v>
@@ -41412,13 +41409,13 @@
         <v>12</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D27" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="E27" s="21" t="s">
         <v>447</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>448</v>
       </c>
       <c r="F27" s="21" t="s">
         <v>48</v>
@@ -41426,40 +41423,40 @@
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="19" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="B28" s="19" t="s">
         <v>12</v>
       </c>
       <c r="C28" s="19" t="s">
+        <v>449</v>
+      </c>
+      <c r="D28" s="19" t="s">
         <v>450</v>
       </c>
-      <c r="D28" s="19" t="s">
+      <c r="E28" s="19" t="s">
         <v>451</v>
       </c>
-      <c r="E28" s="19" t="s">
+      <c r="F28" s="19" t="s">
         <v>452</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="21" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B29" s="21" t="s">
         <v>12</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D29" s="21"/>
       <c r="E29" s="21" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="F29" s="21" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="30" ht="15.75" customHeight="1">
@@ -41470,13 +41467,13 @@
         <v>11</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D30" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="E30" s="19" t="s">
         <v>456</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>457</v>
       </c>
       <c r="F30" s="19" t="s">
         <v>23</v>
@@ -41490,11 +41487,11 @@
         <v>11</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D31" s="21"/>
       <c r="E31" s="21" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="F31" s="21" t="s">
         <v>63</v>
@@ -41508,11 +41505,11 @@
         <v>11</v>
       </c>
       <c r="C32" s="19" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="19" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="F32" s="19" t="s">
         <v>81</v>
@@ -41526,34 +41523,34 @@
         <v>11</v>
       </c>
       <c r="C33" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="D33" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="E33" s="21" t="s">
         <v>460</v>
       </c>
-      <c r="D33" s="21" t="s">
-        <v>456</v>
-      </c>
-      <c r="E33" s="21" t="s">
+      <c r="F33" s="21" t="s">
         <v>461</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>462</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="19" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B34" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C34" s="19" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="19" t="s">
+        <v>463</v>
+      </c>
+      <c r="F34" s="19" t="s">
         <v>464</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>465</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
@@ -41564,36 +41561,36 @@
         <v>11</v>
       </c>
       <c r="C35" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="D35" s="21" t="s">
         <v>466</v>
       </c>
-      <c r="D35" s="21" t="s">
+      <c r="E35" s="21" t="s">
         <v>467</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="F35" s="21" t="s">
         <v>468</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>469</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
       <c r="A36" s="19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B36" s="19" t="s">
         <v>11</v>
       </c>
       <c r="C36" s="19" t="s">
+        <v>470</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>455</v>
+      </c>
+      <c r="E36" s="19" t="s">
         <v>471</v>
       </c>
-      <c r="D36" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="E36" s="19" t="s">
+      <c r="F36" s="19" t="s">
         <v>472</v>
-      </c>
-      <c r="F36" s="19" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
@@ -41604,16 +41601,16 @@
         <v>11</v>
       </c>
       <c r="C37" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="D37" s="21" t="s">
         <v>474</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="E37" s="21" t="s">
         <v>475</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="F37" s="21" t="s">
         <v>476</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>477</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1">
@@ -41624,16 +41621,16 @@
         <v>11</v>
       </c>
       <c r="C38" s="19" t="s">
+        <v>477</v>
+      </c>
+      <c r="D38" s="19" t="s">
         <v>478</v>
       </c>
-      <c r="D38" s="19" t="s">
+      <c r="E38" s="19" t="s">
         <v>479</v>
       </c>
-      <c r="E38" s="19" t="s">
+      <c r="F38" s="19" t="s">
         <v>480</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
@@ -41644,16 +41641,16 @@
         <v>11</v>
       </c>
       <c r="C39" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="D39" s="21" t="s">
         <v>482</v>
       </c>
-      <c r="D39" s="21" t="s">
+      <c r="E39" s="21" t="s">
         <v>483</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="F39" s="21" t="s">
         <v>484</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>485</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
@@ -41664,16 +41661,16 @@
         <v>11</v>
       </c>
       <c r="C40" s="19" t="s">
+        <v>485</v>
+      </c>
+      <c r="D40" s="19" t="s">
         <v>486</v>
       </c>
-      <c r="D40" s="19" t="s">
+      <c r="E40" s="19" t="s">
         <v>487</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>488</v>
-      </c>
       <c r="F40" s="19" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
@@ -41684,16 +41681,16 @@
         <v>11</v>
       </c>
       <c r="C41" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="D41" s="21" t="s">
         <v>489</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="E41" s="21" t="s">
         <v>490</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="F41" s="21" t="s">
         <v>491</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>492</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
@@ -41704,16 +41701,16 @@
         <v>11</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E42" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="F42" s="19" t="s">
         <v>493</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
@@ -41724,16 +41721,16 @@
         <v>11</v>
       </c>
       <c r="C43" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="D43" s="21" t="s">
         <v>495</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="E43" s="21" t="s">
         <v>496</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="F43" s="21" t="s">
         <v>497</v>
-      </c>
-      <c r="F43" s="21" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
@@ -41744,16 +41741,16 @@
         <v>11</v>
       </c>
       <c r="C44" s="19" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E44" s="19" t="s">
+        <v>498</v>
+      </c>
+      <c r="F44" s="19" t="s">
         <v>499</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -2041,7 +2041,7 @@
         <v>23</v>
       </c>
       <c r="F2" s="7">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="G2" s="7">
         <v>1.0</v>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -178,8 +178,8 @@
     <t>stone_death</t>
   </si>
   <si>
-    <t>死亡時：すべての味方のHP+Grade*2
-召喚トリガー：戦闘開始時</t>
+    <t>死亡時：すべての味方のHP+(Grade×2
+)　召喚トリガー：戦闘開始時</t>
   </si>
   <si>
     <t>ヘイトを付ける</t>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -2907,12 +2907,8 @@
       </c>
       <c r="D17" s="6"/>
       <c r="E17" s="6"/>
-      <c r="F17" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="G17" s="7">
-        <v>1.0</v>
-      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
       <c r="J17" s="6"/>
@@ -2944,12 +2940,8 @@
       </c>
       <c r="D18" s="6"/>
       <c r="E18" s="6"/>
-      <c r="F18" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="G18" s="7">
-        <v>2.0</v>
-      </c>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
       <c r="J18" s="6"/>
@@ -2981,12 +2973,8 @@
       </c>
       <c r="D19" s="6"/>
       <c r="E19" s="6"/>
-      <c r="F19" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="G19" s="7">
-        <v>1.0</v>
-      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
       <c r="H19" s="6"/>
       <c r="I19" s="6"/>
       <c r="J19" s="6"/>
@@ -3018,12 +3006,8 @@
       </c>
       <c r="D20" s="6"/>
       <c r="E20" s="6"/>
-      <c r="F20" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="G20" s="7">
-        <v>4.0</v>
-      </c>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
       <c r="H20" s="6"/>
       <c r="I20" s="6"/>
       <c r="J20" s="6"/>
@@ -3055,12 +3039,8 @@
       </c>
       <c r="D21" s="6"/>
       <c r="E21" s="6"/>
-      <c r="F21" s="7">
-        <v>12.0</v>
-      </c>
-      <c r="G21" s="7">
-        <v>15.0</v>
-      </c>
+      <c r="F21" s="7"/>
+      <c r="G21" s="7"/>
       <c r="H21" s="6"/>
       <c r="I21" s="6"/>
       <c r="J21" s="6"/>
@@ -3092,12 +3072,8 @@
       </c>
       <c r="D22" s="6"/>
       <c r="E22" s="6"/>
-      <c r="F22" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G22" s="6">
-        <v>0.0</v>
-      </c>
+      <c r="F22" s="6"/>
+      <c r="G22" s="6"/>
       <c r="H22" s="6"/>
       <c r="I22" s="6"/>
       <c r="J22" s="6"/>
@@ -3131,12 +3107,8 @@
       </c>
       <c r="D23" s="6"/>
       <c r="E23" s="6"/>
-      <c r="F23" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0.0</v>
-      </c>
+      <c r="F23" s="7"/>
+      <c r="G23" s="7"/>
       <c r="H23" s="6"/>
       <c r="I23" s="6"/>
       <c r="J23" s="6"/>
@@ -3168,12 +3140,8 @@
       </c>
       <c r="D24" s="6"/>
       <c r="E24" s="6"/>
-      <c r="F24" s="7">
-        <v>1.0</v>
-      </c>
-      <c r="G24" s="7">
-        <v>1.0</v>
-      </c>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
       <c r="H24" s="6"/>
       <c r="I24" s="6"/>
       <c r="J24" s="6"/>
@@ -3205,12 +3173,8 @@
       </c>
       <c r="D25" s="6"/>
       <c r="E25" s="6"/>
-      <c r="F25" s="6">
-        <v>15.0</v>
-      </c>
-      <c r="G25" s="6">
-        <v>15.0</v>
-      </c>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="6"/>
       <c r="J25" s="6"/>
@@ -3242,12 +3206,8 @@
       </c>
       <c r="D26" s="6"/>
       <c r="E26" s="6"/>
-      <c r="F26" s="7">
-        <v>3.0</v>
-      </c>
-      <c r="G26" s="7">
-        <v>5.0</v>
-      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
       <c r="H26" s="6"/>
       <c r="I26" s="6"/>
       <c r="J26" s="6"/>
@@ -3279,12 +3239,8 @@
       </c>
       <c r="D27" s="6"/>
       <c r="E27" s="6"/>
-      <c r="F27" s="6">
-        <v>0.0</v>
-      </c>
-      <c r="G27" s="7">
-        <v>8.0</v>
-      </c>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7"/>
       <c r="H27" s="6"/>
       <c r="I27" s="6"/>
       <c r="J27" s="6"/>
@@ -3316,12 +3272,8 @@
       </c>
       <c r="D28" s="6"/>
       <c r="E28" s="6"/>
-      <c r="F28" s="7">
-        <v>0.0</v>
-      </c>
-      <c r="G28" s="7">
-        <v>1.0</v>
-      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
       <c r="H28" s="6"/>
       <c r="I28" s="6"/>
       <c r="J28" s="6"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="859" uniqueCount="507">
   <si>
     <t>id</t>
   </si>
@@ -349,6 +349,27 @@
   </si>
   <si>
     <t>あなたが杖を使用した時、</t>
+  </si>
+  <si>
+    <t>マナ生成</t>
+  </si>
+  <si>
+    <t>3マナを生成する。</t>
+  </si>
+  <si>
+    <t>攻撃命令</t>
+  </si>
+  <si>
+    <t>3/3の「狼」を1体召喚する。</t>
+  </si>
+  <si>
+    <t>1/1の「鼠」を3体召喚する。</t>
+  </si>
+  <si>
+    <t>次の行動を2回実行する。</t>
+  </si>
+  <si>
+    <t>全てのマナを次のターンに繰り越す。</t>
   </si>
   <si>
     <t>r_needle</t>
@@ -1632,7 +1653,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1664,6 +1685,9 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -2885,7 +2909,9 @@
       <c r="N16" s="6"/>
       <c r="O16" s="6"/>
       <c r="P16" s="6"/>
-      <c r="Q16" s="7"/>
+      <c r="Q16" s="7" t="s">
+        <v>106</v>
+      </c>
       <c r="R16" s="10"/>
       <c r="S16" s="4"/>
       <c r="T16" s="4"/>
@@ -2934,7 +2960,9 @@
     </row>
     <row r="18">
       <c r="A18" s="6"/>
-      <c r="B18" s="7"/>
+      <c r="B18" s="11" t="s">
+        <v>107</v>
+      </c>
       <c r="C18" s="6" t="s">
         <v>21</v>
       </c>
@@ -2951,7 +2979,9 @@
       <c r="N18" s="6"/>
       <c r="O18" s="6"/>
       <c r="P18" s="6"/>
-      <c r="Q18" s="6"/>
+      <c r="Q18" s="7" t="s">
+        <v>108</v>
+      </c>
       <c r="R18" s="10"/>
       <c r="S18" s="4"/>
       <c r="T18" s="4"/>
@@ -2967,7 +2997,9 @@
     </row>
     <row r="19">
       <c r="A19" s="6"/>
-      <c r="B19" s="7"/>
+      <c r="B19" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="C19" s="6" t="s">
         <v>21</v>
       </c>
@@ -2984,7 +3016,9 @@
       <c r="N19" s="6"/>
       <c r="O19" s="6"/>
       <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
+      <c r="Q19" s="7" t="s">
+        <v>110</v>
+      </c>
       <c r="R19" s="10"/>
       <c r="S19" s="4"/>
       <c r="T19" s="4"/>
@@ -3017,7 +3051,9 @@
       <c r="N20" s="6"/>
       <c r="O20" s="6"/>
       <c r="P20" s="6"/>
-      <c r="Q20" s="6"/>
+      <c r="Q20" s="7" t="s">
+        <v>111</v>
+      </c>
       <c r="R20" s="10"/>
       <c r="S20" s="4"/>
       <c r="T20" s="4"/>
@@ -3050,7 +3086,9 @@
       <c r="N21" s="6"/>
       <c r="O21" s="6"/>
       <c r="P21" s="6"/>
-      <c r="Q21" s="6"/>
+      <c r="Q21" s="7" t="s">
+        <v>112</v>
+      </c>
       <c r="R21" s="10"/>
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
@@ -3084,7 +3122,7 @@
       <c r="O22" s="6"/>
       <c r="P22" s="6"/>
       <c r="Q22" s="7" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="R22" s="10"/>
       <c r="S22" s="4"/>
@@ -4058,13 +4096,13 @@
     </row>
     <row r="52">
       <c r="A52" s="6" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B52" s="7" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D52" s="6"/>
       <c r="E52" s="6"/>
@@ -4075,7 +4113,7 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
       <c r="L52" s="9" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="M52" s="6"/>
       <c r="N52" s="6" t="b">
@@ -4084,7 +4122,7 @@
       <c r="O52" s="6"/>
       <c r="P52" s="6"/>
       <c r="Q52" s="6" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="R52" s="10"/>
       <c r="S52" s="4"/>
@@ -4101,13 +4139,13 @@
     </row>
     <row r="53">
       <c r="A53" s="6" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="B53" s="7" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D53" s="6"/>
       <c r="E53" s="6"/>
@@ -4118,7 +4156,7 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="9" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="M53" s="6"/>
       <c r="N53" s="6" t="b">
@@ -4127,7 +4165,7 @@
       <c r="O53" s="6"/>
       <c r="P53" s="6"/>
       <c r="Q53" s="6" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="R53" s="10"/>
       <c r="S53" s="4"/>
@@ -4144,13 +4182,13 @@
     </row>
     <row r="54">
       <c r="A54" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C54" s="6" t="s">
         <v>116</v>
-      </c>
-      <c r="B54" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="C54" s="6" t="s">
-        <v>109</v>
       </c>
       <c r="D54" s="6"/>
       <c r="E54" s="6"/>
@@ -4161,7 +4199,7 @@
       <c r="J54" s="6"/>
       <c r="K54" s="6"/>
       <c r="L54" s="9" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="M54" s="6"/>
       <c r="N54" s="6" t="b">
@@ -4170,7 +4208,7 @@
       <c r="O54" s="6"/>
       <c r="P54" s="6"/>
       <c r="Q54" s="6" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="R54" s="10"/>
       <c r="S54" s="4"/>
@@ -4187,13 +4225,13 @@
     </row>
     <row r="55">
       <c r="A55" s="6" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="B55" s="7" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D55" s="6"/>
       <c r="E55" s="6"/>
@@ -4204,7 +4242,7 @@
       <c r="J55" s="6"/>
       <c r="K55" s="6"/>
       <c r="L55" s="9" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M55" s="6"/>
       <c r="N55" s="6" t="b">
@@ -4213,7 +4251,7 @@
       <c r="O55" s="6"/>
       <c r="P55" s="6"/>
       <c r="Q55" s="6" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="R55" s="10"/>
       <c r="S55" s="4"/>
@@ -4230,13 +4268,13 @@
     </row>
     <row r="56">
       <c r="A56" s="6" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B56" s="7" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D56" s="6"/>
       <c r="E56" s="6"/>
@@ -4247,7 +4285,7 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="9" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="M56" s="6"/>
       <c r="N56" s="6" t="b">
@@ -4256,7 +4294,7 @@
       <c r="O56" s="6"/>
       <c r="P56" s="6"/>
       <c r="Q56" s="7" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="R56" s="10"/>
       <c r="S56" s="4"/>
@@ -4273,13 +4311,13 @@
     </row>
     <row r="57">
       <c r="A57" s="6" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="B57" s="7" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D57" s="6"/>
       <c r="E57" s="6"/>
@@ -4290,7 +4328,7 @@
       <c r="J57" s="6"/>
       <c r="K57" s="6"/>
       <c r="L57" s="9" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="M57" s="6"/>
       <c r="N57" s="6" t="b">
@@ -4299,7 +4337,7 @@
       <c r="O57" s="6"/>
       <c r="P57" s="6"/>
       <c r="Q57" s="6" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="R57" s="10"/>
       <c r="S57" s="4"/>
@@ -4316,13 +4354,13 @@
     </row>
     <row r="58">
       <c r="A58" s="6" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="B58" s="7" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D58" s="6"/>
       <c r="E58" s="6"/>
@@ -4333,7 +4371,7 @@
       <c r="J58" s="6"/>
       <c r="K58" s="6"/>
       <c r="L58" s="9" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="M58" s="6"/>
       <c r="N58" s="6" t="b">
@@ -4342,7 +4380,7 @@
       <c r="O58" s="6"/>
       <c r="P58" s="6"/>
       <c r="Q58" s="6" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="R58" s="10"/>
       <c r="S58" s="4"/>
@@ -4359,13 +4397,13 @@
     </row>
     <row r="59" ht="15.75" customHeight="1">
       <c r="A59" s="6" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="B59" s="7" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D59" s="6"/>
       <c r="E59" s="6"/>
@@ -4376,7 +4414,7 @@
       <c r="J59" s="6"/>
       <c r="K59" s="6"/>
       <c r="L59" s="9" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="M59" s="6"/>
       <c r="N59" s="6" t="b">
@@ -4385,7 +4423,7 @@
       <c r="O59" s="6"/>
       <c r="P59" s="6"/>
       <c r="Q59" s="6" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="R59" s="10"/>
       <c r="S59" s="4"/>
@@ -4402,13 +4440,13 @@
     </row>
     <row r="60">
       <c r="A60" s="7" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="B60" s="7" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D60" s="6"/>
       <c r="E60" s="6"/>
@@ -4418,8 +4456,8 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6"/>
       <c r="K60" s="6"/>
-      <c r="L60" s="11" t="s">
-        <v>142</v>
+      <c r="L60" s="12" t="s">
+        <v>149</v>
       </c>
       <c r="M60" s="6"/>
       <c r="N60" s="6" t="b">
@@ -4430,7 +4468,7 @@
       </c>
       <c r="P60" s="6"/>
       <c r="Q60" s="7" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="R60" s="10"/>
       <c r="S60" s="4"/>
@@ -4447,13 +4485,13 @@
     </row>
     <row r="61">
       <c r="A61" s="6" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B61" s="7" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D61" s="6"/>
       <c r="E61" s="6"/>
@@ -4464,7 +4502,7 @@
       <c r="J61" s="6"/>
       <c r="K61" s="6"/>
       <c r="L61" s="9" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="M61" s="6"/>
       <c r="N61" s="6" t="b">
@@ -4475,7 +4513,7 @@
       </c>
       <c r="P61" s="6"/>
       <c r="Q61" s="7" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="R61" s="10"/>
       <c r="S61" s="4"/>
@@ -4492,13 +4530,13 @@
     </row>
     <row r="62">
       <c r="A62" s="7" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B62" s="7" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D62" s="6"/>
       <c r="E62" s="6"/>
@@ -4509,7 +4547,7 @@
       <c r="J62" s="6"/>
       <c r="K62" s="6"/>
       <c r="L62" s="9" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="M62" s="6"/>
       <c r="N62" s="6" t="b">
@@ -4520,7 +4558,7 @@
       </c>
       <c r="P62" s="6"/>
       <c r="Q62" s="7" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="R62" s="10"/>
       <c r="S62" s="4"/>
@@ -4537,13 +4575,13 @@
     </row>
     <row r="63">
       <c r="A63" s="7" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="B63" s="7" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D63" s="6"/>
       <c r="E63" s="6"/>
@@ -4554,7 +4592,7 @@
       <c r="J63" s="6"/>
       <c r="K63" s="6"/>
       <c r="L63" s="9" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="M63" s="6"/>
       <c r="N63" s="6" t="b">
@@ -4565,7 +4603,7 @@
       </c>
       <c r="P63" s="6"/>
       <c r="Q63" s="7" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="R63" s="10"/>
       <c r="S63" s="4"/>
@@ -4582,13 +4620,13 @@
     </row>
     <row r="64">
       <c r="A64" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B64" s="7" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D64" s="6"/>
       <c r="E64" s="6"/>
@@ -4599,7 +4637,7 @@
       <c r="J64" s="6"/>
       <c r="K64" s="6"/>
       <c r="L64" s="9" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="M64" s="6"/>
       <c r="N64" s="6" t="b">
@@ -4610,7 +4648,7 @@
       </c>
       <c r="P64" s="6"/>
       <c r="Q64" s="7" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="R64" s="10"/>
       <c r="S64" s="4"/>
@@ -4627,13 +4665,13 @@
     </row>
     <row r="65">
       <c r="A65" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B65" s="7" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D65" s="6"/>
       <c r="E65" s="6"/>
@@ -4644,7 +4682,7 @@
       <c r="J65" s="6"/>
       <c r="K65" s="6"/>
       <c r="L65" s="9" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="M65" s="6"/>
       <c r="N65" s="6" t="b">
@@ -4655,7 +4693,7 @@
       </c>
       <c r="P65" s="6"/>
       <c r="Q65" s="7" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="R65" s="10"/>
       <c r="S65" s="4"/>
@@ -4672,13 +4710,13 @@
     </row>
     <row r="66">
       <c r="A66" s="7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B66" s="7" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D66" s="6"/>
       <c r="E66" s="6"/>
@@ -4689,7 +4727,7 @@
       <c r="J66" s="6"/>
       <c r="K66" s="6"/>
       <c r="L66" s="9" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="M66" s="6"/>
       <c r="N66" s="6" t="b">
@@ -4700,7 +4738,7 @@
       </c>
       <c r="P66" s="6"/>
       <c r="Q66" s="7" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="R66" s="10"/>
       <c r="S66" s="4"/>
@@ -4717,13 +4755,13 @@
     </row>
     <row r="67">
       <c r="A67" s="7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B67" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D67" s="6"/>
       <c r="E67" s="6"/>
@@ -4733,8 +4771,8 @@
       <c r="I67" s="6"/>
       <c r="J67" s="6"/>
       <c r="K67" s="6"/>
-      <c r="L67" s="11" t="s">
-        <v>169</v>
+      <c r="L67" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="M67" s="6"/>
       <c r="N67" s="6" t="b">
@@ -4745,7 +4783,7 @@
       </c>
       <c r="P67" s="6"/>
       <c r="Q67" s="7" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="R67" s="10"/>
       <c r="S67" s="4"/>
@@ -4764,7 +4802,7 @@
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="C68" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D68" s="6"/>
       <c r="E68" s="6"/>
@@ -4782,7 +4820,7 @@
       <c r="O68" s="6"/>
       <c r="P68" s="6"/>
       <c r="Q68" s="7" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="R68" s="10"/>
       <c r="S68" s="4"/>
@@ -4801,7 +4839,7 @@
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="C69" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D69" s="6"/>
       <c r="E69" s="6"/>
@@ -4836,7 +4874,7 @@
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="C70" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D70" s="6"/>
       <c r="E70" s="6"/>
@@ -4871,7 +4909,7 @@
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="C71" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D71" s="6"/>
       <c r="E71" s="6"/>
@@ -4906,7 +4944,7 @@
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="C72" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D72" s="6"/>
       <c r="E72" s="6"/>
@@ -4941,7 +4979,7 @@
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="C73" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D73" s="6"/>
       <c r="E73" s="6"/>
@@ -4976,7 +5014,7 @@
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="C74" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D74" s="6"/>
       <c r="E74" s="6"/>
@@ -5011,7 +5049,7 @@
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="C75" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D75" s="6"/>
       <c r="E75" s="6"/>
@@ -5046,7 +5084,7 @@
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="C76" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D76" s="6"/>
       <c r="E76" s="6"/>
@@ -5081,7 +5119,7 @@
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="C77" s="6" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="D77" s="6"/>
       <c r="E77" s="6"/>
@@ -5113,23 +5151,23 @@
       <c r="AC77" s="5"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="12"/>
-      <c r="B78" s="12"/>
-      <c r="C78" s="12"/>
-      <c r="D78" s="12"/>
-      <c r="E78" s="12"/>
-      <c r="F78" s="12"/>
-      <c r="G78" s="12"/>
-      <c r="H78" s="12"/>
-      <c r="I78" s="12"/>
-      <c r="J78" s="12"/>
-      <c r="K78" s="12"/>
-      <c r="L78" s="12"/>
-      <c r="M78" s="12"/>
-      <c r="N78" s="12"/>
-      <c r="O78" s="12"/>
-      <c r="P78" s="12"/>
-      <c r="Q78" s="12"/>
+      <c r="A78" s="13"/>
+      <c r="B78" s="13"/>
+      <c r="C78" s="13"/>
+      <c r="D78" s="13"/>
+      <c r="E78" s="13"/>
+      <c r="F78" s="13"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
+      <c r="I78" s="13"/>
+      <c r="J78" s="13"/>
+      <c r="K78" s="13"/>
+      <c r="L78" s="13"/>
+      <c r="M78" s="13"/>
+      <c r="N78" s="13"/>
+      <c r="O78" s="13"/>
+      <c r="P78" s="13"/>
+      <c r="Q78" s="13"/>
       <c r="R78" s="5"/>
       <c r="S78" s="4"/>
       <c r="T78" s="4"/>
@@ -34929,1077 +34967,1077 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="13" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="13" t="s">
-        <v>174</v>
-      </c>
-      <c r="F1" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="G1" s="13" t="s">
-        <v>176</v>
-      </c>
-      <c r="H1" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I1" s="13" t="s">
-        <v>178</v>
-      </c>
-      <c r="J1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="K1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>180</v>
       </c>
-      <c r="L1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>181</v>
       </c>
-      <c r="M1" s="13" t="s">
+      <c r="F1" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="G1" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H1" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="I1" s="14" t="s">
+        <v>185</v>
+      </c>
+      <c r="J1" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="K1" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="L1" s="14" t="s">
+        <v>188</v>
+      </c>
+      <c r="M1" s="14" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B2" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="C2" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D2" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="E2" s="14" t="b">
+      <c r="A2" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>190</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>192</v>
+      </c>
+      <c r="E2" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="F2" s="14" t="b">
+      <c r="F2" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G2" s="14">
+      <c r="G2" s="15">
         <v>5.0</v>
       </c>
-      <c r="H2" s="14" t="b">
+      <c r="H2" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="I2" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="J2" s="14" t="s">
-        <v>187</v>
-      </c>
-      <c r="K2" s="14" t="s">
-        <v>188</v>
-      </c>
-      <c r="L2" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="M2" s="15" t="s">
-        <v>190</v>
-      </c>
-      <c r="N2" s="16">
+      <c r="I2" s="15" t="s">
+        <v>193</v>
+      </c>
+      <c r="J2" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="L2" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="M2" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="N2" s="17">
         <v>50.0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="14" t="s">
+      <c r="A3" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="B3" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="C3" s="15" t="s">
         <v>191</v>
       </c>
-      <c r="B3" s="14" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D3" s="14" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="14" t="b">
+      <c r="D3" s="15" t="s">
+        <v>200</v>
+      </c>
+      <c r="E3" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F3" s="14" t="b">
+      <c r="F3" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G3" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H3" s="14" t="b">
+      <c r="G3" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H3" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I3" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="J3" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="K3" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="L3" s="14" t="s">
-        <v>195</v>
-      </c>
-      <c r="M3" s="14" t="s">
-        <v>196</v>
+      <c r="I3" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="J3" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="K3" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="L3" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>203</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="B4" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="E4" s="14" t="b">
+      <c r="A4" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="E4" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F4" s="14" t="b">
+      <c r="F4" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G4" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H4" s="14" t="b">
+      <c r="G4" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H4" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="J4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="K4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="L4" s="14" t="s">
-        <v>200</v>
-      </c>
-      <c r="M4" s="14" t="s">
+      <c r="I4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="L4" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="s">
+        <v>209</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>210</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F5" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G5" s="15" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="s">
-        <v>202</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>203</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D5" s="14" t="s">
-        <v>204</v>
-      </c>
-      <c r="E5" s="14" t="b">
+      <c r="H5" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F5" s="14" t="b">
+      <c r="I5" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="J5" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="K5" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="L5" s="15" t="s">
+        <v>212</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="E6" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G5" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H5" s="14" t="b">
+      <c r="G6" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H6" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I5" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="J5" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="K5" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L5" s="14" t="s">
-        <v>205</v>
-      </c>
-      <c r="M5" s="14" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="s">
-        <v>207</v>
-      </c>
-      <c r="B6" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D6" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="E6" s="14" t="b">
+      <c r="I6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="J6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="K6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" s="15" t="s">
+        <v>217</v>
+      </c>
+      <c r="M6" s="16" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F7" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="14" t="b">
+      <c r="G7" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H7" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H6" s="14" t="b">
+      <c r="I7" s="15" t="s">
+        <v>222</v>
+      </c>
+      <c r="J7" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="K7" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="L7" s="15" t="s">
+        <v>225</v>
+      </c>
+      <c r="M7" s="16" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I6" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="K6" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="L6" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="M6" s="15" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="B7" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="C7" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" s="14" t="b">
+      <c r="F8" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F7" s="14" t="b">
+      <c r="G8" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H8" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>230</v>
+      </c>
+      <c r="J8" s="15" t="s">
+        <v>231</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="M8" s="16" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D9" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E9" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="F9" s="15" t="b">
         <v>1</v>
       </c>
-      <c r="G7" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H7" s="14" t="b">
+      <c r="G9" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H9" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I7" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" s="14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7" s="14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" s="14" t="s">
-        <v>218</v>
-      </c>
-      <c r="M7" s="15" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="s">
-        <v>220</v>
-      </c>
-      <c r="B8" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="E8" s="14" t="b">
+      <c r="I9" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="J9" s="15" t="s">
+        <v>239</v>
+      </c>
+      <c r="K9" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="L9" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="M9" s="16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D10" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="E10" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F8" s="14" t="b">
+      <c r="F10" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H8" s="14" t="b">
+      <c r="G10" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H10" s="15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="J10" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="K10" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="L10" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="M10" s="16" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="E11" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I8" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="J8" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="K8" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="L8" s="14" t="s">
-        <v>226</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="s">
-        <v>228</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>229</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>230</v>
-      </c>
-      <c r="E9" s="14" t="b">
+      <c r="F11" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F9" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="G9" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H9" s="14" t="b">
+      <c r="G11" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I9" s="14" t="s">
-        <v>231</v>
-      </c>
-      <c r="J9" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="K9" s="14" t="s">
-        <v>233</v>
-      </c>
-      <c r="L9" s="14" t="s">
-        <v>234</v>
-      </c>
-      <c r="M9" s="15" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="s">
-        <v>236</v>
-      </c>
-      <c r="B10" s="14" t="s">
-        <v>237</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>238</v>
-      </c>
-      <c r="E10" s="14" t="b">
+      <c r="I11" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="J11" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="K11" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="L11" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="M11" s="16" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" s="15" t="s">
+        <v>260</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>191</v>
+      </c>
+      <c r="D12" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="E12" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F10" s="14" t="b">
+      <c r="F12" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G10" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H10" s="14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" s="14" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" s="14" t="s">
-        <v>240</v>
-      </c>
-      <c r="K10" s="14" t="s">
-        <v>241</v>
-      </c>
-      <c r="L10" s="14" t="s">
-        <v>242</v>
-      </c>
-      <c r="M10" s="15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="s">
-        <v>244</v>
-      </c>
-      <c r="B11" s="14" t="s">
-        <v>245</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>246</v>
-      </c>
-      <c r="E11" s="14" t="b">
+      <c r="G12" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="H12" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F11" s="14" t="b">
+      <c r="I12" s="15" t="s">
+        <v>262</v>
+      </c>
+      <c r="J12" s="15" t="s">
+        <v>263</v>
+      </c>
+      <c r="K12" s="15" t="s">
+        <v>264</v>
+      </c>
+      <c r="L12" s="15" t="s">
+        <v>265</v>
+      </c>
+      <c r="M12" s="16" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15"/>
+      <c r="B13" s="15"/>
+      <c r="C13" s="15"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="15"/>
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="15"/>
+      <c r="I13" s="15"/>
+      <c r="J13" s="15"/>
+      <c r="K13" s="15"/>
+      <c r="L13" s="15"/>
+      <c r="M13" s="16" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15"/>
+      <c r="B14" s="15"/>
+      <c r="C14" s="15"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="15"/>
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="15"/>
+      <c r="I14" s="15"/>
+      <c r="J14" s="15"/>
+      <c r="K14" s="15"/>
+      <c r="L14" s="15"/>
+      <c r="M14" s="16" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15"/>
+      <c r="B15" s="15"/>
+      <c r="C15" s="15"/>
+      <c r="D15" s="15"/>
+      <c r="E15" s="15"/>
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="15"/>
+      <c r="I15" s="15"/>
+      <c r="J15" s="15"/>
+      <c r="K15" s="15"/>
+      <c r="L15" s="15"/>
+      <c r="M15" s="16" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="15"/>
+      <c r="B16" s="15"/>
+      <c r="C16" s="15"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="15"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="15"/>
+      <c r="K16" s="15"/>
+      <c r="L16" s="15"/>
+      <c r="M16" s="16" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="16" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
+      <c r="L18" s="15"/>
+      <c r="M18" s="16" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="16" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
+      <c r="L20" s="15"/>
+      <c r="M20" s="15"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="15"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15"/>
+      <c r="B22" s="15"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="15"/>
+      <c r="F22" s="15"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="15"/>
+      <c r="I22" s="15"/>
+      <c r="J22" s="15"/>
+      <c r="K22" s="15"/>
+      <c r="L22" s="15"/>
+      <c r="M22" s="15"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15"/>
+      <c r="B23" s="15"/>
+      <c r="C23" s="15"/>
+      <c r="D23" s="15"/>
+      <c r="E23" s="15"/>
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="15"/>
+      <c r="J23" s="15"/>
+      <c r="K23" s="15"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="15"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15"/>
+      <c r="B24" s="15"/>
+      <c r="C24" s="15"/>
+      <c r="D24" s="15"/>
+      <c r="E24" s="15"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="15"/>
+      <c r="I24" s="15"/>
+      <c r="J24" s="15"/>
+      <c r="K24" s="15"/>
+      <c r="L24" s="15"/>
+      <c r="M24" s="15"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="15"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="15"/>
+      <c r="J25" s="15"/>
+      <c r="K25" s="15"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="15"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15"/>
+      <c r="B26" s="15"/>
+      <c r="C26" s="15"/>
+      <c r="D26" s="15"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="15"/>
+      <c r="J26" s="15"/>
+      <c r="K26" s="15"/>
+      <c r="L26" s="15"/>
+      <c r="M26" s="15"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="15"/>
+      <c r="B28" s="15"/>
+      <c r="C28" s="15"/>
+      <c r="D28" s="15"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="15"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="15"/>
+      <c r="I28" s="15"/>
+      <c r="J28" s="15"/>
+      <c r="K28" s="15"/>
+      <c r="L28" s="15"/>
+      <c r="M28" s="15"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="15"/>
+      <c r="B29" s="15"/>
+      <c r="C29" s="15"/>
+      <c r="D29" s="15"/>
+      <c r="E29" s="15"/>
+      <c r="F29" s="15"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="15"/>
+      <c r="I29" s="15"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="15"/>
+      <c r="B30" s="15"/>
+      <c r="C30" s="15"/>
+      <c r="D30" s="15"/>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="15"/>
+      <c r="I30" s="15"/>
+      <c r="J30" s="15"/>
+      <c r="K30" s="15"/>
+      <c r="L30" s="15"/>
+      <c r="M30" s="15"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="15"/>
+      <c r="B31" s="15"/>
+      <c r="C31" s="15"/>
+      <c r="D31" s="15"/>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="15"/>
+      <c r="I31" s="15"/>
+      <c r="J31" s="15"/>
+      <c r="K31" s="15"/>
+      <c r="L31" s="15"/>
+      <c r="M31" s="15"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="15"/>
+      <c r="B32" s="15"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="15"/>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="15"/>
+      <c r="I32" s="15"/>
+      <c r="J32" s="15"/>
+      <c r="K32" s="15"/>
+      <c r="L32" s="15"/>
+      <c r="M32" s="15"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15"/>
+      <c r="B33" s="15"/>
+      <c r="C33" s="15"/>
+      <c r="D33" s="15"/>
+      <c r="E33" s="15"/>
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="H33" s="15"/>
+      <c r="I33" s="15"/>
+      <c r="J33" s="15"/>
+      <c r="K33" s="15"/>
+      <c r="L33" s="15"/>
+      <c r="M33" s="15"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="15"/>
+      <c r="B34" s="15"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="H34" s="15"/>
+      <c r="I34" s="15"/>
+      <c r="J34" s="15"/>
+      <c r="K34" s="15"/>
+      <c r="L34" s="15"/>
+      <c r="M34" s="15"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="15"/>
+      <c r="B35" s="15"/>
+      <c r="C35" s="15"/>
+      <c r="D35" s="15"/>
+      <c r="E35" s="15"/>
+      <c r="F35" s="15"/>
+      <c r="G35" s="15"/>
+      <c r="H35" s="15"/>
+      <c r="I35" s="15"/>
+      <c r="J35" s="15"/>
+      <c r="K35" s="15"/>
+      <c r="L35" s="15"/>
+      <c r="M35" s="15"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="15"/>
+      <c r="B36" s="15"/>
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="15" t="s">
+        <v>274</v>
+      </c>
+      <c r="B37" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>277</v>
+      </c>
+      <c r="E37" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G11" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H11" s="14" t="b">
+      <c r="F37" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I11" s="14" t="s">
-        <v>247</v>
-      </c>
-      <c r="J11" s="14" t="s">
-        <v>248</v>
-      </c>
-      <c r="K11" s="14" t="s">
-        <v>249</v>
-      </c>
-      <c r="L11" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="M11" s="15" t="s">
-        <v>251</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="s">
-        <v>252</v>
-      </c>
-      <c r="B12" s="14" t="s">
-        <v>253</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="D12" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="E12" s="14" t="b">
+      <c r="G37" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="H37" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F12" s="14" t="b">
+      <c r="I37" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="J37" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="K37" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="L37" s="15" t="s">
+        <v>278</v>
+      </c>
+      <c r="M37" s="15" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="15" t="s">
+        <v>280</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>281</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D38" s="15" t="s">
+        <v>282</v>
+      </c>
+      <c r="E38" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G12" s="14" t="s">
-        <v>194</v>
-      </c>
-      <c r="H12" s="14" t="b">
+      <c r="F38" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I12" s="14" t="s">
-        <v>255</v>
-      </c>
-      <c r="J12" s="14" t="s">
-        <v>256</v>
-      </c>
-      <c r="K12" s="14" t="s">
-        <v>257</v>
-      </c>
-      <c r="L12" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="M12" s="15" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14"/>
-      <c r="B13" s="14"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="14"/>
-      <c r="E13" s="14"/>
-      <c r="F13" s="14"/>
-      <c r="G13" s="14"/>
-      <c r="H13" s="14"/>
-      <c r="I13" s="14"/>
-      <c r="J13" s="14"/>
-      <c r="K13" s="14"/>
-      <c r="L13" s="14"/>
-      <c r="M13" s="15" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14"/>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-      <c r="G14" s="14"/>
-      <c r="H14" s="14"/>
-      <c r="I14" s="14"/>
-      <c r="J14" s="14"/>
-      <c r="K14" s="14"/>
-      <c r="L14" s="14"/>
-      <c r="M14" s="15" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14"/>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-      <c r="K15" s="14"/>
-      <c r="L15" s="14"/>
-      <c r="M15" s="15" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14"/>
-      <c r="B16" s="14"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="14"/>
-      <c r="E16" s="14"/>
-      <c r="F16" s="14"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="14"/>
-      <c r="I16" s="14"/>
-      <c r="J16" s="14"/>
-      <c r="K16" s="14"/>
-      <c r="L16" s="14"/>
-      <c r="M16" s="15" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
-      <c r="L17" s="14"/>
-      <c r="M17" s="15" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
-      <c r="L18" s="14"/>
-      <c r="M18" s="15" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
-      <c r="L19" s="14"/>
-      <c r="M19" s="15" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
-      <c r="L21" s="14"/>
-      <c r="M21" s="14"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14"/>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14"/>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14"/>
-      <c r="M22" s="14"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-      <c r="K23" s="14"/>
-      <c r="L23" s="14"/>
-      <c r="M23" s="14"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
-      <c r="E24" s="14"/>
-      <c r="F24" s="14"/>
-      <c r="G24" s="14"/>
-      <c r="H24" s="14"/>
-      <c r="I24" s="14"/>
-      <c r="J24" s="14"/>
-      <c r="K24" s="14"/>
-      <c r="L24" s="14"/>
-      <c r="M24" s="14"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
-      <c r="G25" s="14"/>
-      <c r="H25" s="14"/>
-      <c r="I25" s="14"/>
-      <c r="J25" s="14"/>
-      <c r="K25" s="14"/>
-      <c r="L25" s="14"/>
-      <c r="M25" s="14"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="14"/>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-      <c r="G26" s="14"/>
-      <c r="H26" s="14"/>
-      <c r="I26" s="14"/>
-      <c r="J26" s="14"/>
-      <c r="K26" s="14"/>
-      <c r="L26" s="14"/>
-      <c r="M26" s="14"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="14"/>
-      <c r="B27" s="14"/>
-      <c r="C27" s="14"/>
-      <c r="D27" s="14"/>
-      <c r="E27" s="14"/>
-      <c r="F27" s="14"/>
-      <c r="G27" s="14"/>
-      <c r="H27" s="14"/>
-      <c r="I27" s="14"/>
-      <c r="J27" s="14"/>
-      <c r="K27" s="14"/>
-      <c r="L27" s="14"/>
-      <c r="M27" s="14"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="14"/>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-      <c r="G28" s="14"/>
-      <c r="H28" s="14"/>
-      <c r="I28" s="14"/>
-      <c r="J28" s="14"/>
-      <c r="K28" s="14"/>
-      <c r="L28" s="14"/>
-      <c r="M28" s="14"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="14"/>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-      <c r="G29" s="14"/>
-      <c r="H29" s="14"/>
-      <c r="I29" s="14"/>
-      <c r="J29" s="14"/>
-      <c r="K29" s="14"/>
-      <c r="L29" s="14"/>
-      <c r="M29" s="14"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="14"/>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-      <c r="G30" s="14"/>
-      <c r="H30" s="14"/>
-      <c r="I30" s="14"/>
-      <c r="J30" s="14"/>
-      <c r="K30" s="14"/>
-      <c r="L30" s="14"/>
-      <c r="M30" s="14"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="14"/>
-      <c r="B31" s="14"/>
-      <c r="C31" s="14"/>
-      <c r="D31" s="14"/>
-      <c r="E31" s="14"/>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-      <c r="K31" s="14"/>
-      <c r="L31" s="14"/>
-      <c r="M31" s="14"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="14"/>
-      <c r="B32" s="14"/>
-      <c r="C32" s="14"/>
-      <c r="D32" s="14"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="14"/>
-      <c r="G32" s="14"/>
-      <c r="H32" s="14"/>
-      <c r="I32" s="14"/>
-      <c r="J32" s="14"/>
-      <c r="K32" s="14"/>
-      <c r="L32" s="14"/>
-      <c r="M32" s="14"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="14"/>
-      <c r="B33" s="14"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="14"/>
-      <c r="E33" s="14"/>
-      <c r="F33" s="14"/>
-      <c r="G33" s="14"/>
-      <c r="H33" s="14"/>
-      <c r="I33" s="14"/>
-      <c r="J33" s="14"/>
-      <c r="K33" s="14"/>
-      <c r="L33" s="14"/>
-      <c r="M33" s="14"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="14"/>
-      <c r="B34" s="14"/>
-      <c r="C34" s="14"/>
-      <c r="D34" s="14"/>
-      <c r="E34" s="14"/>
-      <c r="F34" s="14"/>
-      <c r="G34" s="14"/>
-      <c r="H34" s="14"/>
-      <c r="I34" s="14"/>
-      <c r="J34" s="14"/>
-      <c r="K34" s="14"/>
-      <c r="L34" s="14"/>
-      <c r="M34" s="14"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="14"/>
-      <c r="B35" s="14"/>
-      <c r="C35" s="14"/>
-      <c r="D35" s="14"/>
-      <c r="E35" s="14"/>
-      <c r="F35" s="14"/>
-      <c r="G35" s="14"/>
-      <c r="H35" s="14"/>
-      <c r="I35" s="14"/>
-      <c r="J35" s="14"/>
-      <c r="K35" s="14"/>
-      <c r="L35" s="14"/>
-      <c r="M35" s="14"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="14"/>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-      <c r="G36" s="14"/>
-      <c r="H36" s="14"/>
-      <c r="I36" s="14"/>
-      <c r="J36" s="14"/>
-      <c r="K36" s="14"/>
-      <c r="L36" s="14"/>
-      <c r="M36" s="14"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="B37" s="14" t="s">
-        <v>268</v>
-      </c>
-      <c r="C37" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="E37" s="14" t="b">
+      <c r="G38" s="15">
+        <v>1.0</v>
+      </c>
+      <c r="H38" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F37" s="14" t="b">
+      <c r="I38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="J38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="K38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="L38" s="15" t="s">
+        <v>283</v>
+      </c>
+      <c r="M38" s="15" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="15" t="s">
+        <v>285</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>286</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="E39" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G37" s="14">
+      <c r="F39" s="15" t="b">
+        <v>0</v>
+      </c>
+      <c r="G39" s="15">
         <v>1.0</v>
       </c>
-      <c r="H37" s="14" t="b">
+      <c r="H39" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I37" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="J37" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="K37" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="L37" s="14" t="s">
-        <v>271</v>
-      </c>
-      <c r="M37" s="14" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="14" t="s">
-        <v>273</v>
-      </c>
-      <c r="B38" s="14" t="s">
-        <v>274</v>
-      </c>
-      <c r="C38" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D38" s="14" t="s">
-        <v>275</v>
-      </c>
-      <c r="E38" s="14" t="b">
+      <c r="I39" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="J39" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="K39" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="L39" s="15" t="s">
+        <v>288</v>
+      </c>
+      <c r="M39" s="15" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="15" t="s">
+        <v>290</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>291</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>292</v>
+      </c>
+      <c r="E40" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F38" s="14" t="b">
+      <c r="F40" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G38" s="14">
+      <c r="G40" s="15">
         <v>1.0</v>
       </c>
-      <c r="H38" s="14" t="b">
+      <c r="H40" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I38" s="14" t="s">
+      <c r="I40" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="J40" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="K40" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="L40" s="15" t="s">
+        <v>293</v>
+      </c>
+      <c r="M40" s="15" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="15" t="s">
+        <v>295</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>296</v>
+      </c>
+      <c r="C41" s="15" t="s">
         <v>276</v>
       </c>
-      <c r="J38" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="K38" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="L38" s="14" t="s">
-        <v>276</v>
-      </c>
-      <c r="M38" s="14" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="14" t="s">
-        <v>278</v>
-      </c>
-      <c r="B39" s="14" t="s">
-        <v>279</v>
-      </c>
-      <c r="C39" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D39" s="14" t="s">
-        <v>280</v>
-      </c>
-      <c r="E39" s="14" t="b">
+      <c r="D41" s="15" t="s">
+        <v>297</v>
+      </c>
+      <c r="E41" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="F39" s="14" t="b">
+      <c r="F41" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="G39" s="14">
+      <c r="G41" s="15">
         <v>1.0</v>
       </c>
-      <c r="H39" s="14" t="b">
+      <c r="H41" s="15" t="b">
         <v>0</v>
       </c>
-      <c r="I39" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="J39" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="K39" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="L39" s="14" t="s">
-        <v>281</v>
-      </c>
-      <c r="M39" s="14" t="s">
-        <v>282</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="14" t="s">
-        <v>283</v>
-      </c>
-      <c r="B40" s="14" t="s">
-        <v>284</v>
-      </c>
-      <c r="C40" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D40" s="14" t="s">
-        <v>285</v>
-      </c>
-      <c r="E40" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="H40" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="J40" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="K40" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="L40" s="14" t="s">
-        <v>286</v>
-      </c>
-      <c r="M40" s="14" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="14" t="s">
-        <v>288</v>
-      </c>
-      <c r="B41" s="14" t="s">
-        <v>289</v>
-      </c>
-      <c r="C41" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="D41" s="14" t="s">
-        <v>290</v>
-      </c>
-      <c r="E41" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" s="14">
-        <v>1.0</v>
-      </c>
-      <c r="H41" s="14" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="J41" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="K41" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="L41" s="14" t="s">
-        <v>291</v>
-      </c>
-      <c r="M41" s="14" t="s">
-        <v>292</v>
+      <c r="I41" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="J41" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="K41" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="L41" s="15" t="s">
+        <v>298</v>
+      </c>
+      <c r="M41" s="15" t="s">
+        <v>299</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>
@@ -37006,143 +37044,143 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="D1" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>295</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>296</v>
+      <c r="C1" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="D2" s="20" t="s">
-        <v>299</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>301</v>
+      <c r="A2" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>304</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>306</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>308</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>302</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>303</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>300</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>304</v>
+      <c r="A3" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>309</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D3" s="23" t="s">
+        <v>310</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>307</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>305</v>
       </c>
-      <c r="B4" s="19" t="s">
+      <c r="D4" s="20" t="s">
+        <v>313</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>307</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>315</v>
+      </c>
+      <c r="C5" s="22" t="s">
         <v>305</v>
       </c>
-      <c r="C4" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>306</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="F4" s="19" t="s">
+      <c r="D5" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>319</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>305</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>320</v>
+      </c>
+      <c r="E6" s="20" t="s">
         <v>307</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>308</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>309</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>312</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>298</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>313</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>300</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>314</v>
+      <c r="F6" s="20" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>315</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>298</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>195</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>310</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>316</v>
+      <c r="A7" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>322</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>305</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>317</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>323</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -38152,579 +38190,579 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>317</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>318</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>319</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>320</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>321</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>322</v>
-      </c>
-      <c r="G1" s="17" t="s">
-        <v>323</v>
-      </c>
-      <c r="H1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>324</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="B1" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="J1" s="17" t="s">
-        <v>296</v>
+      <c r="C1" s="18" t="s">
+        <v>326</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>327</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>328</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>329</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>331</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>332</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>303</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19">
+      <c r="A2" s="20">
         <v>1.0</v>
       </c>
-      <c r="B2" s="19">
+      <c r="B2" s="20">
         <v>18.0</v>
       </c>
-      <c r="C2" s="19">
+      <c r="C2" s="20">
         <v>1.0</v>
       </c>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19">
+      <c r="D2" s="20"/>
+      <c r="E2" s="20">
         <v>1.0</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="G2" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="H2" s="19"/>
-      <c r="I2" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J2" s="19"/>
+      <c r="F2" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="G2" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H2" s="20"/>
+      <c r="I2" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J2" s="20"/>
     </row>
     <row r="3">
-      <c r="A3" s="21">
+      <c r="A3" s="22">
         <v>2.0</v>
       </c>
-      <c r="B3" s="21">
+      <c r="B3" s="22">
         <v>18.0</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="22">
         <v>1.0</v>
       </c>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21">
+      <c r="D3" s="22"/>
+      <c r="E3" s="22">
         <v>1.0</v>
       </c>
-      <c r="F3" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21" t="s">
-        <v>329</v>
-      </c>
-      <c r="J3" s="21"/>
+      <c r="F3" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="G3" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22" t="s">
+        <v>336</v>
+      </c>
+      <c r="J3" s="22"/>
     </row>
     <row r="4">
-      <c r="A4" s="19">
+      <c r="A4" s="20">
         <v>3.0</v>
       </c>
-      <c r="B4" s="19">
+      <c r="B4" s="20">
         <v>18.0</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="20">
         <v>1.0</v>
       </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19">
+      <c r="D4" s="20"/>
+      <c r="E4" s="20">
         <v>1.0</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>326</v>
-      </c>
-      <c r="G4" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19" t="s">
-        <v>330</v>
-      </c>
-      <c r="J4" s="19"/>
+      <c r="F4" s="20" t="s">
+        <v>333</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="20" t="s">
+        <v>337</v>
+      </c>
+      <c r="J4" s="20"/>
     </row>
     <row r="5">
-      <c r="A5" s="21">
+      <c r="A5" s="22">
         <v>4.0</v>
       </c>
-      <c r="B5" s="21">
+      <c r="B5" s="22">
         <v>23.0</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="22">
         <v>1.0</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21">
+      <c r="D5" s="22"/>
+      <c r="E5" s="22">
         <v>1.0</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>326</v>
-      </c>
-      <c r="G5" s="21" t="s">
-        <v>327</v>
-      </c>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21" t="s">
-        <v>331</v>
-      </c>
-      <c r="J5" s="21"/>
+      <c r="F5" s="22" t="s">
+        <v>333</v>
+      </c>
+      <c r="G5" s="22" t="s">
+        <v>334</v>
+      </c>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22" t="s">
+        <v>338</v>
+      </c>
+      <c r="J5" s="22"/>
     </row>
     <row r="6">
-      <c r="A6" s="19">
+      <c r="A6" s="20">
         <v>5.0</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="20">
         <v>31.0</v>
       </c>
-      <c r="C6" s="19">
+      <c r="C6" s="20">
         <v>1.0</v>
       </c>
-      <c r="D6" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="E6" s="19">
+      <c r="D6" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="E6" s="20">
         <v>1.0</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>333</v>
-      </c>
-      <c r="G6" s="19" t="s">
-        <v>327</v>
-      </c>
-      <c r="H6" s="19">
+      <c r="F6" s="20" t="s">
+        <v>340</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>334</v>
+      </c>
+      <c r="H6" s="20">
         <v>1.0</v>
       </c>
-      <c r="I6" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J6" s="19" t="s">
+      <c r="I6" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="J6" s="20" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="22">
+        <v>180.0</v>
+      </c>
+      <c r="C7" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>343</v>
+      </c>
+      <c r="G7" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22" t="s">
         <v>335</v>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="21">
-        <v>180.0</v>
-      </c>
-      <c r="C7" s="21">
+      <c r="J7" s="22"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="20">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="20">
+        <v>220.0</v>
+      </c>
+      <c r="C8" s="20">
         <v>2.0</v>
       </c>
-      <c r="D7" s="21"/>
-      <c r="E7" s="21">
+      <c r="D8" s="20"/>
+      <c r="E8" s="20">
         <v>2.0</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>336</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J7" s="21"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="19">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="19">
-        <v>220.0</v>
-      </c>
-      <c r="C8" s="19">
+      <c r="F8" s="20" t="s">
+        <v>345</v>
+      </c>
+      <c r="G8" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H8" s="20"/>
+      <c r="I8" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J8" s="20"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="22">
+        <v>8.0</v>
+      </c>
+      <c r="B9" s="22">
+        <v>270.0</v>
+      </c>
+      <c r="C9" s="22">
         <v>2.0</v>
       </c>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19">
+      <c r="D9" s="22"/>
+      <c r="E9" s="22">
         <v>2.0</v>
       </c>
-      <c r="F8" s="19" t="s">
-        <v>338</v>
-      </c>
-      <c r="G8" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J8" s="19"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="21">
+      <c r="F9" s="22" t="s">
+        <v>346</v>
+      </c>
+      <c r="G9" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J9" s="22"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="20">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="20">
+        <v>340.0</v>
+      </c>
+      <c r="C10" s="20">
+        <v>2.0</v>
+      </c>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20">
+        <v>2.0</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>347</v>
+      </c>
+      <c r="G10" s="20" t="s">
+        <v>344</v>
+      </c>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J10" s="20"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="22">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="22">
+        <v>600.0</v>
+      </c>
+      <c r="C11" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="E11" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>348</v>
+      </c>
+      <c r="G11" s="22" t="s">
+        <v>344</v>
+      </c>
+      <c r="H11" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>341</v>
+      </c>
+      <c r="J11" s="22" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="20">
+        <v>450.0</v>
+      </c>
+      <c r="C12" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="D12" s="20"/>
+      <c r="E12" s="20">
+        <v>5.0</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="G12" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J12" s="20"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="22">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="22">
+        <v>450.0</v>
+      </c>
+      <c r="C13" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>349</v>
+      </c>
+      <c r="G13" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J13" s="22"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="20">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="20">
+        <v>450.0</v>
+      </c>
+      <c r="C14" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20">
+        <v>5.0</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>349</v>
+      </c>
+      <c r="G14" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="H14" s="20"/>
+      <c r="I14" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J14" s="20"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="22">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="22">
+        <v>585.0</v>
+      </c>
+      <c r="C15" s="22">
+        <v>3.0</v>
+      </c>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>350</v>
+      </c>
+      <c r="G15" s="22" t="s">
+        <v>247</v>
+      </c>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J15" s="22"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="20">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="20">
+        <v>765.0</v>
+      </c>
+      <c r="C16" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>339</v>
+      </c>
+      <c r="E16" s="20">
+        <v>5.0</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>351</v>
+      </c>
+      <c r="G16" s="20" t="s">
+        <v>247</v>
+      </c>
+      <c r="H16" s="20">
+        <v>3.0</v>
+      </c>
+      <c r="I16" s="20" t="s">
+        <v>341</v>
+      </c>
+      <c r="J16" s="20" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="22">
+        <v>4050.0</v>
+      </c>
+      <c r="C17" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="D17" s="22"/>
+      <c r="E17" s="22">
+        <v>15.0</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="G17" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="20">
+        <v>4050.0</v>
+      </c>
+      <c r="C18" s="20">
+        <v>4.0</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20">
+        <v>15.0</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>352</v>
+      </c>
+      <c r="G18" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="H18" s="20"/>
+      <c r="I18" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J18" s="20"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="22">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="22">
+        <v>4050.0</v>
+      </c>
+      <c r="C19" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22">
+        <v>15.0</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>352</v>
+      </c>
+      <c r="G19" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22" t="s">
+        <v>335</v>
+      </c>
+      <c r="J19" s="22"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="20">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="20">
+        <v>5265.0</v>
+      </c>
+      <c r="C20" s="20">
+        <v>4.0</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20">
+        <v>15.0</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>354</v>
+      </c>
+      <c r="G20" s="20" t="s">
+        <v>353</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="20" t="s">
+        <v>335</v>
+      </c>
+      <c r="J20" s="20"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="22">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="22">
+        <v>6885.0</v>
+      </c>
+      <c r="C21" s="22">
+        <v>4.0</v>
+      </c>
+      <c r="D21" s="22" t="s">
+        <v>339</v>
+      </c>
+      <c r="E21" s="22">
+        <v>15.0</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>355</v>
+      </c>
+      <c r="G21" s="22" t="s">
+        <v>353</v>
+      </c>
+      <c r="H21" s="22">
         <v>8.0</v>
       </c>
-      <c r="B9" s="21">
-        <v>270.0</v>
-      </c>
-      <c r="C9" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="D9" s="21"/>
-      <c r="E9" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>339</v>
-      </c>
-      <c r="G9" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J9" s="21"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="19">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="19">
-        <v>340.0</v>
-      </c>
-      <c r="C10" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>340</v>
-      </c>
-      <c r="G10" s="19" t="s">
-        <v>337</v>
-      </c>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J10" s="19"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="21">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="21">
-        <v>600.0</v>
-      </c>
-      <c r="C11" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="D11" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="E11" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="F11" s="21" t="s">
+      <c r="I21" s="22" t="s">
         <v>341</v>
       </c>
-      <c r="G11" s="21" t="s">
-        <v>337</v>
-      </c>
-      <c r="H11" s="21">
-        <v>2.0</v>
-      </c>
-      <c r="I11" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="J11" s="21" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="19">
-        <v>450.0</v>
-      </c>
-      <c r="C12" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="D12" s="19"/>
-      <c r="E12" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="F12" s="19" t="s">
+      <c r="J21" s="22" t="s">
         <v>342</v>
-      </c>
-      <c r="G12" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="H12" s="19"/>
-      <c r="I12" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J12" s="19"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="21">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="21">
-        <v>450.0</v>
-      </c>
-      <c r="C13" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>342</v>
-      </c>
-      <c r="G13" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J13" s="21"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="19">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="19">
-        <v>450.0</v>
-      </c>
-      <c r="C14" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="D14" s="19"/>
-      <c r="E14" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>342</v>
-      </c>
-      <c r="G14" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="H14" s="19"/>
-      <c r="I14" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J14" s="19"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="21">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="21">
-        <v>585.0</v>
-      </c>
-      <c r="C15" s="21">
-        <v>3.0</v>
-      </c>
-      <c r="D15" s="21"/>
-      <c r="E15" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>343</v>
-      </c>
-      <c r="G15" s="21" t="s">
-        <v>240</v>
-      </c>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J15" s="21"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="19">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="19">
-        <v>765.0</v>
-      </c>
-      <c r="C16" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>332</v>
-      </c>
-      <c r="E16" s="19">
-        <v>5.0</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>344</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>240</v>
-      </c>
-      <c r="H16" s="19">
-        <v>3.0</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>334</v>
-      </c>
-      <c r="J16" s="19" t="s">
-        <v>335</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="21">
-        <v>4050.0</v>
-      </c>
-      <c r="C17" s="21">
-        <v>4.0</v>
-      </c>
-      <c r="D17" s="21"/>
-      <c r="E17" s="21">
-        <v>15.0</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="G17" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J17" s="21"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="19">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="19">
-        <v>4050.0</v>
-      </c>
-      <c r="C18" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19">
-        <v>15.0</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>345</v>
-      </c>
-      <c r="G18" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="H18" s="19"/>
-      <c r="I18" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J18" s="19"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="21">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="21">
-        <v>4050.0</v>
-      </c>
-      <c r="C19" s="21">
-        <v>4.0</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21">
-        <v>15.0</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>345</v>
-      </c>
-      <c r="G19" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21" t="s">
-        <v>328</v>
-      </c>
-      <c r="J19" s="21"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="19">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="19">
-        <v>5265.0</v>
-      </c>
-      <c r="C20" s="19">
-        <v>4.0</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19">
-        <v>15.0</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>347</v>
-      </c>
-      <c r="G20" s="19" t="s">
-        <v>346</v>
-      </c>
-      <c r="H20" s="19"/>
-      <c r="I20" s="19" t="s">
-        <v>328</v>
-      </c>
-      <c r="J20" s="19"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="21">
-        <v>6885.0</v>
-      </c>
-      <c r="C21" s="21">
-        <v>4.0</v>
-      </c>
-      <c r="D21" s="21" t="s">
-        <v>332</v>
-      </c>
-      <c r="E21" s="21">
-        <v>15.0</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>348</v>
-      </c>
-      <c r="G21" s="21" t="s">
-        <v>346</v>
-      </c>
-      <c r="H21" s="21">
-        <v>8.0</v>
-      </c>
-      <c r="I21" s="21" t="s">
-        <v>334</v>
-      </c>
-      <c r="J21" s="21" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1"/>
@@ -39729,122 +39767,122 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>349</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>350</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>351</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>294</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>352</v>
+      <c r="A1" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>357</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>358</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="s">
-        <v>353</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>355</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>356</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>357</v>
+      <c r="A2" s="20" t="s">
+        <v>360</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>362</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>363</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E3" s="21" t="s">
+      <c r="A3" s="22" t="s">
+        <v>365</v>
+      </c>
+      <c r="B3" s="22" t="s">
         <v>361</v>
       </c>
+      <c r="C3" s="22" t="s">
+        <v>366</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>367</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>368</v>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
-        <v>362</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>363</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>364</v>
-      </c>
-      <c r="E4" s="19" t="s">
-        <v>365</v>
+      <c r="A4" s="20" t="s">
+        <v>369</v>
+      </c>
+      <c r="B4" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="C4" s="20" t="s">
+        <v>370</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>372</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>367</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>368</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>369</v>
+      <c r="A5" s="22" t="s">
+        <v>373</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>374</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>375</v>
+      </c>
+      <c r="E5" s="22" t="s">
+        <v>376</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="19" t="s">
-        <v>370</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>354</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>371</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>372</v>
-      </c>
-      <c r="E6" s="19" t="s">
-        <v>373</v>
+      <c r="A6" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>361</v>
+      </c>
+      <c r="C6" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>380</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>376</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>377</v>
+      <c r="A7" s="22" t="s">
+        <v>381</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>361</v>
+      </c>
+      <c r="C7" s="22" t="s">
+        <v>382</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>383</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
@@ -40852,857 +40890,857 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.5" customHeight="1">
-      <c r="A1" s="17" t="s">
-        <v>378</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>379</v>
-      </c>
-      <c r="C1" s="17" t="s">
-        <v>293</v>
-      </c>
-      <c r="D1" s="17" t="s">
-        <v>380</v>
-      </c>
-      <c r="E1" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="F1" s="17" t="s">
-        <v>382</v>
+      <c r="A1" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>300</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>387</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>388</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>389</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>385</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>386</v>
-      </c>
-      <c r="F2" s="19" t="s">
-        <v>183</v>
+      <c r="A2" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="B2" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>391</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>392</v>
+      </c>
+      <c r="E2" s="20" t="s">
+        <v>393</v>
+      </c>
+      <c r="F2" s="20" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="21" t="s">
-        <v>193</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>389</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>192</v>
+      <c r="A3" s="22" t="s">
+        <v>200</v>
+      </c>
+      <c r="B3" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C3" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="D3" s="22" t="s">
+        <v>395</v>
+      </c>
+      <c r="E3" s="22" t="s">
+        <v>396</v>
+      </c>
+      <c r="F3" s="22" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="19" t="s">
-        <v>199</v>
-      </c>
-      <c r="B4" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>387</v>
-      </c>
-      <c r="D4" s="19"/>
-      <c r="E4" s="19" t="s">
+      <c r="A4" s="20" t="s">
+        <v>206</v>
+      </c>
+      <c r="B4" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>198</v>
+      <c r="C4" s="20" t="s">
+        <v>394</v>
+      </c>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20" t="s">
+        <v>397</v>
+      </c>
+      <c r="F4" s="20" t="s">
+        <v>205</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="21" t="s">
-        <v>204</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="A5" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="B5" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22" t="s">
+        <v>399</v>
+      </c>
+      <c r="F5" s="22" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21" t="s">
-        <v>392</v>
-      </c>
-      <c r="F5" s="21" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="s">
-        <v>209</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C6" s="19" t="s">
-        <v>384</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>393</v>
-      </c>
-      <c r="E6" s="19" t="s">
+      <c r="D6" s="20" t="s">
+        <v>400</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>401</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="B7" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C7" s="22" t="s">
         <v>394</v>
       </c>
-      <c r="F6" s="19" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="21" t="s">
-        <v>214</v>
-      </c>
-      <c r="B7" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="E7" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="F7" s="21" t="s">
-        <v>213</v>
+      <c r="D7" s="22" t="s">
+        <v>402</v>
+      </c>
+      <c r="E7" s="22" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="22" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="s">
-        <v>222</v>
-      </c>
-      <c r="B8" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C8" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>398</v>
-      </c>
-      <c r="E8" s="19" t="s">
-        <v>399</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>221</v>
+      <c r="A8" s="20" t="s">
+        <v>229</v>
+      </c>
+      <c r="B8" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>405</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>406</v>
+      </c>
+      <c r="F8" s="20" t="s">
+        <v>228</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="21" t="s">
-        <v>230</v>
-      </c>
-      <c r="B9" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" s="21" t="s">
-        <v>387</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="F9" s="21" t="s">
-        <v>229</v>
+      <c r="A9" s="22" t="s">
+        <v>237</v>
+      </c>
+      <c r="B9" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C9" s="22" t="s">
+        <v>394</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>405</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>407</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="s">
-        <v>238</v>
-      </c>
-      <c r="B10" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>402</v>
-      </c>
-      <c r="E10" s="19" t="s">
-        <v>403</v>
-      </c>
-      <c r="F10" s="19" t="s">
-        <v>237</v>
+      <c r="A10" s="20" t="s">
+        <v>245</v>
+      </c>
+      <c r="B10" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>409</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>410</v>
+      </c>
+      <c r="F10" s="20" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="B11" s="21" t="s">
-        <v>383</v>
-      </c>
-      <c r="C11" s="21" t="s">
+      <c r="A11" s="22" t="s">
+        <v>253</v>
+      </c>
+      <c r="B11" s="22" t="s">
+        <v>390</v>
+      </c>
+      <c r="C11" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="D11" s="22" t="s">
+        <v>412</v>
+      </c>
+      <c r="E11" s="22" t="s">
+        <v>413</v>
+      </c>
+      <c r="F11" s="22" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="s">
+        <v>261</v>
+      </c>
+      <c r="B12" s="20" t="s">
+        <v>390</v>
+      </c>
+      <c r="C12" s="20" t="s">
+        <v>414</v>
+      </c>
+      <c r="D12" s="20" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>416</v>
+      </c>
+      <c r="F12" s="20" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="s">
+        <v>277</v>
+      </c>
+      <c r="B13" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C13" s="22" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22" t="s">
+        <v>419</v>
+      </c>
+      <c r="F13" s="22" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="s">
+        <v>282</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>420</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>421</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>422</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="B15" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C15" s="22" t="s">
+        <v>423</v>
+      </c>
+      <c r="D15" s="22" t="s">
+        <v>424</v>
+      </c>
+      <c r="E15" s="22" t="s">
+        <v>425</v>
+      </c>
+      <c r="F15" s="22" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="s">
+        <v>292</v>
+      </c>
+      <c r="B16" s="20" t="s">
+        <v>417</v>
+      </c>
+      <c r="C16" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="D11" s="21" t="s">
-        <v>405</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>406</v>
-      </c>
-      <c r="F11" s="21" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="s">
-        <v>254</v>
-      </c>
-      <c r="B12" s="19" t="s">
-        <v>383</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>407</v>
-      </c>
-      <c r="D12" s="19" t="s">
+      <c r="D16" s="20" t="s">
+        <v>426</v>
+      </c>
+      <c r="E16" s="20" t="s">
+        <v>427</v>
+      </c>
+      <c r="F16" s="20" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="B17" s="22" t="s">
+        <v>417</v>
+      </c>
+      <c r="C17" s="22" t="s">
+        <v>411</v>
+      </c>
+      <c r="D17" s="22" t="s">
+        <v>428</v>
+      </c>
+      <c r="E17" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F17" s="22" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B18" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="20" t="s">
+        <v>429</v>
+      </c>
+      <c r="D18" s="20"/>
+      <c r="E18" s="20" t="s">
+        <v>430</v>
+      </c>
+      <c r="F18" s="20" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B19" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C19" s="22" t="s">
+        <v>432</v>
+      </c>
+      <c r="D19" s="22"/>
+      <c r="E19" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="F19" s="22" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>435</v>
+      </c>
+      <c r="D20" s="20"/>
+      <c r="E20" s="20" t="s">
+        <v>436</v>
+      </c>
+      <c r="F20" s="20" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C21" s="22" t="s">
+        <v>437</v>
+      </c>
+      <c r="D21" s="22"/>
+      <c r="E21" s="22" t="s">
+        <v>438</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B22" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C22" s="20" t="s">
+        <v>439</v>
+      </c>
+      <c r="D22" s="20" t="s">
+        <v>440</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>441</v>
+      </c>
+      <c r="F22" s="20" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="22" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C23" s="22" t="s">
+        <v>442</v>
+      </c>
+      <c r="D23" s="22" t="s">
+        <v>443</v>
+      </c>
+      <c r="E23" s="22" t="s">
+        <v>444</v>
+      </c>
+      <c r="F23" s="22" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="B24" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>445</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20" t="s">
+        <v>446</v>
+      </c>
+      <c r="F24" s="20" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="22" t="s">
+        <v>74</v>
+      </c>
+      <c r="B25" s="22" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" s="22" t="s">
+        <v>447</v>
+      </c>
+      <c r="D25" s="22"/>
+      <c r="E25" s="22" t="s">
+        <v>448</v>
+      </c>
+      <c r="F25" s="22" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="B26" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="20" t="s">
+        <v>450</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>451</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>452</v>
+      </c>
+      <c r="F26" s="20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="22" t="s">
+        <v>404</v>
+      </c>
+      <c r="D27" s="22" t="s">
+        <v>453</v>
+      </c>
+      <c r="E27" s="22" t="s">
+        <v>454</v>
+      </c>
+      <c r="F27" s="22" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="20" t="s">
+        <v>455</v>
+      </c>
+      <c r="B28" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>456</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>457</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>458</v>
+      </c>
+      <c r="F28" s="20" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="22" t="s">
+        <v>460</v>
+      </c>
+      <c r="B29" s="22" t="s">
+        <v>12</v>
+      </c>
+      <c r="C29" s="22" t="s">
         <v>408</v>
       </c>
-      <c r="E12" s="19" t="s">
-        <v>409</v>
-      </c>
-      <c r="F12" s="19" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="21" t="s">
-        <v>270</v>
-      </c>
-      <c r="B13" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="C13" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="F13" s="21" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="s">
-        <v>275</v>
-      </c>
-      <c r="B14" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>413</v>
-      </c>
-      <c r="D14" s="19" t="s">
-        <v>414</v>
-      </c>
-      <c r="E14" s="19" t="s">
-        <v>415</v>
-      </c>
-      <c r="F14" s="19" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="21" t="s">
-        <v>280</v>
-      </c>
-      <c r="B15" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="C15" s="21" t="s">
-        <v>416</v>
-      </c>
-      <c r="D15" s="21" t="s">
-        <v>417</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>418</v>
-      </c>
-      <c r="F15" s="21" t="s">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="s">
-        <v>285</v>
-      </c>
-      <c r="B16" s="19" t="s">
-        <v>410</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="D16" s="19" t="s">
-        <v>419</v>
-      </c>
-      <c r="E16" s="19" t="s">
-        <v>420</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="s">
-        <v>290</v>
-      </c>
-      <c r="B17" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="C17" s="21" t="s">
+      <c r="D29" s="22"/>
+      <c r="E29" s="22" t="s">
+        <v>461</v>
+      </c>
+      <c r="F29" s="22" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C30" s="20" t="s">
         <v>404</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>421</v>
-      </c>
-      <c r="E17" s="21" t="s">
-        <v>291</v>
-      </c>
-      <c r="F17" s="21" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="19" t="s">
-        <v>22</v>
-      </c>
-      <c r="B18" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>422</v>
-      </c>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19" t="s">
-        <v>423</v>
-      </c>
-      <c r="F18" s="19" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="s">
-        <v>32</v>
-      </c>
-      <c r="B19" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C19" s="21" t="s">
-        <v>425</v>
-      </c>
-      <c r="D19" s="21"/>
-      <c r="E19" s="21" t="s">
-        <v>426</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="19" t="s">
-        <v>428</v>
-      </c>
-      <c r="D20" s="19"/>
-      <c r="E20" s="19" t="s">
-        <v>429</v>
-      </c>
-      <c r="F20" s="19" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="21" t="s">
-        <v>47</v>
-      </c>
-      <c r="B21" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>430</v>
-      </c>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21" t="s">
-        <v>431</v>
-      </c>
-      <c r="F21" s="21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B22" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="19" t="s">
-        <v>432</v>
-      </c>
-      <c r="D22" s="19" t="s">
-        <v>433</v>
-      </c>
-      <c r="E22" s="19" t="s">
-        <v>434</v>
-      </c>
-      <c r="F22" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="B23" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C23" s="21" t="s">
-        <v>435</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>436</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>437</v>
-      </c>
-      <c r="F23" s="21" t="s">
+      <c r="D30" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="E30" s="20" t="s">
+        <v>463</v>
+      </c>
+      <c r="F30" s="20" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="22" t="s">
+        <v>65</v>
+      </c>
+      <c r="B31" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C31" s="22" t="s">
+        <v>408</v>
+      </c>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22" t="s">
+        <v>464</v>
+      </c>
+      <c r="F31" s="22" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="19" t="s">
-        <v>80</v>
-      </c>
-      <c r="B24" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>438</v>
-      </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19" t="s">
-        <v>439</v>
-      </c>
-      <c r="F24" s="19" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>408</v>
+      </c>
+      <c r="D32" s="20"/>
+      <c r="E32" s="20" t="s">
+        <v>465</v>
+      </c>
+      <c r="F32" s="20" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="21" t="s">
-        <v>74</v>
-      </c>
-      <c r="B25" s="21" t="s">
-        <v>3</v>
-      </c>
-      <c r="C25" s="21" t="s">
-        <v>440</v>
-      </c>
-      <c r="D25" s="21"/>
-      <c r="E25" s="21" t="s">
-        <v>441</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="19" t="s">
-        <v>87</v>
-      </c>
-      <c r="B26" s="19" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>443</v>
-      </c>
-      <c r="D26" s="19" t="s">
-        <v>444</v>
-      </c>
-      <c r="E26" s="19" t="s">
-        <v>445</v>
-      </c>
-      <c r="F26" s="19" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="D27" s="21" t="s">
-        <v>446</v>
-      </c>
-      <c r="E27" s="21" t="s">
-        <v>447</v>
-      </c>
-      <c r="F27" s="21" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="19" t="s">
-        <v>448</v>
-      </c>
-      <c r="B28" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="C28" s="19" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="B33" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="22" t="s">
+        <v>466</v>
+      </c>
+      <c r="D33" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="E33" s="22" t="s">
+        <v>467</v>
+      </c>
+      <c r="F33" s="22" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="20" t="s">
+        <v>469</v>
+      </c>
+      <c r="B34" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="20" t="s">
         <v>449</v>
       </c>
-      <c r="D28" s="19" t="s">
-        <v>450</v>
-      </c>
-      <c r="E28" s="19" t="s">
-        <v>451</v>
-      </c>
-      <c r="F28" s="19" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="21" t="s">
-        <v>453</v>
-      </c>
-      <c r="B29" s="21" t="s">
-        <v>12</v>
-      </c>
-      <c r="C29" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21" t="s">
-        <v>454</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="19" t="s">
-        <v>25</v>
-      </c>
-      <c r="B30" s="19" t="s">
+      <c r="D34" s="20"/>
+      <c r="E34" s="20" t="s">
+        <v>470</v>
+      </c>
+      <c r="F34" s="20" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="B35" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C30" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="D30" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="E30" s="19" t="s">
-        <v>456</v>
-      </c>
-      <c r="F30" s="19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="B31" s="21" t="s">
+      <c r="C35" s="22" t="s">
+        <v>472</v>
+      </c>
+      <c r="D35" s="22" t="s">
+        <v>473</v>
+      </c>
+      <c r="E35" s="22" t="s">
+        <v>474</v>
+      </c>
+      <c r="F35" s="22" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="20" t="s">
+        <v>476</v>
+      </c>
+      <c r="B36" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C31" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21" t="s">
-        <v>457</v>
-      </c>
-      <c r="F31" s="21" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="B32" s="19" t="s">
+      <c r="C36" s="20" t="s">
+        <v>477</v>
+      </c>
+      <c r="D36" s="20" t="s">
+        <v>462</v>
+      </c>
+      <c r="E36" s="20" t="s">
+        <v>478</v>
+      </c>
+      <c r="F36" s="20" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C32" s="19" t="s">
-        <v>401</v>
-      </c>
-      <c r="D32" s="19"/>
-      <c r="E32" s="19" t="s">
-        <v>458</v>
-      </c>
-      <c r="F32" s="19" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="21" t="s">
-        <v>90</v>
-      </c>
-      <c r="B33" s="21" t="s">
+      <c r="C37" s="22" t="s">
+        <v>480</v>
+      </c>
+      <c r="D37" s="22" t="s">
+        <v>481</v>
+      </c>
+      <c r="E37" s="22" t="s">
+        <v>482</v>
+      </c>
+      <c r="F37" s="22" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="B38" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C33" s="21" t="s">
-        <v>459</v>
-      </c>
-      <c r="D33" s="21" t="s">
-        <v>455</v>
-      </c>
-      <c r="E33" s="21" t="s">
-        <v>460</v>
-      </c>
-      <c r="F33" s="21" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="19" t="s">
-        <v>462</v>
-      </c>
-      <c r="B34" s="19" t="s">
+      <c r="C38" s="20" t="s">
+        <v>484</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>485</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>486</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="22" t="s">
+        <v>117</v>
+      </c>
+      <c r="B39" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C34" s="19" t="s">
-        <v>442</v>
-      </c>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19" t="s">
-        <v>463</v>
-      </c>
-      <c r="F34" s="19" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B35" s="21" t="s">
+      <c r="C39" s="22" t="s">
+        <v>488</v>
+      </c>
+      <c r="D39" s="22" t="s">
+        <v>489</v>
+      </c>
+      <c r="E39" s="22" t="s">
+        <v>490</v>
+      </c>
+      <c r="F39" s="22" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="20" t="s">
+        <v>129</v>
+      </c>
+      <c r="B40" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="C35" s="21" t="s">
-        <v>465</v>
-      </c>
-      <c r="D35" s="21" t="s">
-        <v>466</v>
-      </c>
-      <c r="E35" s="21" t="s">
-        <v>467</v>
-      </c>
-      <c r="F35" s="21" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="19" t="s">
-        <v>469</v>
-      </c>
-      <c r="B36" s="19" t="s">
+      <c r="C40" s="20" t="s">
+        <v>492</v>
+      </c>
+      <c r="D40" s="20" t="s">
+        <v>493</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>494</v>
+      </c>
+      <c r="F40" s="20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="22" t="s">
+        <v>121</v>
+      </c>
+      <c r="B41" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="C36" s="19" t="s">
-        <v>470</v>
-      </c>
-      <c r="D36" s="19" t="s">
-        <v>455</v>
-      </c>
-      <c r="E36" s="19" t="s">
-        <v>471</v>
-      </c>
-      <c r="F36" s="19" t="s">
+      <c r="C41" s="22" t="s">
+        <v>495</v>
+      </c>
+      <c r="D41" s="22" t="s">
+        <v>496</v>
+      </c>
+      <c r="E41" s="22" t="s">
+        <v>497</v>
+      </c>
+      <c r="F41" s="22" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="20" t="s">
+        <v>125</v>
+      </c>
+      <c r="B42" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" s="20" t="s">
+        <v>404</v>
+      </c>
+      <c r="D42" s="20" t="s">
+        <v>496</v>
+      </c>
+      <c r="E42" s="20" t="s">
+        <v>499</v>
+      </c>
+      <c r="F42" s="20" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="B43" s="22" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" s="22" t="s">
+        <v>501</v>
+      </c>
+      <c r="D43" s="22" t="s">
+        <v>502</v>
+      </c>
+      <c r="E43" s="22" t="s">
+        <v>503</v>
+      </c>
+      <c r="F43" s="22" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="B44" s="20" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" s="20" t="s">
         <v>472</v>
       </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="21" t="s">
-        <v>134</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>473</v>
-      </c>
-      <c r="D37" s="21" t="s">
-        <v>474</v>
-      </c>
-      <c r="E37" s="21" t="s">
-        <v>475</v>
-      </c>
-      <c r="F37" s="21" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="19" t="s">
-        <v>138</v>
-      </c>
-      <c r="B38" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C38" s="19" t="s">
-        <v>477</v>
-      </c>
-      <c r="D38" s="19" t="s">
-        <v>478</v>
-      </c>
-      <c r="E38" s="19" t="s">
-        <v>479</v>
-      </c>
-      <c r="F38" s="19" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="21" t="s">
-        <v>110</v>
-      </c>
-      <c r="B39" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C39" s="21" t="s">
-        <v>481</v>
-      </c>
-      <c r="D39" s="21" t="s">
-        <v>482</v>
-      </c>
-      <c r="E39" s="21" t="s">
-        <v>483</v>
-      </c>
-      <c r="F39" s="21" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="B40" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C40" s="19" t="s">
-        <v>485</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>486</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>487</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C41" s="21" t="s">
-        <v>488</v>
-      </c>
-      <c r="D41" s="21" t="s">
-        <v>489</v>
-      </c>
-      <c r="E41" s="21" t="s">
-        <v>490</v>
-      </c>
-      <c r="F41" s="21" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="19" t="s">
-        <v>118</v>
-      </c>
-      <c r="B42" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C42" s="19" t="s">
-        <v>397</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>492</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="21" t="s">
-        <v>130</v>
-      </c>
-      <c r="B43" s="21" t="s">
-        <v>11</v>
-      </c>
-      <c r="C43" s="21" t="s">
-        <v>494</v>
-      </c>
-      <c r="D43" s="21" t="s">
-        <v>495</v>
-      </c>
-      <c r="E43" s="21" t="s">
+      <c r="D44" s="20" t="s">
         <v>496</v>
       </c>
-      <c r="F43" s="21" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="19" t="s">
-        <v>146</v>
-      </c>
-      <c r="B44" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C44" s="19" t="s">
-        <v>465</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>489</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>498</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>499</v>
+      <c r="E44" s="20" t="s">
+        <v>505</v>
+      </c>
+      <c r="F44" s="20" t="s">
+        <v>506</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1"/>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -317,7 +317,7 @@
     <t>🏰</t>
   </si>
   <si>
-    <t>生存時：このキャラクターの攻撃力は最も高い味方の攻撃力に等しい。
+    <t>生存時：ターン開始時、このキャラクターの攻撃力は最も高い味方の攻撃力に等しくなる。
 召喚トリガー：戦闘開始時</t>
   </si>
   <si>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -38500,8 +38500,8 @@
       <c r="B12" s="20">
         <v>450.0</v>
       </c>
-      <c r="C12" s="20">
-        <v>3.0</v>
+      <c r="C12" s="21">
+        <v>5.0</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20">

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -38280,8 +38280,8 @@
       <c r="B4" s="20">
         <v>18.0</v>
       </c>
-      <c r="C4" s="20">
-        <v>1.0</v>
+      <c r="C4" s="21">
+        <v>1.1</v>
       </c>
       <c r="D4" s="20"/>
       <c r="E4" s="20">
@@ -38306,8 +38306,8 @@
       <c r="B5" s="22">
         <v>23.0</v>
       </c>
-      <c r="C5" s="22">
-        <v>1.0</v>
+      <c r="C5" s="23">
+        <v>1.2</v>
       </c>
       <c r="D5" s="22"/>
       <c r="E5" s="22">
@@ -38332,8 +38332,8 @@
       <c r="B6" s="20">
         <v>31.0</v>
       </c>
-      <c r="C6" s="20">
-        <v>1.0</v>
+      <c r="C6" s="21">
+        <v>1.5</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>339</v>
@@ -38416,8 +38416,8 @@
       <c r="B9" s="22">
         <v>270.0</v>
       </c>
-      <c r="C9" s="22">
-        <v>2.0</v>
+      <c r="C9" s="23">
+        <v>2.2</v>
       </c>
       <c r="D9" s="22"/>
       <c r="E9" s="22">
@@ -38442,8 +38442,8 @@
       <c r="B10" s="20">
         <v>340.0</v>
       </c>
-      <c r="C10" s="20">
-        <v>2.0</v>
+      <c r="C10" s="21">
+        <v>2.4</v>
       </c>
       <c r="D10" s="20"/>
       <c r="E10" s="20">
@@ -38468,8 +38468,8 @@
       <c r="B11" s="22">
         <v>600.0</v>
       </c>
-      <c r="C11" s="22">
-        <v>2.0</v>
+      <c r="C11" s="23">
+        <v>2.8</v>
       </c>
       <c r="D11" s="22" t="s">
         <v>339</v>
@@ -38501,7 +38501,7 @@
         <v>450.0</v>
       </c>
       <c r="C12" s="21">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="D12" s="20"/>
       <c r="E12" s="20">
@@ -38526,8 +38526,8 @@
       <c r="B13" s="22">
         <v>450.0</v>
       </c>
-      <c r="C13" s="22">
-        <v>3.0</v>
+      <c r="C13" s="23">
+        <v>4.0</v>
       </c>
       <c r="D13" s="22"/>
       <c r="E13" s="22">
@@ -38552,8 +38552,8 @@
       <c r="B14" s="20">
         <v>450.0</v>
       </c>
-      <c r="C14" s="20">
-        <v>3.0</v>
+      <c r="C14" s="21">
+        <v>4.3</v>
       </c>
       <c r="D14" s="20"/>
       <c r="E14" s="20">
@@ -38578,8 +38578,8 @@
       <c r="B15" s="22">
         <v>585.0</v>
       </c>
-      <c r="C15" s="22">
-        <v>3.0</v>
+      <c r="C15" s="23">
+        <v>4.6</v>
       </c>
       <c r="D15" s="22"/>
       <c r="E15" s="22">
@@ -38604,8 +38604,8 @@
       <c r="B16" s="20">
         <v>765.0</v>
       </c>
-      <c r="C16" s="20">
-        <v>3.0</v>
+      <c r="C16" s="21">
+        <v>5.0</v>
       </c>
       <c r="D16" s="20" t="s">
         <v>339</v>
@@ -38636,8 +38636,8 @@
       <c r="B17" s="22">
         <v>4050.0</v>
       </c>
-      <c r="C17" s="22">
-        <v>4.0</v>
+      <c r="C17" s="23">
+        <v>8.0</v>
       </c>
       <c r="D17" s="22"/>
       <c r="E17" s="22">
@@ -38662,8 +38662,8 @@
       <c r="B18" s="20">
         <v>4050.0</v>
       </c>
-      <c r="C18" s="20">
-        <v>4.0</v>
+      <c r="C18" s="21">
+        <v>8.5</v>
       </c>
       <c r="D18" s="20"/>
       <c r="E18" s="20">
@@ -38688,8 +38688,8 @@
       <c r="B19" s="22">
         <v>4050.0</v>
       </c>
-      <c r="C19" s="22">
-        <v>4.0</v>
+      <c r="C19" s="23">
+        <v>9.0</v>
       </c>
       <c r="D19" s="22"/>
       <c r="E19" s="22">
@@ -38714,8 +38714,8 @@
       <c r="B20" s="20">
         <v>5265.0</v>
       </c>
-      <c r="C20" s="20">
-        <v>4.0</v>
+      <c r="C20" s="21">
+        <v>9.5</v>
       </c>
       <c r="D20" s="20"/>
       <c r="E20" s="20">
@@ -38740,8 +38740,8 @@
       <c r="B21" s="22">
         <v>6885.0</v>
       </c>
-      <c r="C21" s="22">
-        <v>4.0</v>
+      <c r="C21" s="23">
+        <v>10.0</v>
       </c>
       <c r="D21" s="22" t="s">
         <v>339</v>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -38333,7 +38333,7 @@
         <v>31.0</v>
       </c>
       <c r="C6" s="21">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>339</v>

--- a/js/Vesselbound_data.xlsx
+++ b/js/Vesselbound_data.xlsx
@@ -38333,7 +38333,7 @@
         <v>31.0</v>
       </c>
       <c r="C6" s="21">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="D6" s="20" t="s">
         <v>339</v>
